--- a/backend/media/templates/SPI-Final-78.xlsx
+++ b/backend/media/templates/SPI-Final-78.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Forhath PC\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C632680-759C-4D56-9223-4DBEE97FDBF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD33CFA5-637C-4B40-8045-5B6053186BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="570" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="570" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Helper-1" sheetId="10" state="hidden" r:id="rId1"/>
@@ -307,9 +307,6 @@
     <t>12.Warp and weft defect</t>
   </si>
   <si>
-    <t>13.Yarn severance</t>
-  </si>
-  <si>
     <t>1.Hue difference</t>
   </si>
   <si>
@@ -572,6 +569,9 @@
   </si>
   <si>
     <t>E: Others</t>
+  </si>
+  <si>
+    <t>45.Yarn severance</t>
   </si>
 </sst>
 </file>
@@ -1224,7 +1224,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="54">
+  <borders count="59">
     <border>
       <left/>
       <right/>
@@ -1909,6 +1909,61 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="198">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2405,7 +2460,7 @@
     <xf numFmtId="9" fontId="64" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="178">
+  <cellXfs count="185">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2690,10 +2745,6 @@
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="2" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="66" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
       <protection hidden="1"/>
@@ -2771,53 +2822,122 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="5" fillId="2" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="63" fillId="5" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="5" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="63" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="69" fillId="0" borderId="14" xfId="197" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="69" fillId="0" borderId="17" xfId="197" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="69" fillId="0" borderId="29" xfId="197" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="62" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="59" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="16" fontId="5" fillId="2" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="59" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="59" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="59" fillId="36" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="59" fillId="36" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="59" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="10" fontId="58" fillId="0" borderId="41" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="58" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="34" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="34" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-      <protection hidden="1"/>
+    <xf numFmtId="49" fontId="68" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-      <protection hidden="1"/>
+    <xf numFmtId="49" fontId="68" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-      <protection hidden="1"/>
+    <xf numFmtId="49" fontId="68" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2867,6 +2987,14 @@
     <xf numFmtId="0" fontId="57" fillId="28" borderId="27" xfId="123" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="5" fillId="2" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="5" fillId="2" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="16" fontId="5" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
       <protection hidden="1"/>
@@ -2875,122 +3003,77 @@
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="49" fontId="68" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="10" fontId="58" fillId="0" borderId="41" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="58" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="34" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="34" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="2" borderId="54" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="2" borderId="55" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="68" fillId="0" borderId="56" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="68" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="68" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="68" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="68" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="16" fontId="59" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="59" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="59" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="59" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="59" fillId="36" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="5" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="5" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="69" fillId="0" borderId="14" xfId="197" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="69" fillId="0" borderId="17" xfId="197" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="69" fillId="0" borderId="29" xfId="197" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="62" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="59" fillId="36" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="63" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="198">
@@ -3360,139 +3443,139 @@
                   <c:v>12.Warp and weft defect</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13.Yarn severance</c:v>
+                  <c:v>1.Hue difference</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.Hue difference</c:v>
+                  <c:v>2.Unevenness</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.Unevenness</c:v>
+                  <c:v>3.Pieces not symmetrical</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3.Pieces not symmetrical</c:v>
+                  <c:v>4.Deformation (Defect in shape)</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4.Deformation (Defect in shape)</c:v>
+                  <c:v>5.Tight or loose part of fabric</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.Tight or loose part of fabric</c:v>
+                  <c:v>6.Uneven seam</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>6.Uneven seam</c:v>
+                  <c:v>7.Spiralty, wrinkle</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>7.Spiralty, wrinkle</c:v>
+                  <c:v>8.PUCKERING</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>8.PUCKERING</c:v>
+                  <c:v>9.Corrugation</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>9.Corrugation</c:v>
+                  <c:v>10.Thread breakage</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>10.Thread breakage</c:v>
+                  <c:v>11.Lack of elasticity</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>11.Lack of elasticity</c:v>
+                  <c:v>12.Incorrect stitching number</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>12.Incorrect stitching number</c:v>
+                  <c:v>13.Stitches out of seam allowance</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>13.Stitches out of seam allowance</c:v>
+                  <c:v>14.Missing stitch</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>14.Missing stitch</c:v>
+                  <c:v>15.Lack of seam allowance</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>15.Lack of seam allowance</c:v>
+                  <c:v>16.Unexpected tuck</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>16.Unexpected tuck</c:v>
+                  <c:v>17.Unexpected fullness</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>17.Unexpected fullness</c:v>
+                  <c:v>18.Needle mark</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>18.Needle mark</c:v>
+                  <c:v>19.Sewing defects caused by machine</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>19.Sewing defects caused by machine</c:v>
+                  <c:v>20.Incorrect size of lining</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>20.Incorrect size of lining</c:v>
+                  <c:v>21.Skipped stitch</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>21.Skipped stitch</c:v>
+                  <c:v>22.Sewing involving unexpected parts</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>22.Sewing involving unexpected parts</c:v>
+                  <c:v>23.Missing sewing process</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>23.Missing sewing process</c:v>
+                  <c:v>24.Mislocated bar-tack</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>24.Mislocated bar-tack</c:v>
+                  <c:v>25.Incorrect thread tension</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>25.Incorrect thread tension</c:v>
+                  <c:v>26.Falling off of a thread</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>26.Falling off of a thread</c:v>
+                  <c:v>27.Lack of reverse stitch</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>27.Lack of reverse stitch</c:v>
+                  <c:v>28.Incorrect easing</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>28.Incorrect easing</c:v>
+                  <c:v>29.Piecing defect</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>29.Piecing defect</c:v>
+                  <c:v>30.Incorrect lapped seam</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>30.Incorrect lapped seam</c:v>
+                  <c:v>31.Incorrect trimming</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>31.Incorrect trimming</c:v>
+                  <c:v>32.Lack of strength</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>32.Lack of strength</c:v>
+                  <c:v>33.Incorrect buttonhole sewing</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>33.Incorrect buttonhole sewing</c:v>
+                  <c:v>34.Incorrect brand label sewing</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>34.Incorrect brand label sewing</c:v>
+                  <c:v>35.Sewing slip</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>35.Sewing slip</c:v>
+                  <c:v>36.Incorrect position</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>36.Incorrect position</c:v>
+                  <c:v>37.Incorrect pattern matching</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>37.Incorrect pattern matching</c:v>
+                  <c:v>38.Peel off glue/delamination</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>38.Peel off glue/delamination</c:v>
+                  <c:v>39.Visible/see through glue</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>39.Visible/see through glue</c:v>
+                  <c:v>40.Bonding seam uneven/wavy</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>40.Bonding seam uneven/wavy</c:v>
+                  <c:v>41.Bonding seam not catch up/bad selvaged</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>41.Bonding seam not catch up/bad selvaged</c:v>
+                  <c:v>42.Stick glue/leaking glue</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>42.Stick glue/leaking glue</c:v>
+                  <c:v>43.Mold Shape</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>43.Mold Shape</c:v>
+                  <c:v>44.Poor application glue position</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>44.Poor application glue position</c:v>
+                  <c:v>45.Yarn severance</c:v>
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.Unsecured rivet and snap buttons</c:v>
@@ -4273,139 +4356,139 @@
                   <c:v>12.Warp and weft defect</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13.Yarn severance</c:v>
+                  <c:v>1.Hue difference</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.Hue difference</c:v>
+                  <c:v>2.Unevenness</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.Unevenness</c:v>
+                  <c:v>3.Pieces not symmetrical</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3.Pieces not symmetrical</c:v>
+                  <c:v>4.Deformation (Defect in shape)</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4.Deformation (Defect in shape)</c:v>
+                  <c:v>5.Tight or loose part of fabric</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.Tight or loose part of fabric</c:v>
+                  <c:v>6.Uneven seam</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>6.Uneven seam</c:v>
+                  <c:v>7.Spiralty, wrinkle</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>7.Spiralty, wrinkle</c:v>
+                  <c:v>8.PUCKERING</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>8.PUCKERING</c:v>
+                  <c:v>9.Corrugation</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>9.Corrugation</c:v>
+                  <c:v>10.Thread breakage</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>10.Thread breakage</c:v>
+                  <c:v>11.Lack of elasticity</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>11.Lack of elasticity</c:v>
+                  <c:v>12.Incorrect stitching number</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>12.Incorrect stitching number</c:v>
+                  <c:v>13.Stitches out of seam allowance</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>13.Stitches out of seam allowance</c:v>
+                  <c:v>14.Missing stitch</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>14.Missing stitch</c:v>
+                  <c:v>15.Lack of seam allowance</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>15.Lack of seam allowance</c:v>
+                  <c:v>16.Unexpected tuck</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>16.Unexpected tuck</c:v>
+                  <c:v>17.Unexpected fullness</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>17.Unexpected fullness</c:v>
+                  <c:v>18.Needle mark</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>18.Needle mark</c:v>
+                  <c:v>19.Sewing defects caused by machine</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>19.Sewing defects caused by machine</c:v>
+                  <c:v>20.Incorrect size of lining</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>20.Incorrect size of lining</c:v>
+                  <c:v>21.Skipped stitch</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>21.Skipped stitch</c:v>
+                  <c:v>22.Sewing involving unexpected parts</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>22.Sewing involving unexpected parts</c:v>
+                  <c:v>23.Missing sewing process</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>23.Missing sewing process</c:v>
+                  <c:v>24.Mislocated bar-tack</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>24.Mislocated bar-tack</c:v>
+                  <c:v>25.Incorrect thread tension</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>25.Incorrect thread tension</c:v>
+                  <c:v>26.Falling off of a thread</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>26.Falling off of a thread</c:v>
+                  <c:v>27.Lack of reverse stitch</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>27.Lack of reverse stitch</c:v>
+                  <c:v>28.Incorrect easing</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>28.Incorrect easing</c:v>
+                  <c:v>29.Piecing defect</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>29.Piecing defect</c:v>
+                  <c:v>30.Incorrect lapped seam</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>30.Incorrect lapped seam</c:v>
+                  <c:v>31.Incorrect trimming</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>31.Incorrect trimming</c:v>
+                  <c:v>32.Lack of strength</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>32.Lack of strength</c:v>
+                  <c:v>33.Incorrect buttonhole sewing</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>33.Incorrect buttonhole sewing</c:v>
+                  <c:v>34.Incorrect brand label sewing</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>34.Incorrect brand label sewing</c:v>
+                  <c:v>35.Sewing slip</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>35.Sewing slip</c:v>
+                  <c:v>36.Incorrect position</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>36.Incorrect position</c:v>
+                  <c:v>37.Incorrect pattern matching</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>37.Incorrect pattern matching</c:v>
+                  <c:v>38.Peel off glue/delamination</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>38.Peel off glue/delamination</c:v>
+                  <c:v>39.Visible/see through glue</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>39.Visible/see through glue</c:v>
+                  <c:v>40.Bonding seam uneven/wavy</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>40.Bonding seam uneven/wavy</c:v>
+                  <c:v>41.Bonding seam not catch up/bad selvaged</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>41.Bonding seam not catch up/bad selvaged</c:v>
+                  <c:v>42.Stick glue/leaking glue</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>42.Stick glue/leaking glue</c:v>
+                  <c:v>43.Mold Shape</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>43.Mold Shape</c:v>
+                  <c:v>44.Poor application glue position</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>44.Poor application glue position</c:v>
+                  <c:v>45.Yarn severance</c:v>
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.Unsecured rivet and snap buttons</c:v>
@@ -5511,43 +5594,43 @@
     <row r="1" spans="1:18" ht="24" customHeight="1" thickBot="1">
       <c r="A1" s="64" t="str" cm="1">
         <f t="array" ref="A1">_xlfn.TEXTJOIN(",", TRUE, IF(Final!$Z$1:$CY$1&lt;&gt;"", COLUMN(Final!$Z$1:$CY$1)-COLUMN(Final!$Z$1)+1, ""))</f>
-        <v>1,14,58,67,73,76</v>
+        <v>1,13,58,67,73,76</v>
       </c>
       <c r="B1" s="64" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1" s="65" t="s">
         <v>150</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="D1" s="66" t="s">
         <v>151</v>
       </c>
-      <c r="D1" s="66" t="s">
+      <c r="E1" s="67" t="s">
         <v>152</v>
       </c>
-      <c r="E1" s="67" t="s">
+      <c r="F1" s="64" t="s">
         <v>153</v>
       </c>
-      <c r="F1" s="64" t="s">
+      <c r="G1" s="64" t="s">
         <v>154</v>
       </c>
-      <c r="G1" s="64" t="s">
+      <c r="H1" s="65" t="s">
         <v>155</v>
       </c>
-      <c r="H1" s="65" t="s">
+      <c r="I1" s="68" t="s">
         <v>156</v>
       </c>
-      <c r="I1" s="68" t="s">
+      <c r="J1" s="69" t="s">
         <v>157</v>
       </c>
-      <c r="J1" s="69" t="s">
+      <c r="K1" s="69" t="s">
         <v>158</v>
       </c>
-      <c r="K1" s="69" t="s">
+      <c r="L1" s="70" t="s">
         <v>159</v>
       </c>
-      <c r="L1" s="70" t="s">
+      <c r="M1" s="70" t="s">
         <v>160</v>
-      </c>
-      <c r="M1" s="70" t="s">
-        <v>161</v>
       </c>
       <c r="N1" s="72"/>
     </row>
@@ -5576,11 +5659,11 @@
         <f t="shared" ref="F2:F33" si="0">INDEX($A:$A, MATCH(G2, $B:$B, 0))</f>
         <v>#N/A</v>
       </c>
-      <c r="G2" s="105" t="e">
+      <c r="G2" s="104" t="e">
         <f t="shared" ref="G2:G33" si="1">INDEX($B$2:$B$79,MATCH(ROW()-1,$E$2:$E$79,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="H2" s="107" t="e">
+      <c r="H2" s="106" t="e">
         <f>IF(ISBLANK(D2),"",D2/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -5588,7 +5671,7 @@
         <f>IF(AND(INDEX($C$2:$C$79,MATCH(ROW()-1,$E$2:$E$79,0))=0,INDEX($D$2:$D$79,MATCH(ROW()-1,$E$2:$E$79,0))=0),"",INDEX($D$2:$D$79,MATCH(ROW()-1,$E$2:$E$79,0)))</f>
         <v>#N/A</v>
       </c>
-      <c r="J2" s="110" t="e" cm="1">
+      <c r="J2" s="109" t="e" cm="1">
         <f t="array" ref="J2">IF(COUNTIF($I$2:I2, I2)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I2, ""))), "")</f>
         <v>#N/A</v>
       </c>
@@ -5647,11 +5730,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G3" s="106" t="e">
+      <c r="G3" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H3" s="108" t="e">
+      <c r="H3" s="107" t="e">
         <f>IF(ISBLANK(D3),"",D3/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -5659,7 +5742,7 @@
         <f t="shared" ref="I3:I66" si="2">IF(AND(INDEX($C$2:$C$79,MATCH(ROW()-1,$E$2:$E$79,0))=0,INDEX($D$2:$D$79,MATCH(ROW()-1,$E$2:$E$79,0))=0),"",INDEX($D$2:$D$79,MATCH(ROW()-1,$E$2:$E$79,0)))</f>
         <v>#N/A</v>
       </c>
-      <c r="J3" s="110" t="str" cm="1">
+      <c r="J3" s="109" t="str" cm="1">
         <f t="array" ref="J3">IF(COUNTIF($I$2:I3, I3)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I3, ""))), "")</f>
         <v/>
       </c>
@@ -5718,11 +5801,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G4" s="106" t="e">
+      <c r="G4" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H4" s="108" t="e">
+      <c r="H4" s="107" t="e">
         <f>IF(ISBLANK(D4),"",D4/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -5730,7 +5813,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J4" s="110" t="str" cm="1">
+      <c r="J4" s="109" t="str" cm="1">
         <f t="array" ref="J4">IF(COUNTIF($I$2:I4, I4)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I4, ""))), "")</f>
         <v/>
       </c>
@@ -5789,11 +5872,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G5" s="106" t="e">
+      <c r="G5" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H5" s="108" t="e">
+      <c r="H5" s="107" t="e">
         <f>IF(ISBLANK(D5),"",D5/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -5801,7 +5884,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J5" s="110" t="str" cm="1">
+      <c r="J5" s="109" t="str" cm="1">
         <f t="array" ref="J5">IF(COUNTIF($I$2:I5, I5)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I5, ""))), "")</f>
         <v/>
       </c>
@@ -5860,11 +5943,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G6" s="106" t="e">
+      <c r="G6" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H6" s="108" t="e">
+      <c r="H6" s="107" t="e">
         <f>IF(ISBLANK(D6),"",D6/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -5872,7 +5955,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J6" s="110" t="str" cm="1">
+      <c r="J6" s="109" t="str" cm="1">
         <f t="array" ref="J6">IF(COUNTIF($I$2:I6, I6)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I6, ""))), "")</f>
         <v/>
       </c>
@@ -5931,11 +6014,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G7" s="106" t="e">
+      <c r="G7" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H7" s="108" t="e">
+      <c r="H7" s="107" t="e">
         <f>IF(ISBLANK(D7),"",D7/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -5943,7 +6026,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J7" s="110" t="str" cm="1">
+      <c r="J7" s="109" t="str" cm="1">
         <f t="array" ref="J7">IF(COUNTIF($I$2:I7, I7)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I7, ""))), "")</f>
         <v/>
       </c>
@@ -5990,11 +6073,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G8" s="106" t="e">
+      <c r="G8" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H8" s="108" t="e">
+      <c r="H8" s="107" t="e">
         <f>IF(ISBLANK(D8),"",D8/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6002,7 +6085,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J8" s="110" t="str" cm="1">
+      <c r="J8" s="109" t="str" cm="1">
         <f t="array" ref="J8">IF(COUNTIF($I$2:I8, I8)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I8, ""))), "")</f>
         <v/>
       </c>
@@ -6049,11 +6132,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G9" s="106" t="e">
+      <c r="G9" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H9" s="108" t="e">
+      <c r="H9" s="107" t="e">
         <f>IF(ISBLANK(D9),"",D9/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6061,7 +6144,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J9" s="110" t="str" cm="1">
+      <c r="J9" s="109" t="str" cm="1">
         <f t="array" ref="J9">IF(COUNTIF($I$2:I9, I9)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I9, ""))), "")</f>
         <v/>
       </c>
@@ -6108,11 +6191,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G10" s="106" t="e">
+      <c r="G10" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H10" s="108" t="e">
+      <c r="H10" s="107" t="e">
         <f>IF(ISBLANK(D10),"",D10/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6120,7 +6203,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J10" s="110" t="str" cm="1">
+      <c r="J10" s="109" t="str" cm="1">
         <f t="array" ref="J10">IF(COUNTIF($I$2:I10, I10)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I10, ""))), "")</f>
         <v/>
       </c>
@@ -6167,11 +6250,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G11" s="106" t="e">
+      <c r="G11" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H11" s="108" t="e">
+      <c r="H11" s="107" t="e">
         <f>IF(ISBLANK(D11),"",D11/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6179,7 +6262,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J11" s="110" t="str" cm="1">
+      <c r="J11" s="109" t="str" cm="1">
         <f t="array" ref="J11">IF(COUNTIF($I$2:I11, I11)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I11, ""))), "")</f>
         <v/>
       </c>
@@ -6226,11 +6309,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G12" s="106" t="e">
+      <c r="G12" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H12" s="108" t="e">
+      <c r="H12" s="107" t="e">
         <f>IF(ISBLANK(D12),"",D12/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6238,7 +6321,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J12" s="110" t="str" cm="1">
+      <c r="J12" s="109" t="str" cm="1">
         <f t="array" ref="J12">IF(COUNTIF($I$2:I12, I12)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I12, ""))), "")</f>
         <v/>
       </c>
@@ -6285,11 +6368,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G13" s="106" t="e">
+      <c r="G13" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H13" s="108" t="e">
+      <c r="H13" s="107" t="e">
         <f>IF(ISBLANK(D13),"",D13/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6297,7 +6380,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J13" s="110" t="str" cm="1">
+      <c r="J13" s="109" t="str" cm="1">
         <f t="array" ref="J13">IF(COUNTIF($I$2:I13, I13)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I13, ""))), "")</f>
         <v/>
       </c>
@@ -6326,7 +6409,7 @@
       </c>
       <c r="B14" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>13.Yarn severance</v>
+        <v>1.Hue difference</v>
       </c>
       <c r="C14" s="74" t="e">
         <f>IF(ISBLANK(D14),"",D14/Final!$W$4)</f>
@@ -6344,11 +6427,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G14" s="106" t="e">
+      <c r="G14" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H14" s="108" t="e">
+      <c r="H14" s="107" t="e">
         <f>IF(ISBLANK(D14),"",D14/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6356,7 +6439,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J14" s="110" t="str" cm="1">
+      <c r="J14" s="109" t="str" cm="1">
         <f t="array" ref="J14">IF(COUNTIF($I$2:I14, I14)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I14, ""))), "")</f>
         <v/>
       </c>
@@ -6379,13 +6462,13 @@
       <c r="R14" s="81"/>
     </row>
     <row r="15" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A15" s="73" t="str" cm="1">
+      <c r="A15" s="73" cm="1">
         <f t="array" ref="A15">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A14), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B15" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>1.Hue difference</v>
+        <v>2.Unevenness</v>
       </c>
       <c r="C15" s="74" t="e">
         <f>IF(ISBLANK(D15),"",D15/Final!$W$4)</f>
@@ -6403,11 +6486,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G15" s="106" t="e">
+      <c r="G15" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H15" s="108" t="e">
+      <c r="H15" s="107" t="e">
         <f>IF(ISBLANK(D15),"",D15/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6415,7 +6498,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J15" s="110" t="str" cm="1">
+      <c r="J15" s="109" t="str" cm="1">
         <f t="array" ref="J15">IF(COUNTIF($I$2:I15, I15)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I15, ""))), "")</f>
         <v/>
       </c>
@@ -6438,13 +6521,13 @@
       <c r="R15" s="81"/>
     </row>
     <row r="16" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A16" s="73" t="str" cm="1">
+      <c r="A16" s="73" cm="1">
         <f t="array" ref="A16">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A15), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B16" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>2.Unevenness</v>
+        <v>3.Pieces not symmetrical</v>
       </c>
       <c r="C16" s="74" t="e">
         <f>IF(ISBLANK(D16),"",D16/Final!$W$4)</f>
@@ -6462,11 +6545,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G16" s="106" t="e">
+      <c r="G16" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H16" s="108" t="e">
+      <c r="H16" s="107" t="e">
         <f>IF(ISBLANK(D16),"",D16/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6474,7 +6557,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J16" s="110" t="str" cm="1">
+      <c r="J16" s="109" t="str" cm="1">
         <f t="array" ref="J16">IF(COUNTIF($I$2:I16, I16)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I16, ""))), "")</f>
         <v/>
       </c>
@@ -6497,13 +6580,13 @@
       <c r="R16" s="81"/>
     </row>
     <row r="17" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A17" s="73" t="str" cm="1">
+      <c r="A17" s="73" cm="1">
         <f t="array" ref="A17">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A16), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B17" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>3.Pieces not symmetrical</v>
+        <v>4.Deformation (Defect in shape)</v>
       </c>
       <c r="C17" s="74" t="e">
         <f>IF(ISBLANK(D17),"",D17/Final!$W$4)</f>
@@ -6521,11 +6604,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G17" s="106" t="e">
+      <c r="G17" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H17" s="108" t="e">
+      <c r="H17" s="107" t="e">
         <f>IF(ISBLANK(D17),"",D17/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6533,7 +6616,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J17" s="110" t="str" cm="1">
+      <c r="J17" s="109" t="str" cm="1">
         <f t="array" ref="J17">IF(COUNTIF($I$2:I17, I17)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I17, ""))), "")</f>
         <v/>
       </c>
@@ -6556,13 +6639,13 @@
       <c r="R17" s="81"/>
     </row>
     <row r="18" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A18" s="73" t="str" cm="1">
+      <c r="A18" s="73" cm="1">
         <f t="array" ref="A18">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A17), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B18" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>4.Deformation (Defect in shape)</v>
+        <v>5.Tight or loose part of fabric</v>
       </c>
       <c r="C18" s="74" t="e">
         <f>IF(ISBLANK(D18),"",D18/Final!$W$4)</f>
@@ -6580,11 +6663,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G18" s="106" t="e">
+      <c r="G18" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H18" s="108" t="e">
+      <c r="H18" s="107" t="e">
         <f>IF(ISBLANK(D18),"",D18/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6592,7 +6675,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J18" s="110" t="str" cm="1">
+      <c r="J18" s="109" t="str" cm="1">
         <f t="array" ref="J18">IF(COUNTIF($I$2:I18, I18)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I18, ""))), "")</f>
         <v/>
       </c>
@@ -6615,13 +6698,13 @@
       <c r="R18" s="81"/>
     </row>
     <row r="19" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A19" s="73" t="str" cm="1">
+      <c r="A19" s="73" cm="1">
         <f t="array" ref="A19">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A18), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B19" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>5.Tight or loose part of fabric</v>
+        <v>6.Uneven seam</v>
       </c>
       <c r="C19" s="74" t="e">
         <f>IF(ISBLANK(D19),"",D19/Final!$W$4)</f>
@@ -6639,11 +6722,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G19" s="106" t="e">
+      <c r="G19" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H19" s="108" t="e">
+      <c r="H19" s="107" t="e">
         <f>IF(ISBLANK(D19),"",D19/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6651,7 +6734,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J19" s="110" t="str" cm="1">
+      <c r="J19" s="109" t="str" cm="1">
         <f t="array" ref="J19">IF(COUNTIF($I$2:I19, I19)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I19, ""))), "")</f>
         <v/>
       </c>
@@ -6674,13 +6757,13 @@
       <c r="R19" s="81"/>
     </row>
     <row r="20" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A20" s="73" t="str" cm="1">
+      <c r="A20" s="73" cm="1">
         <f t="array" ref="A20">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A19), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B20" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>6.Uneven seam</v>
+        <v>7.Spiralty, wrinkle</v>
       </c>
       <c r="C20" s="74" t="e">
         <f>IF(ISBLANK(D20),"",D20/Final!$W$4)</f>
@@ -6698,11 +6781,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G20" s="106" t="e">
+      <c r="G20" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H20" s="108" t="e">
+      <c r="H20" s="107" t="e">
         <f>IF(ISBLANK(D20),"",D20/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6710,7 +6793,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J20" s="110" t="str" cm="1">
+      <c r="J20" s="109" t="str" cm="1">
         <f t="array" ref="J20">IF(COUNTIF($I$2:I20, I20)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I20, ""))), "")</f>
         <v/>
       </c>
@@ -6733,13 +6816,13 @@
       <c r="R20" s="81"/>
     </row>
     <row r="21" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A21" s="73" t="str" cm="1">
+      <c r="A21" s="73" cm="1">
         <f t="array" ref="A21">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A20), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B21" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>7.Spiralty, wrinkle</v>
+        <v>8.PUCKERING</v>
       </c>
       <c r="C21" s="74" t="e">
         <f>IF(ISBLANK(D21),"",D21/Final!$W$4)</f>
@@ -6757,11 +6840,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G21" s="106" t="e">
+      <c r="G21" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H21" s="108" t="e">
+      <c r="H21" s="107" t="e">
         <f>IF(ISBLANK(D21),"",D21/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6769,7 +6852,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J21" s="110" t="str" cm="1">
+      <c r="J21" s="109" t="str" cm="1">
         <f t="array" ref="J21">IF(COUNTIF($I$2:I21, I21)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I21, ""))), "")</f>
         <v/>
       </c>
@@ -6792,13 +6875,13 @@
       <c r="R21" s="81"/>
     </row>
     <row r="22" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A22" s="73" t="str" cm="1">
+      <c r="A22" s="73" cm="1">
         <f t="array" ref="A22">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A21), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B22" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>8.PUCKERING</v>
+        <v>9.Corrugation</v>
       </c>
       <c r="C22" s="74" t="e">
         <f>IF(ISBLANK(D22),"",D22/Final!$W$4)</f>
@@ -6816,11 +6899,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G22" s="106" t="e">
+      <c r="G22" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H22" s="108" t="e">
+      <c r="H22" s="107" t="e">
         <f>IF(ISBLANK(D22),"",D22/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6828,7 +6911,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J22" s="110" t="str" cm="1">
+      <c r="J22" s="109" t="str" cm="1">
         <f t="array" ref="J22">IF(COUNTIF($I$2:I22, I22)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I22, ""))), "")</f>
         <v/>
       </c>
@@ -6851,13 +6934,13 @@
       <c r="R22" s="81"/>
     </row>
     <row r="23" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A23" s="73" t="str" cm="1">
+      <c r="A23" s="73" cm="1">
         <f t="array" ref="A23">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A22), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B23" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>9.Corrugation</v>
+        <v>10.Thread breakage</v>
       </c>
       <c r="C23" s="74" t="e">
         <f>IF(ISBLANK(D23),"",D23/Final!$W$4)</f>
@@ -6875,11 +6958,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G23" s="106" t="e">
+      <c r="G23" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H23" s="108" t="e">
+      <c r="H23" s="107" t="e">
         <f>IF(ISBLANK(D23),"",D23/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6887,7 +6970,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J23" s="110" t="str" cm="1">
+      <c r="J23" s="109" t="str" cm="1">
         <f t="array" ref="J23">IF(COUNTIF($I$2:I23, I23)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I23, ""))), "")</f>
         <v/>
       </c>
@@ -6910,13 +6993,13 @@
       <c r="R23" s="81"/>
     </row>
     <row r="24" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A24" s="73" t="str" cm="1">
+      <c r="A24" s="73" cm="1">
         <f t="array" ref="A24">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A23), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B24" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>10.Thread breakage</v>
+        <v>11.Lack of elasticity</v>
       </c>
       <c r="C24" s="74" t="e">
         <f>IF(ISBLANK(D24),"",D24/Final!$W$4)</f>
@@ -6934,11 +7017,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G24" s="106" t="e">
+      <c r="G24" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H24" s="108" t="e">
+      <c r="H24" s="107" t="e">
         <f>IF(ISBLANK(D24),"",D24/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6946,7 +7029,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J24" s="110" t="str" cm="1">
+      <c r="J24" s="109" t="str" cm="1">
         <f t="array" ref="J24">IF(COUNTIF($I$2:I24, I24)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I24, ""))), "")</f>
         <v/>
       </c>
@@ -6969,13 +7052,13 @@
       <c r="R24" s="81"/>
     </row>
     <row r="25" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A25" s="73" t="str" cm="1">
+      <c r="A25" s="73" cm="1">
         <f t="array" ref="A25">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A24), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B25" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>11.Lack of elasticity</v>
+        <v>12.Incorrect stitching number</v>
       </c>
       <c r="C25" s="74" t="e">
         <f>IF(ISBLANK(D25),"",D25/Final!$W$4)</f>
@@ -6993,11 +7076,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G25" s="106" t="e">
+      <c r="G25" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H25" s="108" t="e">
+      <c r="H25" s="107" t="e">
         <f>IF(ISBLANK(D25),"",D25/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7005,7 +7088,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J25" s="110" t="str" cm="1">
+      <c r="J25" s="109" t="str" cm="1">
         <f t="array" ref="J25">IF(COUNTIF($I$2:I25, I25)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I25, ""))), "")</f>
         <v/>
       </c>
@@ -7028,13 +7111,13 @@
       <c r="R25" s="81"/>
     </row>
     <row r="26" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A26" s="73" t="str" cm="1">
+      <c r="A26" s="73" cm="1">
         <f t="array" ref="A26">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A25), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B26" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>12.Incorrect stitching number</v>
+        <v>13.Stitches out of seam allowance</v>
       </c>
       <c r="C26" s="74" t="e">
         <f>IF(ISBLANK(D26),"",D26/Final!$W$4)</f>
@@ -7052,11 +7135,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G26" s="106" t="e">
+      <c r="G26" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H26" s="108" t="e">
+      <c r="H26" s="107" t="e">
         <f>IF(ISBLANK(D26),"",D26/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7064,7 +7147,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J26" s="110" t="str" cm="1">
+      <c r="J26" s="109" t="str" cm="1">
         <f t="array" ref="J26">IF(COUNTIF($I$2:I26, I26)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I26, ""))), "")</f>
         <v/>
       </c>
@@ -7087,13 +7170,13 @@
       <c r="R26" s="81"/>
     </row>
     <row r="27" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A27" s="73" t="str" cm="1">
+      <c r="A27" s="73" cm="1">
         <f t="array" ref="A27">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A26), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B27" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>13.Stitches out of seam allowance</v>
+        <v>14.Missing stitch</v>
       </c>
       <c r="C27" s="74" t="e">
         <f>IF(ISBLANK(D27),"",D27/Final!$W$4)</f>
@@ -7111,11 +7194,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G27" s="106" t="e">
+      <c r="G27" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H27" s="108" t="e">
+      <c r="H27" s="107" t="e">
         <f>IF(ISBLANK(D27),"",D27/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7123,7 +7206,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J27" s="110" t="str" cm="1">
+      <c r="J27" s="109" t="str" cm="1">
         <f t="array" ref="J27">IF(COUNTIF($I$2:I27, I27)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I27, ""))), "")</f>
         <v/>
       </c>
@@ -7146,13 +7229,13 @@
       <c r="R27" s="81"/>
     </row>
     <row r="28" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A28" s="73" t="str" cm="1">
+      <c r="A28" s="73" cm="1">
         <f t="array" ref="A28">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A27), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B28" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>14.Missing stitch</v>
+        <v>15.Lack of seam allowance</v>
       </c>
       <c r="C28" s="74" t="e">
         <f>IF(ISBLANK(D28),"",D28/Final!$W$4)</f>
@@ -7170,11 +7253,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G28" s="106" t="e">
+      <c r="G28" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H28" s="108" t="e">
+      <c r="H28" s="107" t="e">
         <f>IF(ISBLANK(D28),"",D28/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7182,7 +7265,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J28" s="110" t="str" cm="1">
+      <c r="J28" s="109" t="str" cm="1">
         <f t="array" ref="J28">IF(COUNTIF($I$2:I28, I28)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I28, ""))), "")</f>
         <v/>
       </c>
@@ -7205,13 +7288,13 @@
       <c r="R28" s="81"/>
     </row>
     <row r="29" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A29" s="73" t="str" cm="1">
+      <c r="A29" s="73" cm="1">
         <f t="array" ref="A29">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A28), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B29" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>15.Lack of seam allowance</v>
+        <v>16.Unexpected tuck</v>
       </c>
       <c r="C29" s="74" t="e">
         <f>IF(ISBLANK(D29),"",D29/Final!$W$4)</f>
@@ -7229,11 +7312,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G29" s="106" t="e">
+      <c r="G29" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H29" s="108" t="e">
+      <c r="H29" s="107" t="e">
         <f>IF(ISBLANK(D29),"",D29/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7241,7 +7324,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J29" s="110" t="str" cm="1">
+      <c r="J29" s="109" t="str" cm="1">
         <f t="array" ref="J29">IF(COUNTIF($I$2:I29, I29)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I29, ""))), "")</f>
         <v/>
       </c>
@@ -7264,13 +7347,13 @@
       <c r="R29" s="81"/>
     </row>
     <row r="30" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A30" s="73" t="str" cm="1">
+      <c r="A30" s="73" cm="1">
         <f t="array" ref="A30">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A29), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B30" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>16.Unexpected tuck</v>
+        <v>17.Unexpected fullness</v>
       </c>
       <c r="C30" s="74" t="e">
         <f>IF(ISBLANK(D30),"",D30/Final!$W$4)</f>
@@ -7288,11 +7371,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G30" s="106" t="e">
+      <c r="G30" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H30" s="108" t="e">
+      <c r="H30" s="107" t="e">
         <f>IF(ISBLANK(D30),"",D30/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7300,7 +7383,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J30" s="110" t="str" cm="1">
+      <c r="J30" s="109" t="str" cm="1">
         <f t="array" ref="J30">IF(COUNTIF($I$2:I30, I30)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I30, ""))), "")</f>
         <v/>
       </c>
@@ -7323,13 +7406,13 @@
       <c r="R30" s="81"/>
     </row>
     <row r="31" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A31" s="73" t="str" cm="1">
+      <c r="A31" s="73" cm="1">
         <f t="array" ref="A31">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A30), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B31" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>17.Unexpected fullness</v>
+        <v>18.Needle mark</v>
       </c>
       <c r="C31" s="74" t="e">
         <f>IF(ISBLANK(D31),"",D31/Final!$W$4)</f>
@@ -7347,11 +7430,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G31" s="106" t="e">
+      <c r="G31" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H31" s="108" t="e">
+      <c r="H31" s="107" t="e">
         <f>IF(ISBLANK(D31),"",D31/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7359,7 +7442,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J31" s="110" t="str" cm="1">
+      <c r="J31" s="109" t="str" cm="1">
         <f t="array" ref="J31">IF(COUNTIF($I$2:I31, I31)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I31, ""))), "")</f>
         <v/>
       </c>
@@ -7382,13 +7465,13 @@
       <c r="R31" s="81"/>
     </row>
     <row r="32" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A32" s="73" t="str" cm="1">
+      <c r="A32" s="73" cm="1">
         <f t="array" ref="A32">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A31), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B32" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>18.Needle mark</v>
+        <v>19.Sewing defects caused by machine</v>
       </c>
       <c r="C32" s="74" t="e">
         <f>IF(ISBLANK(D32),"",D32/Final!$W$4)</f>
@@ -7406,11 +7489,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G32" s="106" t="e">
+      <c r="G32" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H32" s="108" t="e">
+      <c r="H32" s="107" t="e">
         <f>IF(ISBLANK(D32),"",D32/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7418,7 +7501,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J32" s="110" t="str" cm="1">
+      <c r="J32" s="109" t="str" cm="1">
         <f t="array" ref="J32">IF(COUNTIF($I$2:I32, I32)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I32, ""))), "")</f>
         <v/>
       </c>
@@ -7441,13 +7524,13 @@
       <c r="R32" s="81"/>
     </row>
     <row r="33" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A33" s="73" t="str" cm="1">
+      <c r="A33" s="73" cm="1">
         <f t="array" ref="A33">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A32), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B33" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>19.Sewing defects caused by machine</v>
+        <v>20.Incorrect size of lining</v>
       </c>
       <c r="C33" s="74" t="e">
         <f>IF(ISBLANK(D33),"",D33/Final!$W$4)</f>
@@ -7465,11 +7548,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G33" s="106" t="e">
+      <c r="G33" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H33" s="108" t="e">
+      <c r="H33" s="107" t="e">
         <f>IF(ISBLANK(D33),"",D33/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7477,7 +7560,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J33" s="110" t="str" cm="1">
+      <c r="J33" s="109" t="str" cm="1">
         <f t="array" ref="J33">IF(COUNTIF($I$2:I33, I33)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I33, ""))), "")</f>
         <v/>
       </c>
@@ -7500,13 +7583,13 @@
       <c r="R33" s="81"/>
     </row>
     <row r="34" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A34" s="73" t="str" cm="1">
+      <c r="A34" s="73" cm="1">
         <f t="array" ref="A34">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A33), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B34" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>20.Incorrect size of lining</v>
+        <v>21.Skipped stitch</v>
       </c>
       <c r="C34" s="74" t="e">
         <f>IF(ISBLANK(D34),"",D34/Final!$W$4)</f>
@@ -7524,11 +7607,11 @@
         <f t="shared" ref="F34:F65" si="4">INDEX($A:$A, MATCH(G34, $B:$B, 0))</f>
         <v>#N/A</v>
       </c>
-      <c r="G34" s="106" t="e">
+      <c r="G34" s="105" t="e">
         <f t="shared" ref="G34:G65" si="5">INDEX($B$2:$B$79,MATCH(ROW()-1,$E$2:$E$79,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="H34" s="108" t="e">
+      <c r="H34" s="107" t="e">
         <f>IF(ISBLANK(D34),"",D34/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7536,7 +7619,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J34" s="110" t="str" cm="1">
+      <c r="J34" s="109" t="str" cm="1">
         <f t="array" ref="J34">IF(COUNTIF($I$2:I34, I34)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I34, ""))), "")</f>
         <v/>
       </c>
@@ -7559,13 +7642,13 @@
       <c r="R34" s="81"/>
     </row>
     <row r="35" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A35" s="73" t="str" cm="1">
+      <c r="A35" s="73" cm="1">
         <f t="array" ref="A35">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A34), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B35" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>21.Skipped stitch</v>
+        <v>22.Sewing involving unexpected parts</v>
       </c>
       <c r="C35" s="74" t="e">
         <f>IF(ISBLANK(D35),"",D35/Final!$W$4)</f>
@@ -7583,11 +7666,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G35" s="106" t="e">
+      <c r="G35" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H35" s="108" t="e">
+      <c r="H35" s="107" t="e">
         <f>IF(ISBLANK(D35),"",D35/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7595,7 +7678,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J35" s="110" t="str" cm="1">
+      <c r="J35" s="109" t="str" cm="1">
         <f t="array" ref="J35">IF(COUNTIF($I$2:I35, I35)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I35, ""))), "")</f>
         <v/>
       </c>
@@ -7618,13 +7701,13 @@
       <c r="R35" s="81"/>
     </row>
     <row r="36" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A36" s="73" t="str" cm="1">
+      <c r="A36" s="73" cm="1">
         <f t="array" ref="A36">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A35), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B36" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>22.Sewing involving unexpected parts</v>
+        <v>23.Missing sewing process</v>
       </c>
       <c r="C36" s="74" t="e">
         <f>IF(ISBLANK(D36),"",D36/Final!$W$4)</f>
@@ -7642,11 +7725,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G36" s="106" t="e">
+      <c r="G36" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H36" s="108" t="e">
+      <c r="H36" s="107" t="e">
         <f>IF(ISBLANK(D36),"",D36/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7654,7 +7737,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J36" s="110" t="str" cm="1">
+      <c r="J36" s="109" t="str" cm="1">
         <f t="array" ref="J36">IF(COUNTIF($I$2:I36, I36)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I36, ""))), "")</f>
         <v/>
       </c>
@@ -7677,13 +7760,13 @@
       <c r="R36" s="81"/>
     </row>
     <row r="37" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A37" s="73" t="str" cm="1">
+      <c r="A37" s="73" cm="1">
         <f t="array" ref="A37">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A36), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B37" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>23.Missing sewing process</v>
+        <v>24.Mislocated bar-tack</v>
       </c>
       <c r="C37" s="74" t="e">
         <f>IF(ISBLANK(D37),"",D37/Final!$W$4)</f>
@@ -7701,11 +7784,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G37" s="106" t="e">
+      <c r="G37" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H37" s="108" t="e">
+      <c r="H37" s="107" t="e">
         <f>IF(ISBLANK(D37),"",D37/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7713,7 +7796,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J37" s="110" t="str" cm="1">
+      <c r="J37" s="109" t="str" cm="1">
         <f t="array" ref="J37">IF(COUNTIF($I$2:I37, I37)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I37, ""))), "")</f>
         <v/>
       </c>
@@ -7732,13 +7815,13 @@
       <c r="N37" s="72"/>
     </row>
     <row r="38" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A38" s="73" t="str" cm="1">
+      <c r="A38" s="73" cm="1">
         <f t="array" ref="A38">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A37), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B38" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>24.Mislocated bar-tack</v>
+        <v>25.Incorrect thread tension</v>
       </c>
       <c r="C38" s="74" t="e">
         <f>IF(ISBLANK(D38),"",D38/Final!$W$4)</f>
@@ -7756,11 +7839,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G38" s="106" t="e">
+      <c r="G38" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H38" s="108" t="e">
+      <c r="H38" s="107" t="e">
         <f>IF(ISBLANK(D38),"",D38/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7768,7 +7851,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J38" s="110" t="str" cm="1">
+      <c r="J38" s="109" t="str" cm="1">
         <f t="array" ref="J38">IF(COUNTIF($I$2:I38, I38)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I38, ""))), "")</f>
         <v/>
       </c>
@@ -7787,13 +7870,13 @@
       <c r="N38" s="72"/>
     </row>
     <row r="39" spans="1:18">
-      <c r="A39" s="73" t="str" cm="1">
+      <c r="A39" s="73" cm="1">
         <f t="array" ref="A39">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A38), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B39" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>25.Incorrect thread tension</v>
+        <v>26.Falling off of a thread</v>
       </c>
       <c r="C39" s="74" t="e">
         <f>IF(ISBLANK(D39),"",D39/Final!$W$4)</f>
@@ -7811,11 +7894,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G39" s="106" t="e">
+      <c r="G39" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H39" s="108" t="e">
+      <c r="H39" s="107" t="e">
         <f>IF(ISBLANK(D39),"",D39/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7825,13 +7908,13 @@
       </c>
     </row>
     <row r="40" spans="1:18">
-      <c r="A40" s="73" t="str" cm="1">
+      <c r="A40" s="73" cm="1">
         <f t="array" ref="A40">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A39), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B40" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>26.Falling off of a thread</v>
+        <v>27.Lack of reverse stitch</v>
       </c>
       <c r="C40" s="74" t="e">
         <f>IF(ISBLANK(D40),"",D40/Final!$W$4)</f>
@@ -7849,11 +7932,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G40" s="106" t="e">
+      <c r="G40" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H40" s="108" t="e">
+      <c r="H40" s="107" t="e">
         <f>IF(ISBLANK(D40),"",D40/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7863,13 +7946,13 @@
       </c>
     </row>
     <row r="41" spans="1:18">
-      <c r="A41" s="73" t="str" cm="1">
+      <c r="A41" s="73" cm="1">
         <f t="array" ref="A41">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A40), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B41" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>27.Lack of reverse stitch</v>
+        <v>28.Incorrect easing</v>
       </c>
       <c r="C41" s="74" t="e">
         <f>IF(ISBLANK(D41),"",D41/Final!$W$4)</f>
@@ -7887,11 +7970,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G41" s="106" t="e">
+      <c r="G41" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H41" s="108" t="e">
+      <c r="H41" s="107" t="e">
         <f>IF(ISBLANK(D41),"",D41/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7901,13 +7984,13 @@
       </c>
     </row>
     <row r="42" spans="1:18">
-      <c r="A42" s="73" t="str" cm="1">
+      <c r="A42" s="73" cm="1">
         <f t="array" ref="A42">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A41), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B42" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>28.Incorrect easing</v>
+        <v>29.Piecing defect</v>
       </c>
       <c r="C42" s="74" t="e">
         <f>IF(ISBLANK(D42),"",D42/Final!$W$4)</f>
@@ -7925,11 +8008,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G42" s="106" t="e">
+      <c r="G42" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H42" s="108" t="e">
+      <c r="H42" s="107" t="e">
         <f>IF(ISBLANK(D42),"",D42/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7939,13 +8022,13 @@
       </c>
     </row>
     <row r="43" spans="1:18">
-      <c r="A43" s="73" t="str" cm="1">
+      <c r="A43" s="73" cm="1">
         <f t="array" ref="A43">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A42), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B43" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>29.Piecing defect</v>
+        <v>30.Incorrect lapped seam</v>
       </c>
       <c r="C43" s="74" t="e">
         <f>IF(ISBLANK(D43),"",D43/Final!$W$4)</f>
@@ -7963,11 +8046,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G43" s="106" t="e">
+      <c r="G43" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H43" s="108" t="e">
+      <c r="H43" s="107" t="e">
         <f>IF(ISBLANK(D43),"",D43/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7977,13 +8060,13 @@
       </c>
     </row>
     <row r="44" spans="1:18">
-      <c r="A44" s="73" t="str" cm="1">
+      <c r="A44" s="73" cm="1">
         <f t="array" ref="A44">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A43), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B44" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>30.Incorrect lapped seam</v>
+        <v>31.Incorrect trimming</v>
       </c>
       <c r="C44" s="74" t="e">
         <f>IF(ISBLANK(D44),"",D44/Final!$W$4)</f>
@@ -8001,11 +8084,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G44" s="106" t="e">
+      <c r="G44" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H44" s="108" t="e">
+      <c r="H44" s="107" t="e">
         <f>IF(ISBLANK(D44),"",D44/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8015,13 +8098,13 @@
       </c>
     </row>
     <row r="45" spans="1:18">
-      <c r="A45" s="73" t="str" cm="1">
+      <c r="A45" s="73" cm="1">
         <f t="array" ref="A45">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A44), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B45" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>31.Incorrect trimming</v>
+        <v>32.Lack of strength</v>
       </c>
       <c r="C45" s="74" t="e">
         <f>IF(ISBLANK(D45),"",D45/Final!$W$4)</f>
@@ -8039,11 +8122,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G45" s="106" t="e">
+      <c r="G45" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H45" s="108" t="e">
+      <c r="H45" s="107" t="e">
         <f>IF(ISBLANK(D45),"",D45/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8053,13 +8136,13 @@
       </c>
     </row>
     <row r="46" spans="1:18">
-      <c r="A46" s="73" t="str" cm="1">
+      <c r="A46" s="73" cm="1">
         <f t="array" ref="A46">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A45), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B46" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>32.Lack of strength</v>
+        <v>33.Incorrect buttonhole sewing</v>
       </c>
       <c r="C46" s="74" t="e">
         <f>IF(ISBLANK(D46),"",D46/Final!$W$4)</f>
@@ -8077,11 +8160,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G46" s="106" t="e">
+      <c r="G46" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H46" s="108" t="e">
+      <c r="H46" s="107" t="e">
         <f>IF(ISBLANK(D46),"",D46/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8091,13 +8174,13 @@
       </c>
     </row>
     <row r="47" spans="1:18">
-      <c r="A47" s="73" t="str" cm="1">
+      <c r="A47" s="73" cm="1">
         <f t="array" ref="A47">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A46), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B47" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>33.Incorrect buttonhole sewing</v>
+        <v>34.Incorrect brand label sewing</v>
       </c>
       <c r="C47" s="74" t="e">
         <f>IF(ISBLANK(D47),"",D47/Final!$W$4)</f>
@@ -8115,11 +8198,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G47" s="106" t="e">
+      <c r="G47" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H47" s="108" t="e">
+      <c r="H47" s="107" t="e">
         <f>IF(ISBLANK(D47),"",D47/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8129,13 +8212,13 @@
       </c>
     </row>
     <row r="48" spans="1:18">
-      <c r="A48" s="73" t="str" cm="1">
+      <c r="A48" s="73" cm="1">
         <f t="array" ref="A48">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A47), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B48" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>34.Incorrect brand label sewing</v>
+        <v>35.Sewing slip</v>
       </c>
       <c r="C48" s="74" t="e">
         <f>IF(ISBLANK(D48),"",D48/Final!$W$4)</f>
@@ -8153,11 +8236,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G48" s="106" t="e">
+      <c r="G48" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H48" s="108" t="e">
+      <c r="H48" s="107" t="e">
         <f>IF(ISBLANK(D48),"",D48/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8167,13 +8250,13 @@
       </c>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49" s="73" t="str" cm="1">
+      <c r="A49" s="73" cm="1">
         <f t="array" ref="A49">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A48), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B49" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>35.Sewing slip</v>
+        <v>36.Incorrect position</v>
       </c>
       <c r="C49" s="74" t="e">
         <f>IF(ISBLANK(D49),"",D49/Final!$W$4)</f>
@@ -8191,11 +8274,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G49" s="106" t="e">
+      <c r="G49" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H49" s="108" t="e">
+      <c r="H49" s="107" t="e">
         <f>IF(ISBLANK(D49),"",D49/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8205,13 +8288,13 @@
       </c>
     </row>
     <row r="50" spans="1:9">
-      <c r="A50" s="73" t="str" cm="1">
+      <c r="A50" s="73" cm="1">
         <f t="array" ref="A50">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A49), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B50" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>36.Incorrect position</v>
+        <v>37.Incorrect pattern matching</v>
       </c>
       <c r="C50" s="74" t="e">
         <f>IF(ISBLANK(D50),"",D50/Final!$W$4)</f>
@@ -8229,11 +8312,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G50" s="106" t="e">
+      <c r="G50" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H50" s="108" t="e">
+      <c r="H50" s="107" t="e">
         <f>IF(ISBLANK(D50),"",D50/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8243,13 +8326,13 @@
       </c>
     </row>
     <row r="51" spans="1:9">
-      <c r="A51" s="73" t="str" cm="1">
+      <c r="A51" s="73" cm="1">
         <f t="array" ref="A51">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A50), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B51" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>37.Incorrect pattern matching</v>
+        <v>38.Peel off glue/delamination</v>
       </c>
       <c r="C51" s="74" t="e">
         <f>IF(ISBLANK(D51),"",D51/Final!$W$4)</f>
@@ -8267,11 +8350,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G51" s="106" t="e">
+      <c r="G51" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H51" s="108" t="e">
+      <c r="H51" s="107" t="e">
         <f>IF(ISBLANK(D51),"",D51/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8281,13 +8364,13 @@
       </c>
     </row>
     <row r="52" spans="1:9">
-      <c r="A52" s="73" t="str" cm="1">
+      <c r="A52" s="73" cm="1">
         <f t="array" ref="A52">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A51), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B52" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>38.Peel off glue/delamination</v>
+        <v>39.Visible/see through glue</v>
       </c>
       <c r="C52" s="74" t="e">
         <f>IF(ISBLANK(D52),"",D52/Final!$W$4)</f>
@@ -8305,11 +8388,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G52" s="106" t="e">
+      <c r="G52" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H52" s="108" t="e">
+      <c r="H52" s="107" t="e">
         <f>IF(ISBLANK(D52),"",D52/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8319,13 +8402,13 @@
       </c>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="73" t="str" cm="1">
+      <c r="A53" s="73" cm="1">
         <f t="array" ref="A53">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A52), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B53" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>39.Visible/see through glue</v>
+        <v>40.Bonding seam uneven/wavy</v>
       </c>
       <c r="C53" s="74" t="e">
         <f>IF(ISBLANK(D53),"",D53/Final!$W$4)</f>
@@ -8343,11 +8426,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G53" s="106" t="e">
+      <c r="G53" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H53" s="108" t="e">
+      <c r="H53" s="107" t="e">
         <f>IF(ISBLANK(D53),"",D53/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8357,13 +8440,13 @@
       </c>
     </row>
     <row r="54" spans="1:9">
-      <c r="A54" s="73" t="str" cm="1">
+      <c r="A54" s="73" cm="1">
         <f t="array" ref="A54">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A53), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B54" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>40.Bonding seam uneven/wavy</v>
+        <v>41.Bonding seam not catch up/bad selvaged</v>
       </c>
       <c r="C54" s="74" t="e">
         <f>IF(ISBLANK(D54),"",D54/Final!$W$4)</f>
@@ -8381,11 +8464,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G54" s="106" t="e">
+      <c r="G54" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H54" s="108" t="e">
+      <c r="H54" s="107" t="e">
         <f>IF(ISBLANK(D54),"",D54/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8395,13 +8478,13 @@
       </c>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" s="73" t="str" cm="1">
+      <c r="A55" s="73" cm="1">
         <f t="array" ref="A55">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A54), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B55" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>41.Bonding seam not catch up/bad selvaged</v>
+        <v>42.Stick glue/leaking glue</v>
       </c>
       <c r="C55" s="74" t="e">
         <f>IF(ISBLANK(D55),"",D55/Final!$W$4)</f>
@@ -8419,11 +8502,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G55" s="106" t="e">
+      <c r="G55" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H55" s="108" t="e">
+      <c r="H55" s="107" t="e">
         <f>IF(ISBLANK(D55),"",D55/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8433,13 +8516,13 @@
       </c>
     </row>
     <row r="56" spans="1:9">
-      <c r="A56" s="73" t="str" cm="1">
+      <c r="A56" s="73" cm="1">
         <f t="array" ref="A56">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A55), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B56" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>42.Stick glue/leaking glue</v>
+        <v>43.Mold Shape</v>
       </c>
       <c r="C56" s="74" t="e">
         <f>IF(ISBLANK(D56),"",D56/Final!$W$4)</f>
@@ -8457,11 +8540,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G56" s="106" t="e">
+      <c r="G56" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H56" s="108" t="e">
+      <c r="H56" s="107" t="e">
         <f>IF(ISBLANK(D56),"",D56/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8471,13 +8554,13 @@
       </c>
     </row>
     <row r="57" spans="1:9">
-      <c r="A57" s="73" t="str" cm="1">
+      <c r="A57" s="73" cm="1">
         <f t="array" ref="A57">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A56), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B57" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>43.Mold Shape</v>
+        <v>44.Poor application glue position</v>
       </c>
       <c r="C57" s="74" t="e">
         <f>IF(ISBLANK(D57),"",D57/Final!$W$4)</f>
@@ -8495,11 +8578,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G57" s="106" t="e">
+      <c r="G57" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H57" s="108" t="e">
+      <c r="H57" s="107" t="e">
         <f>IF(ISBLANK(D57),"",D57/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8509,13 +8592,13 @@
       </c>
     </row>
     <row r="58" spans="1:9">
-      <c r="A58" s="73" t="str" cm="1">
+      <c r="A58" s="73" cm="1">
         <f t="array" ref="A58">INDEX(Final!$Z$1:$CY$1, LOOKUP(ROW(A57), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B58" s="73" t="str">
         <f>INDEX(Final!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>44.Poor application glue position</v>
+        <v>45.Yarn severance</v>
       </c>
       <c r="C58" s="74" t="e">
         <f>IF(ISBLANK(D58),"",D58/Final!$W$4)</f>
@@ -8533,11 +8616,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G58" s="106" t="e">
+      <c r="G58" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H58" s="108" t="e">
+      <c r="H58" s="107" t="e">
         <f>IF(ISBLANK(D58),"",D58/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8571,11 +8654,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G59" s="106" t="e">
+      <c r="G59" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H59" s="108" t="e">
+      <c r="H59" s="107" t="e">
         <f>IF(ISBLANK(D59),"",D59/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8609,11 +8692,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G60" s="106" t="e">
+      <c r="G60" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H60" s="108" t="e">
+      <c r="H60" s="107" t="e">
         <f>IF(ISBLANK(D60),"",D60/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8647,11 +8730,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G61" s="106" t="e">
+      <c r="G61" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H61" s="108" t="e">
+      <c r="H61" s="107" t="e">
         <f>IF(ISBLANK(D61),"",D61/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8685,11 +8768,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G62" s="106" t="e">
+      <c r="G62" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H62" s="108" t="e">
+      <c r="H62" s="107" t="e">
         <f>IF(ISBLANK(D62),"",D62/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8723,11 +8806,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G63" s="106" t="e">
+      <c r="G63" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H63" s="108" t="e">
+      <c r="H63" s="107" t="e">
         <f>IF(ISBLANK(D63),"",D63/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8761,11 +8844,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G64" s="106" t="e">
+      <c r="G64" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H64" s="108" t="e">
+      <c r="H64" s="107" t="e">
         <f>IF(ISBLANK(D64),"",D64/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8799,11 +8882,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G65" s="106" t="e">
+      <c r="G65" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H65" s="108" t="e">
+      <c r="H65" s="107" t="e">
         <f>IF(ISBLANK(D65),"",D65/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8837,11 +8920,11 @@
         <f t="shared" ref="F66:F79" si="6">INDEX($A:$A, MATCH(G66, $B:$B, 0))</f>
         <v>#N/A</v>
       </c>
-      <c r="G66" s="106" t="e">
+      <c r="G66" s="105" t="e">
         <f t="shared" ref="G66:G79" si="7">INDEX($B$2:$B$79,MATCH(ROW()-1,$E$2:$E$79,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="H66" s="108" t="e">
+      <c r="H66" s="107" t="e">
         <f>IF(ISBLANK(D66),"",D66/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8875,11 +8958,11 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="G67" s="106" t="e">
+      <c r="G67" s="105" t="e">
         <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
-      <c r="H67" s="108" t="e">
+      <c r="H67" s="107" t="e">
         <f>IF(ISBLANK(D67),"",D67/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8913,11 +8996,11 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="G68" s="106" t="e">
+      <c r="G68" s="105" t="e">
         <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
-      <c r="H68" s="108" t="e">
+      <c r="H68" s="107" t="e">
         <f>IF(ISBLANK(D68),"",D68/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8951,11 +9034,11 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="G69" s="106" t="e">
+      <c r="G69" s="105" t="e">
         <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
-      <c r="H69" s="108" t="e">
+      <c r="H69" s="107" t="e">
         <f>IF(ISBLANK(D69),"",D69/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8989,11 +9072,11 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="G70" s="106" t="e">
+      <c r="G70" s="105" t="e">
         <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
-      <c r="H70" s="108" t="e">
+      <c r="H70" s="107" t="e">
         <f>IF(ISBLANK(D70),"",D70/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9027,11 +9110,11 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="G71" s="106" t="e">
+      <c r="G71" s="105" t="e">
         <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
-      <c r="H71" s="108" t="e">
+      <c r="H71" s="107" t="e">
         <f>IF(ISBLANK(D71),"",D71/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9065,11 +9148,11 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="G72" s="106" t="e">
+      <c r="G72" s="105" t="e">
         <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
-      <c r="H72" s="108" t="e">
+      <c r="H72" s="107" t="e">
         <f>IF(ISBLANK(D72),"",D72/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9103,11 +9186,11 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="G73" s="106" t="e">
+      <c r="G73" s="105" t="e">
         <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
-      <c r="H73" s="108" t="e">
+      <c r="H73" s="107" t="e">
         <f>IF(ISBLANK(D73),"",D73/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9141,11 +9224,11 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="G74" s="106" t="e">
+      <c r="G74" s="105" t="e">
         <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
-      <c r="H74" s="108" t="e">
+      <c r="H74" s="107" t="e">
         <f>IF(ISBLANK(D74),"",D74/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9179,11 +9262,11 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="G75" s="106" t="e">
+      <c r="G75" s="105" t="e">
         <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
-      <c r="H75" s="108" t="e">
+      <c r="H75" s="107" t="e">
         <f>IF(ISBLANK(D75),"",D75/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9217,11 +9300,11 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="G76" s="106" t="e">
+      <c r="G76" s="105" t="e">
         <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
-      <c r="H76" s="108" t="e">
+      <c r="H76" s="107" t="e">
         <f>IF(ISBLANK(D76),"",D76/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9255,11 +9338,11 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="G77" s="106" t="e">
+      <c r="G77" s="105" t="e">
         <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
-      <c r="H77" s="108" t="e">
+      <c r="H77" s="107" t="e">
         <f>IF(ISBLANK(D77),"",D77/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9293,11 +9376,11 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="G78" s="106" t="e">
+      <c r="G78" s="105" t="e">
         <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
-      <c r="H78" s="108" t="e">
+      <c r="H78" s="107" t="e">
         <f>IF(ISBLANK(D78),"",D78/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9331,11 +9414,11 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="G79" s="106" t="e">
+      <c r="G79" s="105" t="e">
         <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
-      <c r="H79" s="109" t="e">
+      <c r="H79" s="108" t="e">
         <f>IF(ISBLANK(D79),"",D79/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9374,43 +9457,43 @@
     <row r="1" spans="1:18" ht="24" customHeight="1" thickBot="1">
       <c r="A1" s="64" t="str" cm="1">
         <f t="array" ref="A1">_xlfn.TEXTJOIN(",", TRUE, IF('Re-Final'!$Z$1:$CY$1&lt;&gt;"", COLUMN('Re-Final'!$Z$1:$CY$1)-COLUMN('Re-Final'!$Z$1)+1, ""))</f>
-        <v>1,14,58,67,73,76</v>
+        <v>1,13,58,67,73,76</v>
       </c>
       <c r="B1" s="64" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1" s="65" t="s">
         <v>150</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="D1" s="66" t="s">
         <v>151</v>
       </c>
-      <c r="D1" s="66" t="s">
+      <c r="E1" s="67" t="s">
         <v>152</v>
       </c>
-      <c r="E1" s="67" t="s">
+      <c r="F1" s="64" t="s">
         <v>153</v>
       </c>
-      <c r="F1" s="64" t="s">
+      <c r="G1" s="64" t="s">
         <v>154</v>
       </c>
-      <c r="G1" s="64" t="s">
+      <c r="H1" s="65" t="s">
         <v>155</v>
       </c>
-      <c r="H1" s="65" t="s">
+      <c r="I1" s="68" t="s">
         <v>156</v>
       </c>
-      <c r="I1" s="68" t="s">
+      <c r="J1" s="69" t="s">
         <v>157</v>
       </c>
-      <c r="J1" s="69" t="s">
+      <c r="K1" s="69" t="s">
         <v>158</v>
       </c>
-      <c r="K1" s="69" t="s">
+      <c r="L1" s="70" t="s">
         <v>159</v>
       </c>
-      <c r="L1" s="70" t="s">
+      <c r="M1" s="71" t="s">
         <v>160</v>
-      </c>
-      <c r="M1" s="71" t="s">
-        <v>161</v>
       </c>
       <c r="N1" s="72"/>
     </row>
@@ -9439,11 +9522,11 @@
         <f t="shared" ref="F2:F33" si="0">INDEX($A:$A, MATCH(G2, $B:$B, 0))</f>
         <v>#N/A</v>
       </c>
-      <c r="G2" s="105" t="e">
+      <c r="G2" s="104" t="e">
         <f t="shared" ref="G2:G33" si="1">INDEX($B$2:$B$79,MATCH(ROW()-1,$E$2:$E$79,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="H2" s="107" t="e">
+      <c r="H2" s="106" t="e">
         <f>IF(ISBLANK(D2),"",D2/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9451,7 +9534,7 @@
         <f>IF(AND(INDEX($C$2:$C$79,MATCH(ROW()-1,$E$2:$E$79,0))=0,INDEX($D$2:$D$79,MATCH(ROW()-1,$E$2:$E$79,0))=0),"",INDEX($D$2:$D$79,MATCH(ROW()-1,$E$2:$E$79,0)))</f>
         <v>#N/A</v>
       </c>
-      <c r="J2" s="110" t="e" cm="1">
+      <c r="J2" s="109" t="e" cm="1">
         <f t="array" ref="J2">IF(COUNTIF($I$2:I2, I2)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I2, ""))), "")</f>
         <v>#N/A</v>
       </c>
@@ -9510,11 +9593,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G3" s="106" t="e">
+      <c r="G3" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H3" s="108" t="e">
+      <c r="H3" s="107" t="e">
         <f>IF(ISBLANK(D3),"",D3/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9522,7 +9605,7 @@
         <f t="shared" ref="I3:I66" si="2">IF(AND(INDEX($C$2:$C$79,MATCH(ROW()-1,$E$2:$E$79,0))=0,INDEX($D$2:$D$79,MATCH(ROW()-1,$E$2:$E$79,0))=0),"",INDEX($D$2:$D$79,MATCH(ROW()-1,$E$2:$E$79,0)))</f>
         <v>#N/A</v>
       </c>
-      <c r="J3" s="110" t="str" cm="1">
+      <c r="J3" s="109" t="str" cm="1">
         <f t="array" ref="J3">IF(COUNTIF($I$2:I3, I3)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I3, ""))), "")</f>
         <v/>
       </c>
@@ -9581,11 +9664,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G4" s="106" t="e">
+      <c r="G4" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H4" s="108" t="e">
+      <c r="H4" s="107" t="e">
         <f>IF(ISBLANK(D4),"",D4/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9593,7 +9676,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J4" s="110" t="str" cm="1">
+      <c r="J4" s="109" t="str" cm="1">
         <f t="array" ref="J4">IF(COUNTIF($I$2:I4, I4)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I4, ""))), "")</f>
         <v/>
       </c>
@@ -9652,11 +9735,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G5" s="106" t="e">
+      <c r="G5" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H5" s="108" t="e">
+      <c r="H5" s="107" t="e">
         <f>IF(ISBLANK(D5),"",D5/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9664,7 +9747,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J5" s="110" t="str" cm="1">
+      <c r="J5" s="109" t="str" cm="1">
         <f t="array" ref="J5">IF(COUNTIF($I$2:I5, I5)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I5, ""))), "")</f>
         <v/>
       </c>
@@ -9723,11 +9806,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G6" s="106" t="e">
+      <c r="G6" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H6" s="108" t="e">
+      <c r="H6" s="107" t="e">
         <f>IF(ISBLANK(D6),"",D6/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9735,7 +9818,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J6" s="110" t="str" cm="1">
+      <c r="J6" s="109" t="str" cm="1">
         <f t="array" ref="J6">IF(COUNTIF($I$2:I6, I6)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I6, ""))), "")</f>
         <v/>
       </c>
@@ -9794,11 +9877,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G7" s="106" t="e">
+      <c r="G7" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H7" s="108" t="e">
+      <c r="H7" s="107" t="e">
         <f>IF(ISBLANK(D7),"",D7/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9806,7 +9889,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J7" s="110" t="str" cm="1">
+      <c r="J7" s="109" t="str" cm="1">
         <f t="array" ref="J7">IF(COUNTIF($I$2:I7, I7)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I7, ""))), "")</f>
         <v/>
       </c>
@@ -9853,11 +9936,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G8" s="106" t="e">
+      <c r="G8" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H8" s="108" t="e">
+      <c r="H8" s="107" t="e">
         <f>IF(ISBLANK(D8),"",D8/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9865,7 +9948,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J8" s="110" t="str" cm="1">
+      <c r="J8" s="109" t="str" cm="1">
         <f t="array" ref="J8">IF(COUNTIF($I$2:I8, I8)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I8, ""))), "")</f>
         <v/>
       </c>
@@ -9912,11 +9995,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G9" s="106" t="e">
+      <c r="G9" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H9" s="108" t="e">
+      <c r="H9" s="107" t="e">
         <f>IF(ISBLANK(D9),"",D9/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9924,7 +10007,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J9" s="110" t="str" cm="1">
+      <c r="J9" s="109" t="str" cm="1">
         <f t="array" ref="J9">IF(COUNTIF($I$2:I9, I9)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I9, ""))), "")</f>
         <v/>
       </c>
@@ -9971,11 +10054,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G10" s="106" t="e">
+      <c r="G10" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H10" s="108" t="e">
+      <c r="H10" s="107" t="e">
         <f>IF(ISBLANK(D10),"",D10/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9983,7 +10066,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J10" s="110" t="str" cm="1">
+      <c r="J10" s="109" t="str" cm="1">
         <f t="array" ref="J10">IF(COUNTIF($I$2:I10, I10)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I10, ""))), "")</f>
         <v/>
       </c>
@@ -10030,11 +10113,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G11" s="106" t="e">
+      <c r="G11" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H11" s="108" t="e">
+      <c r="H11" s="107" t="e">
         <f>IF(ISBLANK(D11),"",D11/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -10042,7 +10125,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J11" s="110" t="str" cm="1">
+      <c r="J11" s="109" t="str" cm="1">
         <f t="array" ref="J11">IF(COUNTIF($I$2:I11, I11)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I11, ""))), "")</f>
         <v/>
       </c>
@@ -10089,11 +10172,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G12" s="106" t="e">
+      <c r="G12" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H12" s="108" t="e">
+      <c r="H12" s="107" t="e">
         <f>IF(ISBLANK(D12),"",D12/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -10101,7 +10184,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J12" s="110" t="str" cm="1">
+      <c r="J12" s="109" t="str" cm="1">
         <f t="array" ref="J12">IF(COUNTIF($I$2:I12, I12)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I12, ""))), "")</f>
         <v/>
       </c>
@@ -10148,11 +10231,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G13" s="106" t="e">
+      <c r="G13" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H13" s="108" t="e">
+      <c r="H13" s="107" t="e">
         <f>IF(ISBLANK(D13),"",D13/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -10160,7 +10243,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J13" s="110" t="str" cm="1">
+      <c r="J13" s="109" t="str" cm="1">
         <f t="array" ref="J13">IF(COUNTIF($I$2:I13, I13)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I13, ""))), "")</f>
         <v/>
       </c>
@@ -10189,7 +10272,7 @@
       </c>
       <c r="B14" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>13.Yarn severance</v>
+        <v>1.Hue difference</v>
       </c>
       <c r="C14" s="74" t="e">
         <f>IF(ISBLANK(D14),"",D14/'Re-Final'!$W$4)</f>
@@ -10207,11 +10290,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G14" s="106" t="e">
+      <c r="G14" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H14" s="108" t="e">
+      <c r="H14" s="107" t="e">
         <f>IF(ISBLANK(D14),"",D14/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -10219,7 +10302,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J14" s="110" t="str" cm="1">
+      <c r="J14" s="109" t="str" cm="1">
         <f t="array" ref="J14">IF(COUNTIF($I$2:I14, I14)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I14, ""))), "")</f>
         <v/>
       </c>
@@ -10242,13 +10325,13 @@
       <c r="R14" s="81"/>
     </row>
     <row r="15" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A15" s="73" t="str" cm="1">
+      <c r="A15" s="73" cm="1">
         <f t="array" ref="A15">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A14), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B15" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>1.Hue difference</v>
+        <v>2.Unevenness</v>
       </c>
       <c r="C15" s="74" t="e">
         <f>IF(ISBLANK(D15),"",D15/'Re-Final'!$W$4)</f>
@@ -10266,11 +10349,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G15" s="106" t="e">
+      <c r="G15" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H15" s="108" t="e">
+      <c r="H15" s="107" t="e">
         <f>IF(ISBLANK(D15),"",D15/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -10278,7 +10361,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J15" s="110" t="str" cm="1">
+      <c r="J15" s="109" t="str" cm="1">
         <f t="array" ref="J15">IF(COUNTIF($I$2:I15, I15)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I15, ""))), "")</f>
         <v/>
       </c>
@@ -10301,13 +10384,13 @@
       <c r="R15" s="81"/>
     </row>
     <row r="16" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A16" s="73" t="str" cm="1">
+      <c r="A16" s="73" cm="1">
         <f t="array" ref="A16">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A15), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B16" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>2.Unevenness</v>
+        <v>3.Pieces not symmetrical</v>
       </c>
       <c r="C16" s="74" t="e">
         <f>IF(ISBLANK(D16),"",D16/'Re-Final'!$W$4)</f>
@@ -10325,11 +10408,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G16" s="106" t="e">
+      <c r="G16" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H16" s="108" t="e">
+      <c r="H16" s="107" t="e">
         <f>IF(ISBLANK(D16),"",D16/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -10337,7 +10420,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J16" s="110" t="str" cm="1">
+      <c r="J16" s="109" t="str" cm="1">
         <f t="array" ref="J16">IF(COUNTIF($I$2:I16, I16)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I16, ""))), "")</f>
         <v/>
       </c>
@@ -10360,13 +10443,13 @@
       <c r="R16" s="81"/>
     </row>
     <row r="17" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A17" s="73" t="str" cm="1">
+      <c r="A17" s="73" cm="1">
         <f t="array" ref="A17">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A16), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B17" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>3.Pieces not symmetrical</v>
+        <v>4.Deformation (Defect in shape)</v>
       </c>
       <c r="C17" s="74" t="e">
         <f>IF(ISBLANK(D17),"",D17/'Re-Final'!$W$4)</f>
@@ -10384,11 +10467,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G17" s="106" t="e">
+      <c r="G17" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H17" s="108" t="e">
+      <c r="H17" s="107" t="e">
         <f>IF(ISBLANK(D17),"",D17/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -10396,7 +10479,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J17" s="110" t="str" cm="1">
+      <c r="J17" s="109" t="str" cm="1">
         <f t="array" ref="J17">IF(COUNTIF($I$2:I17, I17)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I17, ""))), "")</f>
         <v/>
       </c>
@@ -10419,13 +10502,13 @@
       <c r="R17" s="81"/>
     </row>
     <row r="18" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A18" s="73" t="str" cm="1">
+      <c r="A18" s="73" cm="1">
         <f t="array" ref="A18">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A17), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B18" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>4.Deformation (Defect in shape)</v>
+        <v>5.Tight or loose part of fabric</v>
       </c>
       <c r="C18" s="74" t="e">
         <f>IF(ISBLANK(D18),"",D18/'Re-Final'!$W$4)</f>
@@ -10443,11 +10526,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G18" s="106" t="e">
+      <c r="G18" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H18" s="108" t="e">
+      <c r="H18" s="107" t="e">
         <f>IF(ISBLANK(D18),"",D18/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -10455,7 +10538,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J18" s="110" t="str" cm="1">
+      <c r="J18" s="109" t="str" cm="1">
         <f t="array" ref="J18">IF(COUNTIF($I$2:I18, I18)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I18, ""))), "")</f>
         <v/>
       </c>
@@ -10478,13 +10561,13 @@
       <c r="R18" s="81"/>
     </row>
     <row r="19" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A19" s="73" t="str" cm="1">
+      <c r="A19" s="73" cm="1">
         <f t="array" ref="A19">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A18), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B19" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>5.Tight or loose part of fabric</v>
+        <v>6.Uneven seam</v>
       </c>
       <c r="C19" s="74" t="e">
         <f>IF(ISBLANK(D19),"",D19/'Re-Final'!$W$4)</f>
@@ -10502,11 +10585,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G19" s="106" t="e">
+      <c r="G19" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H19" s="108" t="e">
+      <c r="H19" s="107" t="e">
         <f>IF(ISBLANK(D19),"",D19/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -10514,7 +10597,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J19" s="110" t="str" cm="1">
+      <c r="J19" s="109" t="str" cm="1">
         <f t="array" ref="J19">IF(COUNTIF($I$2:I19, I19)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I19, ""))), "")</f>
         <v/>
       </c>
@@ -10537,13 +10620,13 @@
       <c r="R19" s="81"/>
     </row>
     <row r="20" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A20" s="73" t="str" cm="1">
+      <c r="A20" s="73" cm="1">
         <f t="array" ref="A20">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A19), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B20" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>6.Uneven seam</v>
+        <v>7.Spiralty, wrinkle</v>
       </c>
       <c r="C20" s="74" t="e">
         <f>IF(ISBLANK(D20),"",D20/'Re-Final'!$W$4)</f>
@@ -10561,11 +10644,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G20" s="106" t="e">
+      <c r="G20" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H20" s="108" t="e">
+      <c r="H20" s="107" t="e">
         <f>IF(ISBLANK(D20),"",D20/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -10573,7 +10656,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J20" s="110" t="str" cm="1">
+      <c r="J20" s="109" t="str" cm="1">
         <f t="array" ref="J20">IF(COUNTIF($I$2:I20, I20)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I20, ""))), "")</f>
         <v/>
       </c>
@@ -10596,13 +10679,13 @@
       <c r="R20" s="81"/>
     </row>
     <row r="21" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A21" s="73" t="str" cm="1">
+      <c r="A21" s="73" cm="1">
         <f t="array" ref="A21">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A20), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B21" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>7.Spiralty, wrinkle</v>
+        <v>8.PUCKERING</v>
       </c>
       <c r="C21" s="74" t="e">
         <f>IF(ISBLANK(D21),"",D21/'Re-Final'!$W$4)</f>
@@ -10620,11 +10703,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G21" s="106" t="e">
+      <c r="G21" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H21" s="108" t="e">
+      <c r="H21" s="107" t="e">
         <f>IF(ISBLANK(D21),"",D21/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -10632,7 +10715,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J21" s="110" t="str" cm="1">
+      <c r="J21" s="109" t="str" cm="1">
         <f t="array" ref="J21">IF(COUNTIF($I$2:I21, I21)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I21, ""))), "")</f>
         <v/>
       </c>
@@ -10655,13 +10738,13 @@
       <c r="R21" s="81"/>
     </row>
     <row r="22" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A22" s="73" t="str" cm="1">
+      <c r="A22" s="73" cm="1">
         <f t="array" ref="A22">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A21), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B22" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>8.PUCKERING</v>
+        <v>9.Corrugation</v>
       </c>
       <c r="C22" s="74" t="e">
         <f>IF(ISBLANK(D22),"",D22/'Re-Final'!$W$4)</f>
@@ -10679,11 +10762,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G22" s="106" t="e">
+      <c r="G22" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H22" s="108" t="e">
+      <c r="H22" s="107" t="e">
         <f>IF(ISBLANK(D22),"",D22/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -10691,7 +10774,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J22" s="110" t="str" cm="1">
+      <c r="J22" s="109" t="str" cm="1">
         <f t="array" ref="J22">IF(COUNTIF($I$2:I22, I22)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I22, ""))), "")</f>
         <v/>
       </c>
@@ -10714,13 +10797,13 @@
       <c r="R22" s="81"/>
     </row>
     <row r="23" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A23" s="73" t="str" cm="1">
+      <c r="A23" s="73" cm="1">
         <f t="array" ref="A23">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A22), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B23" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>9.Corrugation</v>
+        <v>10.Thread breakage</v>
       </c>
       <c r="C23" s="74" t="e">
         <f>IF(ISBLANK(D23),"",D23/'Re-Final'!$W$4)</f>
@@ -10738,11 +10821,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G23" s="106" t="e">
+      <c r="G23" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H23" s="108" t="e">
+      <c r="H23" s="107" t="e">
         <f>IF(ISBLANK(D23),"",D23/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -10750,7 +10833,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J23" s="110" t="str" cm="1">
+      <c r="J23" s="109" t="str" cm="1">
         <f t="array" ref="J23">IF(COUNTIF($I$2:I23, I23)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I23, ""))), "")</f>
         <v/>
       </c>
@@ -10773,13 +10856,13 @@
       <c r="R23" s="81"/>
     </row>
     <row r="24" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A24" s="73" t="str" cm="1">
+      <c r="A24" s="73" cm="1">
         <f t="array" ref="A24">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A23), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B24" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>10.Thread breakage</v>
+        <v>11.Lack of elasticity</v>
       </c>
       <c r="C24" s="74" t="e">
         <f>IF(ISBLANK(D24),"",D24/'Re-Final'!$W$4)</f>
@@ -10797,11 +10880,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G24" s="106" t="e">
+      <c r="G24" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H24" s="108" t="e">
+      <c r="H24" s="107" t="e">
         <f>IF(ISBLANK(D24),"",D24/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -10809,7 +10892,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J24" s="110" t="str" cm="1">
+      <c r="J24" s="109" t="str" cm="1">
         <f t="array" ref="J24">IF(COUNTIF($I$2:I24, I24)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I24, ""))), "")</f>
         <v/>
       </c>
@@ -10832,13 +10915,13 @@
       <c r="R24" s="81"/>
     </row>
     <row r="25" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A25" s="73" t="str" cm="1">
+      <c r="A25" s="73" cm="1">
         <f t="array" ref="A25">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A24), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B25" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>11.Lack of elasticity</v>
+        <v>12.Incorrect stitching number</v>
       </c>
       <c r="C25" s="74" t="e">
         <f>IF(ISBLANK(D25),"",D25/'Re-Final'!$W$4)</f>
@@ -10856,11 +10939,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G25" s="106" t="e">
+      <c r="G25" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H25" s="108" t="e">
+      <c r="H25" s="107" t="e">
         <f>IF(ISBLANK(D25),"",D25/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -10868,7 +10951,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J25" s="110" t="str" cm="1">
+      <c r="J25" s="109" t="str" cm="1">
         <f t="array" ref="J25">IF(COUNTIF($I$2:I25, I25)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I25, ""))), "")</f>
         <v/>
       </c>
@@ -10891,13 +10974,13 @@
       <c r="R25" s="81"/>
     </row>
     <row r="26" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A26" s="73" t="str" cm="1">
+      <c r="A26" s="73" cm="1">
         <f t="array" ref="A26">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A25), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B26" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>12.Incorrect stitching number</v>
+        <v>13.Stitches out of seam allowance</v>
       </c>
       <c r="C26" s="74" t="e">
         <f>IF(ISBLANK(D26),"",D26/'Re-Final'!$W$4)</f>
@@ -10915,11 +10998,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G26" s="106" t="e">
+      <c r="G26" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H26" s="108" t="e">
+      <c r="H26" s="107" t="e">
         <f>IF(ISBLANK(D26),"",D26/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -10927,7 +11010,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J26" s="110" t="str" cm="1">
+      <c r="J26" s="109" t="str" cm="1">
         <f t="array" ref="J26">IF(COUNTIF($I$2:I26, I26)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I26, ""))), "")</f>
         <v/>
       </c>
@@ -10950,13 +11033,13 @@
       <c r="R26" s="81"/>
     </row>
     <row r="27" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A27" s="73" t="str" cm="1">
+      <c r="A27" s="73" cm="1">
         <f t="array" ref="A27">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A26), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B27" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>13.Stitches out of seam allowance</v>
+        <v>14.Missing stitch</v>
       </c>
       <c r="C27" s="74" t="e">
         <f>IF(ISBLANK(D27),"",D27/'Re-Final'!$W$4)</f>
@@ -10974,11 +11057,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G27" s="106" t="e">
+      <c r="G27" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H27" s="108" t="e">
+      <c r="H27" s="107" t="e">
         <f>IF(ISBLANK(D27),"",D27/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -10986,7 +11069,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J27" s="110" t="str" cm="1">
+      <c r="J27" s="109" t="str" cm="1">
         <f t="array" ref="J27">IF(COUNTIF($I$2:I27, I27)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I27, ""))), "")</f>
         <v/>
       </c>
@@ -11009,13 +11092,13 @@
       <c r="R27" s="81"/>
     </row>
     <row r="28" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A28" s="73" t="str" cm="1">
+      <c r="A28" s="73" cm="1">
         <f t="array" ref="A28">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A27), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B28" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>14.Missing stitch</v>
+        <v>15.Lack of seam allowance</v>
       </c>
       <c r="C28" s="74" t="e">
         <f>IF(ISBLANK(D28),"",D28/'Re-Final'!$W$4)</f>
@@ -11033,11 +11116,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G28" s="106" t="e">
+      <c r="G28" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H28" s="108" t="e">
+      <c r="H28" s="107" t="e">
         <f>IF(ISBLANK(D28),"",D28/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -11045,7 +11128,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J28" s="110" t="str" cm="1">
+      <c r="J28" s="109" t="str" cm="1">
         <f t="array" ref="J28">IF(COUNTIF($I$2:I28, I28)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I28, ""))), "")</f>
         <v/>
       </c>
@@ -11068,13 +11151,13 @@
       <c r="R28" s="81"/>
     </row>
     <row r="29" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A29" s="73" t="str" cm="1">
+      <c r="A29" s="73" cm="1">
         <f t="array" ref="A29">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A28), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B29" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>15.Lack of seam allowance</v>
+        <v>16.Unexpected tuck</v>
       </c>
       <c r="C29" s="74" t="e">
         <f>IF(ISBLANK(D29),"",D29/'Re-Final'!$W$4)</f>
@@ -11092,11 +11175,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G29" s="106" t="e">
+      <c r="G29" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H29" s="108" t="e">
+      <c r="H29" s="107" t="e">
         <f>IF(ISBLANK(D29),"",D29/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -11104,7 +11187,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J29" s="110" t="str" cm="1">
+      <c r="J29" s="109" t="str" cm="1">
         <f t="array" ref="J29">IF(COUNTIF($I$2:I29, I29)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I29, ""))), "")</f>
         <v/>
       </c>
@@ -11127,13 +11210,13 @@
       <c r="R29" s="81"/>
     </row>
     <row r="30" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A30" s="73" t="str" cm="1">
+      <c r="A30" s="73" cm="1">
         <f t="array" ref="A30">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A29), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B30" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>16.Unexpected tuck</v>
+        <v>17.Unexpected fullness</v>
       </c>
       <c r="C30" s="74" t="e">
         <f>IF(ISBLANK(D30),"",D30/'Re-Final'!$W$4)</f>
@@ -11151,11 +11234,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G30" s="106" t="e">
+      <c r="G30" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H30" s="108" t="e">
+      <c r="H30" s="107" t="e">
         <f>IF(ISBLANK(D30),"",D30/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -11163,7 +11246,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J30" s="110" t="str" cm="1">
+      <c r="J30" s="109" t="str" cm="1">
         <f t="array" ref="J30">IF(COUNTIF($I$2:I30, I30)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I30, ""))), "")</f>
         <v/>
       </c>
@@ -11186,13 +11269,13 @@
       <c r="R30" s="81"/>
     </row>
     <row r="31" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A31" s="73" t="str" cm="1">
+      <c r="A31" s="73" cm="1">
         <f t="array" ref="A31">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A30), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B31" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>17.Unexpected fullness</v>
+        <v>18.Needle mark</v>
       </c>
       <c r="C31" s="74" t="e">
         <f>IF(ISBLANK(D31),"",D31/'Re-Final'!$W$4)</f>
@@ -11210,11 +11293,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G31" s="106" t="e">
+      <c r="G31" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H31" s="108" t="e">
+      <c r="H31" s="107" t="e">
         <f>IF(ISBLANK(D31),"",D31/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -11222,7 +11305,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J31" s="110" t="str" cm="1">
+      <c r="J31" s="109" t="str" cm="1">
         <f t="array" ref="J31">IF(COUNTIF($I$2:I31, I31)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I31, ""))), "")</f>
         <v/>
       </c>
@@ -11245,13 +11328,13 @@
       <c r="R31" s="81"/>
     </row>
     <row r="32" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A32" s="73" t="str" cm="1">
+      <c r="A32" s="73" cm="1">
         <f t="array" ref="A32">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A31), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B32" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>18.Needle mark</v>
+        <v>19.Sewing defects caused by machine</v>
       </c>
       <c r="C32" s="74" t="e">
         <f>IF(ISBLANK(D32),"",D32/'Re-Final'!$W$4)</f>
@@ -11269,11 +11352,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G32" s="106" t="e">
+      <c r="G32" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H32" s="108" t="e">
+      <c r="H32" s="107" t="e">
         <f>IF(ISBLANK(D32),"",D32/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -11281,7 +11364,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J32" s="110" t="str" cm="1">
+      <c r="J32" s="109" t="str" cm="1">
         <f t="array" ref="J32">IF(COUNTIF($I$2:I32, I32)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I32, ""))), "")</f>
         <v/>
       </c>
@@ -11304,13 +11387,13 @@
       <c r="R32" s="81"/>
     </row>
     <row r="33" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A33" s="73" t="str" cm="1">
+      <c r="A33" s="73" cm="1">
         <f t="array" ref="A33">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A32), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B33" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>19.Sewing defects caused by machine</v>
+        <v>20.Incorrect size of lining</v>
       </c>
       <c r="C33" s="74" t="e">
         <f>IF(ISBLANK(D33),"",D33/'Re-Final'!$W$4)</f>
@@ -11328,11 +11411,11 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G33" s="106" t="e">
+      <c r="G33" s="105" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="H33" s="108" t="e">
+      <c r="H33" s="107" t="e">
         <f>IF(ISBLANK(D33),"",D33/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -11340,7 +11423,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J33" s="110" t="str" cm="1">
+      <c r="J33" s="109" t="str" cm="1">
         <f t="array" ref="J33">IF(COUNTIF($I$2:I33, I33)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I33, ""))), "")</f>
         <v/>
       </c>
@@ -11363,13 +11446,13 @@
       <c r="R33" s="81"/>
     </row>
     <row r="34" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A34" s="73" t="str" cm="1">
+      <c r="A34" s="73" cm="1">
         <f t="array" ref="A34">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A33), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B34" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>20.Incorrect size of lining</v>
+        <v>21.Skipped stitch</v>
       </c>
       <c r="C34" s="74" t="e">
         <f>IF(ISBLANK(D34),"",D34/'Re-Final'!$W$4)</f>
@@ -11387,11 +11470,11 @@
         <f t="shared" ref="F34:F65" si="4">INDEX($A:$A, MATCH(G34, $B:$B, 0))</f>
         <v>#N/A</v>
       </c>
-      <c r="G34" s="106" t="e">
+      <c r="G34" s="105" t="e">
         <f t="shared" ref="G34:G65" si="5">INDEX($B$2:$B$79,MATCH(ROW()-1,$E$2:$E$79,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="H34" s="108" t="e">
+      <c r="H34" s="107" t="e">
         <f>IF(ISBLANK(D34),"",D34/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -11399,7 +11482,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J34" s="110" t="str" cm="1">
+      <c r="J34" s="109" t="str" cm="1">
         <f t="array" ref="J34">IF(COUNTIF($I$2:I34, I34)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I34, ""))), "")</f>
         <v/>
       </c>
@@ -11422,13 +11505,13 @@
       <c r="R34" s="81"/>
     </row>
     <row r="35" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A35" s="73" t="str" cm="1">
+      <c r="A35" s="73" cm="1">
         <f t="array" ref="A35">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A34), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B35" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>21.Skipped stitch</v>
+        <v>22.Sewing involving unexpected parts</v>
       </c>
       <c r="C35" s="74" t="e">
         <f>IF(ISBLANK(D35),"",D35/'Re-Final'!$W$4)</f>
@@ -11446,11 +11529,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G35" s="106" t="e">
+      <c r="G35" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H35" s="108" t="e">
+      <c r="H35" s="107" t="e">
         <f>IF(ISBLANK(D35),"",D35/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -11458,7 +11541,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J35" s="110" t="str" cm="1">
+      <c r="J35" s="109" t="str" cm="1">
         <f t="array" ref="J35">IF(COUNTIF($I$2:I35, I35)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I35, ""))), "")</f>
         <v/>
       </c>
@@ -11481,13 +11564,13 @@
       <c r="R35" s="81"/>
     </row>
     <row r="36" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A36" s="73" t="str" cm="1">
+      <c r="A36" s="73" cm="1">
         <f t="array" ref="A36">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A35), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B36" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>22.Sewing involving unexpected parts</v>
+        <v>23.Missing sewing process</v>
       </c>
       <c r="C36" s="74" t="e">
         <f>IF(ISBLANK(D36),"",D36/'Re-Final'!$W$4)</f>
@@ -11505,11 +11588,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G36" s="106" t="e">
+      <c r="G36" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H36" s="108" t="e">
+      <c r="H36" s="107" t="e">
         <f>IF(ISBLANK(D36),"",D36/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -11517,7 +11600,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J36" s="110" t="str" cm="1">
+      <c r="J36" s="109" t="str" cm="1">
         <f t="array" ref="J36">IF(COUNTIF($I$2:I36, I36)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I36, ""))), "")</f>
         <v/>
       </c>
@@ -11540,13 +11623,13 @@
       <c r="R36" s="81"/>
     </row>
     <row r="37" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A37" s="73" t="str" cm="1">
+      <c r="A37" s="73" cm="1">
         <f t="array" ref="A37">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A36), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B37" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>23.Missing sewing process</v>
+        <v>24.Mislocated bar-tack</v>
       </c>
       <c r="C37" s="74" t="e">
         <f>IF(ISBLANK(D37),"",D37/'Re-Final'!$W$4)</f>
@@ -11564,11 +11647,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G37" s="106" t="e">
+      <c r="G37" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H37" s="108" t="e">
+      <c r="H37" s="107" t="e">
         <f>IF(ISBLANK(D37),"",D37/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -11576,7 +11659,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J37" s="110" t="str" cm="1">
+      <c r="J37" s="109" t="str" cm="1">
         <f t="array" ref="J37">IF(COUNTIF($I$2:I37, I37)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I37, ""))), "")</f>
         <v/>
       </c>
@@ -11595,13 +11678,13 @@
       <c r="N37" s="72"/>
     </row>
     <row r="38" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A38" s="73" t="str" cm="1">
+      <c r="A38" s="73" cm="1">
         <f t="array" ref="A38">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A37), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B38" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>24.Mislocated bar-tack</v>
+        <v>25.Incorrect thread tension</v>
       </c>
       <c r="C38" s="74" t="e">
         <f>IF(ISBLANK(D38),"",D38/'Re-Final'!$W$4)</f>
@@ -11619,11 +11702,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G38" s="106" t="e">
+      <c r="G38" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H38" s="108" t="e">
+      <c r="H38" s="107" t="e">
         <f>IF(ISBLANK(D38),"",D38/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -11631,7 +11714,7 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J38" s="110" t="str" cm="1">
+      <c r="J38" s="109" t="str" cm="1">
         <f t="array" ref="J38">IF(COUNTIF($I$2:I38, I38)=1, _xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER($F$2:$F$79, $I$2:$I$79=I38, ""))), "")</f>
         <v/>
       </c>
@@ -11650,13 +11733,13 @@
       <c r="N38" s="72"/>
     </row>
     <row r="39" spans="1:18">
-      <c r="A39" s="73" t="str" cm="1">
+      <c r="A39" s="73" cm="1">
         <f t="array" ref="A39">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A38), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B39" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>25.Incorrect thread tension</v>
+        <v>26.Falling off of a thread</v>
       </c>
       <c r="C39" s="74" t="e">
         <f>IF(ISBLANK(D39),"",D39/'Re-Final'!$W$4)</f>
@@ -11674,11 +11757,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G39" s="106" t="e">
+      <c r="G39" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H39" s="108" t="e">
+      <c r="H39" s="107" t="e">
         <f>IF(ISBLANK(D39),"",D39/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -11688,13 +11771,13 @@
       </c>
     </row>
     <row r="40" spans="1:18">
-      <c r="A40" s="73" t="str" cm="1">
+      <c r="A40" s="73" cm="1">
         <f t="array" ref="A40">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A39), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B40" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>26.Falling off of a thread</v>
+        <v>27.Lack of reverse stitch</v>
       </c>
       <c r="C40" s="74" t="e">
         <f>IF(ISBLANK(D40),"",D40/'Re-Final'!$W$4)</f>
@@ -11712,11 +11795,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G40" s="106" t="e">
+      <c r="G40" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H40" s="108" t="e">
+      <c r="H40" s="107" t="e">
         <f>IF(ISBLANK(D40),"",D40/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -11726,13 +11809,13 @@
       </c>
     </row>
     <row r="41" spans="1:18">
-      <c r="A41" s="73" t="str" cm="1">
+      <c r="A41" s="73" cm="1">
         <f t="array" ref="A41">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A40), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B41" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>27.Lack of reverse stitch</v>
+        <v>28.Incorrect easing</v>
       </c>
       <c r="C41" s="74" t="e">
         <f>IF(ISBLANK(D41),"",D41/'Re-Final'!$W$4)</f>
@@ -11750,11 +11833,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G41" s="106" t="e">
+      <c r="G41" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H41" s="108" t="e">
+      <c r="H41" s="107" t="e">
         <f>IF(ISBLANK(D41),"",D41/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -11764,13 +11847,13 @@
       </c>
     </row>
     <row r="42" spans="1:18">
-      <c r="A42" s="73" t="str" cm="1">
+      <c r="A42" s="73" cm="1">
         <f t="array" ref="A42">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A41), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B42" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>28.Incorrect easing</v>
+        <v>29.Piecing defect</v>
       </c>
       <c r="C42" s="74" t="e">
         <f>IF(ISBLANK(D42),"",D42/'Re-Final'!$W$4)</f>
@@ -11788,11 +11871,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G42" s="106" t="e">
+      <c r="G42" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H42" s="108" t="e">
+      <c r="H42" s="107" t="e">
         <f>IF(ISBLANK(D42),"",D42/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -11802,13 +11885,13 @@
       </c>
     </row>
     <row r="43" spans="1:18">
-      <c r="A43" s="73" t="str" cm="1">
+      <c r="A43" s="73" cm="1">
         <f t="array" ref="A43">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A42), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B43" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>29.Piecing defect</v>
+        <v>30.Incorrect lapped seam</v>
       </c>
       <c r="C43" s="74" t="e">
         <f>IF(ISBLANK(D43),"",D43/'Re-Final'!$W$4)</f>
@@ -11826,11 +11909,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G43" s="106" t="e">
+      <c r="G43" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H43" s="108" t="e">
+      <c r="H43" s="107" t="e">
         <f>IF(ISBLANK(D43),"",D43/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -11840,13 +11923,13 @@
       </c>
     </row>
     <row r="44" spans="1:18">
-      <c r="A44" s="73" t="str" cm="1">
+      <c r="A44" s="73" cm="1">
         <f t="array" ref="A44">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A43), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B44" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>30.Incorrect lapped seam</v>
+        <v>31.Incorrect trimming</v>
       </c>
       <c r="C44" s="74" t="e">
         <f>IF(ISBLANK(D44),"",D44/'Re-Final'!$W$4)</f>
@@ -11864,11 +11947,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G44" s="106" t="e">
+      <c r="G44" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H44" s="108" t="e">
+      <c r="H44" s="107" t="e">
         <f>IF(ISBLANK(D44),"",D44/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -11878,13 +11961,13 @@
       </c>
     </row>
     <row r="45" spans="1:18">
-      <c r="A45" s="73" t="str" cm="1">
+      <c r="A45" s="73" cm="1">
         <f t="array" ref="A45">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A44), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B45" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>31.Incorrect trimming</v>
+        <v>32.Lack of strength</v>
       </c>
       <c r="C45" s="74" t="e">
         <f>IF(ISBLANK(D45),"",D45/'Re-Final'!$W$4)</f>
@@ -11902,11 +11985,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G45" s="106" t="e">
+      <c r="G45" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H45" s="108" t="e">
+      <c r="H45" s="107" t="e">
         <f>IF(ISBLANK(D45),"",D45/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -11916,13 +11999,13 @@
       </c>
     </row>
     <row r="46" spans="1:18">
-      <c r="A46" s="73" t="str" cm="1">
+      <c r="A46" s="73" cm="1">
         <f t="array" ref="A46">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A45), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B46" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>32.Lack of strength</v>
+        <v>33.Incorrect buttonhole sewing</v>
       </c>
       <c r="C46" s="74" t="e">
         <f>IF(ISBLANK(D46),"",D46/'Re-Final'!$W$4)</f>
@@ -11940,11 +12023,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G46" s="106" t="e">
+      <c r="G46" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H46" s="108" t="e">
+      <c r="H46" s="107" t="e">
         <f>IF(ISBLANK(D46),"",D46/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -11954,13 +12037,13 @@
       </c>
     </row>
     <row r="47" spans="1:18">
-      <c r="A47" s="73" t="str" cm="1">
+      <c r="A47" s="73" cm="1">
         <f t="array" ref="A47">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A46), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B47" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>33.Incorrect buttonhole sewing</v>
+        <v>34.Incorrect brand label sewing</v>
       </c>
       <c r="C47" s="74" t="e">
         <f>IF(ISBLANK(D47),"",D47/'Re-Final'!$W$4)</f>
@@ -11978,11 +12061,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G47" s="106" t="e">
+      <c r="G47" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H47" s="108" t="e">
+      <c r="H47" s="107" t="e">
         <f>IF(ISBLANK(D47),"",D47/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -11992,13 +12075,13 @@
       </c>
     </row>
     <row r="48" spans="1:18">
-      <c r="A48" s="73" t="str" cm="1">
+      <c r="A48" s="73" cm="1">
         <f t="array" ref="A48">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A47), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B48" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>34.Incorrect brand label sewing</v>
+        <v>35.Sewing slip</v>
       </c>
       <c r="C48" s="74" t="e">
         <f>IF(ISBLANK(D48),"",D48/'Re-Final'!$W$4)</f>
@@ -12016,11 +12099,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G48" s="106" t="e">
+      <c r="G48" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H48" s="108" t="e">
+      <c r="H48" s="107" t="e">
         <f>IF(ISBLANK(D48),"",D48/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12030,13 +12113,13 @@
       </c>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49" s="73" t="str" cm="1">
+      <c r="A49" s="73" cm="1">
         <f t="array" ref="A49">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A48), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B49" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>35.Sewing slip</v>
+        <v>36.Incorrect position</v>
       </c>
       <c r="C49" s="74" t="e">
         <f>IF(ISBLANK(D49),"",D49/'Re-Final'!$W$4)</f>
@@ -12054,11 +12137,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G49" s="106" t="e">
+      <c r="G49" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H49" s="108" t="e">
+      <c r="H49" s="107" t="e">
         <f>IF(ISBLANK(D49),"",D49/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12068,13 +12151,13 @@
       </c>
     </row>
     <row r="50" spans="1:9">
-      <c r="A50" s="73" t="str" cm="1">
+      <c r="A50" s="73" cm="1">
         <f t="array" ref="A50">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A49), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B50" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>36.Incorrect position</v>
+        <v>37.Incorrect pattern matching</v>
       </c>
       <c r="C50" s="74" t="e">
         <f>IF(ISBLANK(D50),"",D50/'Re-Final'!$W$4)</f>
@@ -12092,11 +12175,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G50" s="106" t="e">
+      <c r="G50" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H50" s="108" t="e">
+      <c r="H50" s="107" t="e">
         <f>IF(ISBLANK(D50),"",D50/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12106,13 +12189,13 @@
       </c>
     </row>
     <row r="51" spans="1:9">
-      <c r="A51" s="73" t="str" cm="1">
+      <c r="A51" s="73" cm="1">
         <f t="array" ref="A51">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A50), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B51" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>37.Incorrect pattern matching</v>
+        <v>38.Peel off glue/delamination</v>
       </c>
       <c r="C51" s="74" t="e">
         <f>IF(ISBLANK(D51),"",D51/'Re-Final'!$W$4)</f>
@@ -12130,11 +12213,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G51" s="106" t="e">
+      <c r="G51" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H51" s="108" t="e">
+      <c r="H51" s="107" t="e">
         <f>IF(ISBLANK(D51),"",D51/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12144,13 +12227,13 @@
       </c>
     </row>
     <row r="52" spans="1:9">
-      <c r="A52" s="73" t="str" cm="1">
+      <c r="A52" s="73" cm="1">
         <f t="array" ref="A52">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A51), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B52" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>38.Peel off glue/delamination</v>
+        <v>39.Visible/see through glue</v>
       </c>
       <c r="C52" s="74" t="e">
         <f>IF(ISBLANK(D52),"",D52/'Re-Final'!$W$4)</f>
@@ -12168,11 +12251,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G52" s="106" t="e">
+      <c r="G52" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H52" s="108" t="e">
+      <c r="H52" s="107" t="e">
         <f>IF(ISBLANK(D52),"",D52/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12182,13 +12265,13 @@
       </c>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="73" t="str" cm="1">
+      <c r="A53" s="73" cm="1">
         <f t="array" ref="A53">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A52), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B53" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>39.Visible/see through glue</v>
+        <v>40.Bonding seam uneven/wavy</v>
       </c>
       <c r="C53" s="74" t="e">
         <f>IF(ISBLANK(D53),"",D53/'Re-Final'!$W$4)</f>
@@ -12206,11 +12289,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G53" s="106" t="e">
+      <c r="G53" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H53" s="108" t="e">
+      <c r="H53" s="107" t="e">
         <f>IF(ISBLANK(D53),"",D53/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12220,13 +12303,13 @@
       </c>
     </row>
     <row r="54" spans="1:9">
-      <c r="A54" s="73" t="str" cm="1">
+      <c r="A54" s="73" cm="1">
         <f t="array" ref="A54">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A53), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B54" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>40.Bonding seam uneven/wavy</v>
+        <v>41.Bonding seam not catch up/bad selvaged</v>
       </c>
       <c r="C54" s="74" t="e">
         <f>IF(ISBLANK(D54),"",D54/'Re-Final'!$W$4)</f>
@@ -12244,11 +12327,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G54" s="106" t="e">
+      <c r="G54" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H54" s="108" t="e">
+      <c r="H54" s="107" t="e">
         <f>IF(ISBLANK(D54),"",D54/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12258,13 +12341,13 @@
       </c>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" s="73" t="str" cm="1">
+      <c r="A55" s="73" cm="1">
         <f t="array" ref="A55">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A54), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B55" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>41.Bonding seam not catch up/bad selvaged</v>
+        <v>42.Stick glue/leaking glue</v>
       </c>
       <c r="C55" s="74" t="e">
         <f>IF(ISBLANK(D55),"",D55/'Re-Final'!$W$4)</f>
@@ -12282,11 +12365,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G55" s="106" t="e">
+      <c r="G55" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H55" s="108" t="e">
+      <c r="H55" s="107" t="e">
         <f>IF(ISBLANK(D55),"",D55/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12296,13 +12379,13 @@
       </c>
     </row>
     <row r="56" spans="1:9">
-      <c r="A56" s="73" t="str" cm="1">
+      <c r="A56" s="73" cm="1">
         <f t="array" ref="A56">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A55), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B56" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>42.Stick glue/leaking glue</v>
+        <v>43.Mold Shape</v>
       </c>
       <c r="C56" s="74" t="e">
         <f>IF(ISBLANK(D56),"",D56/'Re-Final'!$W$4)</f>
@@ -12320,11 +12403,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G56" s="106" t="e">
+      <c r="G56" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H56" s="108" t="e">
+      <c r="H56" s="107" t="e">
         <f>IF(ISBLANK(D56),"",D56/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12334,13 +12417,13 @@
       </c>
     </row>
     <row r="57" spans="1:9">
-      <c r="A57" s="73" t="str" cm="1">
+      <c r="A57" s="73" cm="1">
         <f t="array" ref="A57">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A56), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B57" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>43.Mold Shape</v>
+        <v>44.Poor application glue position</v>
       </c>
       <c r="C57" s="74" t="e">
         <f>IF(ISBLANK(D57),"",D57/'Re-Final'!$W$4)</f>
@@ -12358,11 +12441,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G57" s="106" t="e">
+      <c r="G57" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H57" s="108" t="e">
+      <c r="H57" s="107" t="e">
         <f>IF(ISBLANK(D57),"",D57/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12372,13 +12455,13 @@
       </c>
     </row>
     <row r="58" spans="1:9">
-      <c r="A58" s="73" t="str" cm="1">
+      <c r="A58" s="73" cm="1">
         <f t="array" ref="A58">INDEX('Re-Final'!$Z$1:$CY$1, LOOKUP(ROW(A57), {1,14,58,67,73,76}, {1,14,58,67,73,76}))</f>
-        <v>B : Sewing</v>
+        <v>0</v>
       </c>
       <c r="B58" s="73" t="str">
         <f>INDEX('Re-Final'!$Z$2:$CY$2, ROW()-ROW($B$2)+1)</f>
-        <v>44.Poor application glue position</v>
+        <v>45.Yarn severance</v>
       </c>
       <c r="C58" s="74" t="e">
         <f>IF(ISBLANK(D58),"",D58/'Re-Final'!$W$4)</f>
@@ -12396,11 +12479,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G58" s="106" t="e">
+      <c r="G58" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H58" s="108" t="e">
+      <c r="H58" s="107" t="e">
         <f>IF(ISBLANK(D58),"",D58/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12434,11 +12517,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G59" s="106" t="e">
+      <c r="G59" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H59" s="108" t="e">
+      <c r="H59" s="107" t="e">
         <f>IF(ISBLANK(D59),"",D59/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12472,11 +12555,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G60" s="106" t="e">
+      <c r="G60" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H60" s="108" t="e">
+      <c r="H60" s="107" t="e">
         <f>IF(ISBLANK(D60),"",D60/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12510,11 +12593,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G61" s="106" t="e">
+      <c r="G61" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H61" s="108" t="e">
+      <c r="H61" s="107" t="e">
         <f>IF(ISBLANK(D61),"",D61/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12548,11 +12631,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G62" s="106" t="e">
+      <c r="G62" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H62" s="108" t="e">
+      <c r="H62" s="107" t="e">
         <f>IF(ISBLANK(D62),"",D62/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12586,11 +12669,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G63" s="106" t="e">
+      <c r="G63" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H63" s="108" t="e">
+      <c r="H63" s="107" t="e">
         <f>IF(ISBLANK(D63),"",D63/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12624,11 +12707,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G64" s="106" t="e">
+      <c r="G64" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H64" s="108" t="e">
+      <c r="H64" s="107" t="e">
         <f>IF(ISBLANK(D64),"",D64/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12662,11 +12745,11 @@
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="G65" s="106" t="e">
+      <c r="G65" s="105" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="H65" s="108" t="e">
+      <c r="H65" s="107" t="e">
         <f>IF(ISBLANK(D65),"",D65/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12700,11 +12783,11 @@
         <f t="shared" ref="F66:F79" si="6">INDEX($A:$A, MATCH(G66, $B:$B, 0))</f>
         <v>#N/A</v>
       </c>
-      <c r="G66" s="106" t="e">
+      <c r="G66" s="105" t="e">
         <f t="shared" ref="G66:G79" si="7">INDEX($B$2:$B$79,MATCH(ROW()-1,$E$2:$E$79,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="H66" s="108" t="e">
+      <c r="H66" s="107" t="e">
         <f>IF(ISBLANK(D66),"",D66/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12738,11 +12821,11 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="G67" s="106" t="e">
+      <c r="G67" s="105" t="e">
         <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
-      <c r="H67" s="108" t="e">
+      <c r="H67" s="107" t="e">
         <f>IF(ISBLANK(D67),"",D67/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12776,11 +12859,11 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="G68" s="106" t="e">
+      <c r="G68" s="105" t="e">
         <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
-      <c r="H68" s="108" t="e">
+      <c r="H68" s="107" t="e">
         <f>IF(ISBLANK(D68),"",D68/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12814,11 +12897,11 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="G69" s="106" t="e">
+      <c r="G69" s="105" t="e">
         <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
-      <c r="H69" s="108" t="e">
+      <c r="H69" s="107" t="e">
         <f>IF(ISBLANK(D69),"",D69/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12852,11 +12935,11 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="G70" s="106" t="e">
+      <c r="G70" s="105" t="e">
         <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
-      <c r="H70" s="108" t="e">
+      <c r="H70" s="107" t="e">
         <f>IF(ISBLANK(D70),"",D70/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12890,11 +12973,11 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="G71" s="106" t="e">
+      <c r="G71" s="105" t="e">
         <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
-      <c r="H71" s="108" t="e">
+      <c r="H71" s="107" t="e">
         <f>IF(ISBLANK(D71),"",D71/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12928,11 +13011,11 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="G72" s="106" t="e">
+      <c r="G72" s="105" t="e">
         <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
-      <c r="H72" s="108" t="e">
+      <c r="H72" s="107" t="e">
         <f>IF(ISBLANK(D72),"",D72/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12966,11 +13049,11 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="G73" s="106" t="e">
+      <c r="G73" s="105" t="e">
         <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
-      <c r="H73" s="108" t="e">
+      <c r="H73" s="107" t="e">
         <f>IF(ISBLANK(D73),"",D73/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -13004,11 +13087,11 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="G74" s="106" t="e">
+      <c r="G74" s="105" t="e">
         <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
-      <c r="H74" s="108" t="e">
+      <c r="H74" s="107" t="e">
         <f>IF(ISBLANK(D74),"",D74/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -13042,11 +13125,11 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="G75" s="106" t="e">
+      <c r="G75" s="105" t="e">
         <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
-      <c r="H75" s="108" t="e">
+      <c r="H75" s="107" t="e">
         <f>IF(ISBLANK(D75),"",D75/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -13080,11 +13163,11 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="G76" s="106" t="e">
+      <c r="G76" s="105" t="e">
         <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
-      <c r="H76" s="108" t="e">
+      <c r="H76" s="107" t="e">
         <f>IF(ISBLANK(D76),"",D76/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -13118,11 +13201,11 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="G77" s="106" t="e">
+      <c r="G77" s="105" t="e">
         <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
-      <c r="H77" s="108" t="e">
+      <c r="H77" s="107" t="e">
         <f>IF(ISBLANK(D77),"",D77/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -13156,11 +13239,11 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="G78" s="106" t="e">
+      <c r="G78" s="105" t="e">
         <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
-      <c r="H78" s="108" t="e">
+      <c r="H78" s="107" t="e">
         <f>IF(ISBLANK(D78),"",D78/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -13194,11 +13277,11 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="G79" s="106" t="e">
+      <c r="G79" s="105" t="e">
         <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
-      <c r="H79" s="109" t="e">
+      <c r="H79" s="108" t="e">
         <f>IF(ISBLANK(D79),"",D79/Final!$W$4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -13260,463 +13343,463 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:169" s="1" customFormat="1" ht="28.5" customHeight="1" thickBot="1">
-      <c r="A1" s="131" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="132"/>
-      <c r="L1" s="132"/>
-      <c r="M1" s="132"/>
-      <c r="N1" s="132"/>
-      <c r="O1" s="132"/>
-      <c r="P1" s="132"/>
-      <c r="Q1" s="132"/>
-      <c r="R1" s="132"/>
-      <c r="S1" s="132"/>
-      <c r="T1" s="132"/>
-      <c r="U1" s="132"/>
-      <c r="V1" s="132"/>
-      <c r="W1" s="133"/>
-      <c r="X1" s="121" t="s">
+      <c r="A1" s="148" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
+      <c r="R1" s="149"/>
+      <c r="S1" s="149"/>
+      <c r="T1" s="149"/>
+      <c r="U1" s="149"/>
+      <c r="V1" s="149"/>
+      <c r="W1" s="150"/>
+      <c r="X1" s="167" t="s">
         <v>1</v>
       </c>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="148" t="s">
+      <c r="Y1" s="168"/>
+      <c r="Z1" s="145" t="s">
+        <v>161</v>
+      </c>
+      <c r="AA1" s="146"/>
+      <c r="AB1" s="146"/>
+      <c r="AC1" s="146"/>
+      <c r="AD1" s="146"/>
+      <c r="AE1" s="146"/>
+      <c r="AF1" s="146"/>
+      <c r="AG1" s="146"/>
+      <c r="AH1" s="146"/>
+      <c r="AI1" s="146"/>
+      <c r="AJ1" s="146"/>
+      <c r="AK1" s="147"/>
+      <c r="AL1" s="182" t="s">
         <v>162</v>
       </c>
-      <c r="AA1" s="149"/>
-      <c r="AB1" s="149"/>
-      <c r="AC1" s="149"/>
-      <c r="AD1" s="149"/>
-      <c r="AE1" s="149"/>
-      <c r="AF1" s="149"/>
-      <c r="AG1" s="149"/>
-      <c r="AH1" s="149"/>
-      <c r="AI1" s="149"/>
-      <c r="AJ1" s="149"/>
-      <c r="AK1" s="149"/>
-      <c r="AL1" s="150"/>
-      <c r="AM1" s="148" t="s">
+      <c r="AM1" s="183"/>
+      <c r="AN1" s="183"/>
+      <c r="AO1" s="183"/>
+      <c r="AP1" s="183"/>
+      <c r="AQ1" s="183"/>
+      <c r="AR1" s="183"/>
+      <c r="AS1" s="183"/>
+      <c r="AT1" s="183"/>
+      <c r="AU1" s="183"/>
+      <c r="AV1" s="183"/>
+      <c r="AW1" s="183"/>
+      <c r="AX1" s="183"/>
+      <c r="AY1" s="183"/>
+      <c r="AZ1" s="183"/>
+      <c r="BA1" s="183"/>
+      <c r="BB1" s="183"/>
+      <c r="BC1" s="183"/>
+      <c r="BD1" s="183"/>
+      <c r="BE1" s="183"/>
+      <c r="BF1" s="183"/>
+      <c r="BG1" s="183"/>
+      <c r="BH1" s="183"/>
+      <c r="BI1" s="183"/>
+      <c r="BJ1" s="183"/>
+      <c r="BK1" s="183"/>
+      <c r="BL1" s="183"/>
+      <c r="BM1" s="183"/>
+      <c r="BN1" s="183"/>
+      <c r="BO1" s="183"/>
+      <c r="BP1" s="183"/>
+      <c r="BQ1" s="183"/>
+      <c r="BR1" s="183"/>
+      <c r="BS1" s="183"/>
+      <c r="BT1" s="183"/>
+      <c r="BU1" s="183"/>
+      <c r="BV1" s="183"/>
+      <c r="BW1" s="183"/>
+      <c r="BX1" s="183"/>
+      <c r="BY1" s="183"/>
+      <c r="BZ1" s="183"/>
+      <c r="CA1" s="183"/>
+      <c r="CB1" s="183"/>
+      <c r="CC1" s="183"/>
+      <c r="CD1" s="184"/>
+      <c r="CE1" s="145" t="s">
+        <v>125</v>
+      </c>
+      <c r="CF1" s="146"/>
+      <c r="CG1" s="146"/>
+      <c r="CH1" s="146"/>
+      <c r="CI1" s="146"/>
+      <c r="CJ1" s="146"/>
+      <c r="CK1" s="146"/>
+      <c r="CL1" s="146"/>
+      <c r="CM1" s="147"/>
+      <c r="CN1" s="145" t="s">
+        <v>135</v>
+      </c>
+      <c r="CO1" s="146"/>
+      <c r="CP1" s="146"/>
+      <c r="CQ1" s="146"/>
+      <c r="CR1" s="146"/>
+      <c r="CS1" s="147"/>
+      <c r="CT1" s="145" t="s">
+        <v>142</v>
+      </c>
+      <c r="CU1" s="146"/>
+      <c r="CV1" s="147"/>
+      <c r="CW1" s="145" t="s">
         <v>163</v>
       </c>
-      <c r="AN1" s="149"/>
-      <c r="AO1" s="149"/>
-      <c r="AP1" s="149"/>
-      <c r="AQ1" s="149"/>
-      <c r="AR1" s="149"/>
-      <c r="AS1" s="149"/>
-      <c r="AT1" s="149"/>
-      <c r="AU1" s="149"/>
-      <c r="AV1" s="149"/>
-      <c r="AW1" s="149"/>
-      <c r="AX1" s="149"/>
-      <c r="AY1" s="149"/>
-      <c r="AZ1" s="149"/>
-      <c r="BA1" s="149"/>
-      <c r="BB1" s="149"/>
-      <c r="BC1" s="149"/>
-      <c r="BD1" s="149"/>
-      <c r="BE1" s="149"/>
-      <c r="BF1" s="149"/>
-      <c r="BG1" s="149"/>
-      <c r="BH1" s="149"/>
-      <c r="BI1" s="149"/>
-      <c r="BJ1" s="149"/>
-      <c r="BK1" s="149"/>
-      <c r="BL1" s="149"/>
-      <c r="BM1" s="149"/>
-      <c r="BN1" s="149"/>
-      <c r="BO1" s="149"/>
-      <c r="BP1" s="149"/>
-      <c r="BQ1" s="149"/>
-      <c r="BR1" s="149"/>
-      <c r="BS1" s="149"/>
-      <c r="BT1" s="149"/>
-      <c r="BU1" s="149"/>
-      <c r="BV1" s="149"/>
-      <c r="BW1" s="149"/>
-      <c r="BX1" s="149"/>
-      <c r="BY1" s="149"/>
-      <c r="BZ1" s="149"/>
-      <c r="CA1" s="149"/>
-      <c r="CB1" s="149"/>
-      <c r="CC1" s="149"/>
-      <c r="CD1" s="149"/>
-      <c r="CE1" s="148" t="s">
+      <c r="CX1" s="146"/>
+      <c r="CY1" s="147"/>
+    </row>
+    <row r="2" spans="1:169" s="1" customFormat="1" ht="140.44999999999999" customHeight="1" thickBot="1">
+      <c r="A2" s="163" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="163" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="163" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="163" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="163" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="163" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="163" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="163" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="163" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="163" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="163" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="163" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="163" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="163" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="163" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="165" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q2" s="63" t="s">
+        <v>148</v>
+      </c>
+      <c r="R2" s="163" t="s">
+        <v>147</v>
+      </c>
+      <c r="S2" s="163" t="s">
+        <v>13</v>
+      </c>
+      <c r="T2" s="163" t="s">
+        <v>25</v>
+      </c>
+      <c r="U2" s="163" t="s">
+        <v>14</v>
+      </c>
+      <c r="V2" s="173" t="s">
+        <v>15</v>
+      </c>
+      <c r="W2" s="175" t="s">
+        <v>68</v>
+      </c>
+      <c r="X2" s="169" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y2" s="171" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z2" s="177" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA2" s="178" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB2" s="178" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC2" s="178" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD2" s="178" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE2" s="179" t="s">
+        <v>74</v>
+      </c>
+      <c r="AF2" s="179" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG2" s="179" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH2" s="179" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI2" s="179" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ2" s="179" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK2" s="179" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL2" s="177" t="s">
+        <v>81</v>
+      </c>
+      <c r="AM2" s="178" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN2" s="178" t="s">
+        <v>83</v>
+      </c>
+      <c r="AO2" s="178" t="s">
+        <v>84</v>
+      </c>
+      <c r="AP2" s="178" t="s">
+        <v>85</v>
+      </c>
+      <c r="AQ2" s="178" t="s">
+        <v>86</v>
+      </c>
+      <c r="AR2" s="178" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS2" s="178" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT2" s="178" t="s">
+        <v>89</v>
+      </c>
+      <c r="AU2" s="178" t="s">
+        <v>90</v>
+      </c>
+      <c r="AV2" s="178" t="s">
+        <v>91</v>
+      </c>
+      <c r="AW2" s="178" t="s">
+        <v>92</v>
+      </c>
+      <c r="AX2" s="178" t="s">
+        <v>93</v>
+      </c>
+      <c r="AY2" s="178" t="s">
+        <v>94</v>
+      </c>
+      <c r="AZ2" s="178" t="s">
+        <v>95</v>
+      </c>
+      <c r="BA2" s="178" t="s">
+        <v>96</v>
+      </c>
+      <c r="BB2" s="178" t="s">
+        <v>97</v>
+      </c>
+      <c r="BC2" s="178" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD2" s="178" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE2" s="178" t="s">
+        <v>100</v>
+      </c>
+      <c r="BF2" s="178" t="s">
+        <v>101</v>
+      </c>
+      <c r="BG2" s="178" t="s">
+        <v>102</v>
+      </c>
+      <c r="BH2" s="178" t="s">
+        <v>103</v>
+      </c>
+      <c r="BI2" s="178" t="s">
+        <v>104</v>
+      </c>
+      <c r="BJ2" s="178" t="s">
+        <v>105</v>
+      </c>
+      <c r="BK2" s="178" t="s">
+        <v>106</v>
+      </c>
+      <c r="BL2" s="178" t="s">
+        <v>107</v>
+      </c>
+      <c r="BM2" s="178" t="s">
+        <v>108</v>
+      </c>
+      <c r="BN2" s="178" t="s">
+        <v>109</v>
+      </c>
+      <c r="BO2" s="178" t="s">
+        <v>110</v>
+      </c>
+      <c r="BP2" s="178" t="s">
+        <v>111</v>
+      </c>
+      <c r="BQ2" s="178" t="s">
+        <v>112</v>
+      </c>
+      <c r="BR2" s="178" t="s">
+        <v>113</v>
+      </c>
+      <c r="BS2" s="178" t="s">
+        <v>114</v>
+      </c>
+      <c r="BT2" s="178" t="s">
+        <v>115</v>
+      </c>
+      <c r="BU2" s="178" t="s">
+        <v>116</v>
+      </c>
+      <c r="BV2" s="178" t="s">
+        <v>117</v>
+      </c>
+      <c r="BW2" s="178" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX2" s="178" t="s">
+        <v>119</v>
+      </c>
+      <c r="BY2" s="178" t="s">
+        <v>120</v>
+      </c>
+      <c r="BZ2" s="178" t="s">
+        <v>121</v>
+      </c>
+      <c r="CA2" s="178" t="s">
+        <v>122</v>
+      </c>
+      <c r="CB2" s="178" t="s">
+        <v>123</v>
+      </c>
+      <c r="CC2" s="178" t="s">
+        <v>124</v>
+      </c>
+      <c r="CD2" s="180" t="s">
+        <v>169</v>
+      </c>
+      <c r="CE2" s="181" t="s">
         <v>126</v>
       </c>
-      <c r="CF1" s="149"/>
-      <c r="CG1" s="149"/>
-      <c r="CH1" s="149"/>
-      <c r="CI1" s="149"/>
-      <c r="CJ1" s="149"/>
-      <c r="CK1" s="149"/>
-      <c r="CL1" s="149"/>
-      <c r="CM1" s="150"/>
-      <c r="CN1" s="148" t="s">
+      <c r="CF2" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="CG2" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH2" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="CI2" s="94" t="s">
+        <v>130</v>
+      </c>
+      <c r="CJ2" s="94" t="s">
+        <v>131</v>
+      </c>
+      <c r="CK2" s="94" t="s">
+        <v>132</v>
+      </c>
+      <c r="CL2" s="94" t="s">
+        <v>133</v>
+      </c>
+      <c r="CM2" s="95" t="s">
+        <v>134</v>
+      </c>
+      <c r="CN2" s="96" t="s">
         <v>136</v>
       </c>
-      <c r="CO1" s="149"/>
-      <c r="CP1" s="149"/>
-      <c r="CQ1" s="149"/>
-      <c r="CR1" s="149"/>
-      <c r="CS1" s="150"/>
-      <c r="CT1" s="148" t="s">
+      <c r="CO2" s="97" t="s">
+        <v>137</v>
+      </c>
+      <c r="CP2" s="98" t="s">
+        <v>138</v>
+      </c>
+      <c r="CQ2" s="98" t="s">
+        <v>139</v>
+      </c>
+      <c r="CR2" s="98" t="s">
+        <v>140</v>
+      </c>
+      <c r="CS2" s="99" t="s">
+        <v>141</v>
+      </c>
+      <c r="CT2" s="100" t="s">
         <v>143</v>
       </c>
-      <c r="CU1" s="149"/>
-      <c r="CV1" s="150"/>
-      <c r="CW1" s="148" t="s">
-        <v>164</v>
-      </c>
-      <c r="CX1" s="149"/>
-      <c r="CY1" s="150"/>
-    </row>
-    <row r="2" spans="1:169" s="1" customFormat="1" ht="140.44999999999999" customHeight="1" thickBot="1">
-      <c r="A2" s="119" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="119" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="119" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="119" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="119" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="119" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="119" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="119" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="119" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="119" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" s="119" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" s="119" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="119" t="s">
-        <v>10</v>
-      </c>
-      <c r="N2" s="119" t="s">
-        <v>11</v>
-      </c>
-      <c r="O2" s="119" t="s">
-        <v>12</v>
-      </c>
-      <c r="P2" s="146" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q2" s="63" t="s">
-        <v>149</v>
-      </c>
-      <c r="R2" s="119" t="s">
-        <v>148</v>
-      </c>
-      <c r="S2" s="119" t="s">
-        <v>13</v>
-      </c>
-      <c r="T2" s="119" t="s">
-        <v>25</v>
-      </c>
-      <c r="U2" s="119" t="s">
-        <v>14</v>
-      </c>
-      <c r="V2" s="127" t="s">
-        <v>15</v>
-      </c>
-      <c r="W2" s="129" t="s">
-        <v>68</v>
-      </c>
-      <c r="X2" s="123" t="s">
-        <v>17</v>
-      </c>
-      <c r="Y2" s="125" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z2" s="93" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA2" s="94" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB2" s="94" t="s">
-        <v>71</v>
-      </c>
-      <c r="AC2" s="94" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD2" s="94" t="s">
-        <v>73</v>
-      </c>
-      <c r="AE2" s="95" t="s">
-        <v>74</v>
-      </c>
-      <c r="AF2" s="95" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG2" s="95" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH2" s="95" t="s">
-        <v>77</v>
-      </c>
-      <c r="AI2" s="95" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ2" s="95" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK2" s="95" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL2" s="96" t="s">
-        <v>81</v>
-      </c>
-      <c r="AM2" s="93" t="s">
-        <v>82</v>
-      </c>
-      <c r="AN2" s="94" t="s">
-        <v>83</v>
-      </c>
-      <c r="AO2" s="94" t="s">
-        <v>84</v>
-      </c>
-      <c r="AP2" s="94" t="s">
-        <v>85</v>
-      </c>
-      <c r="AQ2" s="94" t="s">
-        <v>86</v>
-      </c>
-      <c r="AR2" s="94" t="s">
-        <v>87</v>
-      </c>
-      <c r="AS2" s="94" t="s">
-        <v>88</v>
-      </c>
-      <c r="AT2" s="94" t="s">
-        <v>89</v>
-      </c>
-      <c r="AU2" s="94" t="s">
-        <v>90</v>
-      </c>
-      <c r="AV2" s="94" t="s">
-        <v>91</v>
-      </c>
-      <c r="AW2" s="94" t="s">
-        <v>92</v>
-      </c>
-      <c r="AX2" s="94" t="s">
-        <v>93</v>
-      </c>
-      <c r="AY2" s="94" t="s">
-        <v>94</v>
-      </c>
-      <c r="AZ2" s="94" t="s">
-        <v>95</v>
-      </c>
-      <c r="BA2" s="94" t="s">
-        <v>96</v>
-      </c>
-      <c r="BB2" s="94" t="s">
-        <v>97</v>
-      </c>
-      <c r="BC2" s="94" t="s">
-        <v>98</v>
-      </c>
-      <c r="BD2" s="94" t="s">
-        <v>99</v>
-      </c>
-      <c r="BE2" s="94" t="s">
-        <v>100</v>
-      </c>
-      <c r="BF2" s="94" t="s">
-        <v>101</v>
-      </c>
-      <c r="BG2" s="94" t="s">
-        <v>102</v>
-      </c>
-      <c r="BH2" s="94" t="s">
-        <v>103</v>
-      </c>
-      <c r="BI2" s="94" t="s">
-        <v>104</v>
-      </c>
-      <c r="BJ2" s="94" t="s">
-        <v>105</v>
-      </c>
-      <c r="BK2" s="94" t="s">
-        <v>106</v>
-      </c>
-      <c r="BL2" s="94" t="s">
-        <v>107</v>
-      </c>
-      <c r="BM2" s="94" t="s">
-        <v>108</v>
-      </c>
-      <c r="BN2" s="94" t="s">
-        <v>109</v>
-      </c>
-      <c r="BO2" s="94" t="s">
-        <v>110</v>
-      </c>
-      <c r="BP2" s="94" t="s">
-        <v>111</v>
-      </c>
-      <c r="BQ2" s="94" t="s">
-        <v>112</v>
-      </c>
-      <c r="BR2" s="94" t="s">
-        <v>113</v>
-      </c>
-      <c r="BS2" s="94" t="s">
-        <v>114</v>
-      </c>
-      <c r="BT2" s="94" t="s">
-        <v>115</v>
-      </c>
-      <c r="BU2" s="94" t="s">
-        <v>116</v>
-      </c>
-      <c r="BV2" s="94" t="s">
-        <v>117</v>
-      </c>
-      <c r="BW2" s="94" t="s">
-        <v>118</v>
-      </c>
-      <c r="BX2" s="94" t="s">
-        <v>119</v>
-      </c>
-      <c r="BY2" s="94" t="s">
-        <v>120</v>
-      </c>
-      <c r="BZ2" s="94" t="s">
-        <v>121</v>
-      </c>
-      <c r="CA2" s="94" t="s">
-        <v>122</v>
-      </c>
-      <c r="CB2" s="94" t="s">
-        <v>123</v>
-      </c>
-      <c r="CC2" s="94" t="s">
-        <v>124</v>
-      </c>
-      <c r="CD2" s="94" t="s">
-        <v>125</v>
-      </c>
-      <c r="CE2" s="93" t="s">
-        <v>127</v>
-      </c>
-      <c r="CF2" s="94" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG2" s="94" t="s">
-        <v>129</v>
-      </c>
-      <c r="CH2" s="94" t="s">
-        <v>130</v>
-      </c>
-      <c r="CI2" s="94" t="s">
-        <v>131</v>
-      </c>
-      <c r="CJ2" s="94" t="s">
-        <v>132</v>
-      </c>
-      <c r="CK2" s="94" t="s">
-        <v>133</v>
-      </c>
-      <c r="CL2" s="94" t="s">
-        <v>134</v>
-      </c>
-      <c r="CM2" s="96" t="s">
-        <v>135</v>
-      </c>
-      <c r="CN2" s="97" t="s">
-        <v>137</v>
-      </c>
-      <c r="CO2" s="98" t="s">
-        <v>138</v>
-      </c>
-      <c r="CP2" s="99" t="s">
-        <v>139</v>
-      </c>
-      <c r="CQ2" s="99" t="s">
-        <v>140</v>
-      </c>
-      <c r="CR2" s="99" t="s">
-        <v>141</v>
-      </c>
-      <c r="CS2" s="100" t="s">
-        <v>142</v>
-      </c>
-      <c r="CT2" s="101" t="s">
+      <c r="CU2" s="101" t="s">
         <v>144</v>
       </c>
-      <c r="CU2" s="102" t="s">
+      <c r="CV2" s="102" t="s">
         <v>145</v>
       </c>
-      <c r="CV2" s="103" t="s">
-        <v>146</v>
-      </c>
-      <c r="CW2" s="104" t="s">
+      <c r="CW2" s="103" t="s">
         <v>27</v>
       </c>
-      <c r="CX2" s="102" t="s">
+      <c r="CX2" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="CY2" s="103" t="s">
+      <c r="CY2" s="102" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:169" s="1" customFormat="1" ht="21" hidden="1" customHeight="1" thickBot="1">
-      <c r="A3" s="120"/>
-      <c r="B3" s="120"/>
-      <c r="C3" s="120"/>
-      <c r="D3" s="120"/>
-      <c r="E3" s="120"/>
-      <c r="F3" s="120"/>
-      <c r="G3" s="120"/>
-      <c r="H3" s="120"/>
-      <c r="I3" s="120"/>
-      <c r="J3" s="120"/>
-      <c r="K3" s="120"/>
-      <c r="L3" s="120"/>
-      <c r="M3" s="120"/>
-      <c r="N3" s="120"/>
-      <c r="O3" s="120"/>
-      <c r="P3" s="147"/>
+      <c r="A3" s="164"/>
+      <c r="B3" s="164"/>
+      <c r="C3" s="164"/>
+      <c r="D3" s="164"/>
+      <c r="E3" s="164"/>
+      <c r="F3" s="164"/>
+      <c r="G3" s="164"/>
+      <c r="H3" s="164"/>
+      <c r="I3" s="164"/>
+      <c r="J3" s="164"/>
+      <c r="K3" s="164"/>
+      <c r="L3" s="164"/>
+      <c r="M3" s="164"/>
+      <c r="N3" s="164"/>
+      <c r="O3" s="164"/>
+      <c r="P3" s="166"/>
       <c r="Q3" s="62"/>
-      <c r="R3" s="120"/>
-      <c r="S3" s="120"/>
-      <c r="T3" s="120"/>
-      <c r="U3" s="120"/>
-      <c r="V3" s="128"/>
-      <c r="W3" s="130"/>
-      <c r="X3" s="124"/>
-      <c r="Y3" s="126"/>
+      <c r="R3" s="164"/>
+      <c r="S3" s="164"/>
+      <c r="T3" s="164"/>
+      <c r="U3" s="164"/>
+      <c r="V3" s="174"/>
+      <c r="W3" s="176"/>
+      <c r="X3" s="170"/>
+      <c r="Y3" s="172"/>
       <c r="Z3" s="47" t="e">
         <f>Z4/$W$4</f>
         <v>#DIV/0!</v>
@@ -14031,27 +14114,27 @@
       </c>
     </row>
     <row r="4" spans="1:169" s="1" customFormat="1" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A4" s="158" t="s">
+      <c r="A4" s="142" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="159"/>
-      <c r="C4" s="159"/>
-      <c r="D4" s="159"/>
-      <c r="E4" s="159"/>
-      <c r="F4" s="159"/>
-      <c r="G4" s="159"/>
-      <c r="H4" s="159"/>
-      <c r="I4" s="159"/>
-      <c r="J4" s="159"/>
-      <c r="K4" s="159"/>
-      <c r="L4" s="159"/>
-      <c r="M4" s="159"/>
-      <c r="N4" s="159"/>
-      <c r="O4" s="159"/>
-      <c r="P4" s="159"/>
-      <c r="Q4" s="159"/>
-      <c r="R4" s="159"/>
-      <c r="S4" s="160"/>
+      <c r="B4" s="143"/>
+      <c r="C4" s="143"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="143"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="143"/>
+      <c r="H4" s="143"/>
+      <c r="I4" s="143"/>
+      <c r="J4" s="143"/>
+      <c r="K4" s="143"/>
+      <c r="L4" s="143"/>
+      <c r="M4" s="143"/>
+      <c r="N4" s="143"/>
+      <c r="O4" s="143"/>
+      <c r="P4" s="143"/>
+      <c r="Q4" s="143"/>
+      <c r="R4" s="143"/>
+      <c r="S4" s="144"/>
       <c r="T4" s="42">
         <f>SUM(T12:T1000)</f>
         <v>0</v>
@@ -14384,10 +14467,10 @@
       </c>
     </row>
     <row r="5" spans="1:169" ht="44.25" customHeight="1">
-      <c r="J5" s="142" t="s">
+      <c r="J5" s="159" t="s">
         <v>20</v>
       </c>
-      <c r="K5" s="143"/>
+      <c r="K5" s="160"/>
       <c r="L5" s="20" t="s">
         <v>30</v>
       </c>
@@ -14420,10 +14503,10 @@
       <c r="CZ5" s="9"/>
     </row>
     <row r="6" spans="1:169" ht="45.6" customHeight="1">
-      <c r="J6" s="144">
+      <c r="J6" s="161">
         <v>1</v>
       </c>
-      <c r="K6" s="145"/>
+      <c r="K6" s="162"/>
       <c r="L6" s="22" t="e">
         <f>'Helper-1'!O2</f>
         <v>#N/A</v>
@@ -14460,10 +14543,10 @@
       <c r="CZ6" s="9"/>
     </row>
     <row r="7" spans="1:169" ht="45.6" customHeight="1">
-      <c r="J7" s="134">
+      <c r="J7" s="151">
         <v>2</v>
       </c>
-      <c r="K7" s="135"/>
+      <c r="K7" s="152"/>
       <c r="L7" s="25" t="e">
         <f>'Helper-1'!O3</f>
         <v>#N/A</v>
@@ -14500,10 +14583,10 @@
       <c r="CZ7" s="9"/>
     </row>
     <row r="8" spans="1:169" ht="45.6" customHeight="1">
-      <c r="J8" s="136">
+      <c r="J8" s="153">
         <v>3</v>
       </c>
-      <c r="K8" s="137"/>
+      <c r="K8" s="154"/>
       <c r="L8" s="28" t="e">
         <f>'Helper-1'!O4</f>
         <v>#N/A</v>
@@ -14540,10 +14623,10 @@
       <c r="CZ8" s="9"/>
     </row>
     <row r="9" spans="1:169" ht="45.6" customHeight="1">
-      <c r="J9" s="138">
+      <c r="J9" s="155">
         <v>4</v>
       </c>
-      <c r="K9" s="139"/>
+      <c r="K9" s="156"/>
       <c r="L9" s="31" t="e">
         <f>'Helper-1'!O5</f>
         <v>#N/A</v>
@@ -14580,10 +14663,10 @@
       <c r="CZ9" s="9"/>
     </row>
     <row r="10" spans="1:169" ht="45.6" customHeight="1" thickBot="1">
-      <c r="J10" s="140">
+      <c r="J10" s="157">
         <v>5</v>
       </c>
-      <c r="K10" s="141"/>
+      <c r="K10" s="158"/>
       <c r="L10" s="34" t="e">
         <f>'Helper-1'!O6</f>
         <v>#N/A</v>
@@ -24577,28 +24660,9 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="A4:S4"/>
-    <mergeCell ref="CW1:CY1"/>
-    <mergeCell ref="Z1:AL1"/>
-    <mergeCell ref="AM1:CD1"/>
-    <mergeCell ref="CE1:CM1"/>
-    <mergeCell ref="CN1:CS1"/>
-    <mergeCell ref="CT1:CV1"/>
-    <mergeCell ref="A1:W1"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="P2:P3"/>
-    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="Z1:AK1"/>
+    <mergeCell ref="AL1:CD1"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:I3"/>
@@ -24615,7 +24679,26 @@
     <mergeCell ref="T2:T3"/>
     <mergeCell ref="U2:U3"/>
     <mergeCell ref="V2:V3"/>
-    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="CW1:CY1"/>
+    <mergeCell ref="CE1:CM1"/>
+    <mergeCell ref="CN1:CS1"/>
+    <mergeCell ref="CT1:CV1"/>
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="A2:A3"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.3" footer="0.3"/>
@@ -24671,463 +24754,463 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:169" s="1" customFormat="1" ht="28.5" customHeight="1" thickBot="1">
-      <c r="A1" s="131" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="132"/>
-      <c r="L1" s="132"/>
-      <c r="M1" s="132"/>
-      <c r="N1" s="132"/>
-      <c r="O1" s="132"/>
-      <c r="P1" s="132"/>
-      <c r="Q1" s="132"/>
-      <c r="R1" s="132"/>
-      <c r="S1" s="132"/>
-      <c r="T1" s="132"/>
-      <c r="U1" s="132"/>
-      <c r="V1" s="132"/>
-      <c r="W1" s="133"/>
-      <c r="X1" s="121" t="s">
+      <c r="A1" s="148" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
+      <c r="R1" s="149"/>
+      <c r="S1" s="149"/>
+      <c r="T1" s="149"/>
+      <c r="U1" s="149"/>
+      <c r="V1" s="149"/>
+      <c r="W1" s="150"/>
+      <c r="X1" s="167" t="s">
         <v>1</v>
       </c>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="148" t="s">
+      <c r="Y1" s="168"/>
+      <c r="Z1" s="145" t="s">
+        <v>161</v>
+      </c>
+      <c r="AA1" s="146"/>
+      <c r="AB1" s="146"/>
+      <c r="AC1" s="146"/>
+      <c r="AD1" s="146"/>
+      <c r="AE1" s="146"/>
+      <c r="AF1" s="146"/>
+      <c r="AG1" s="146"/>
+      <c r="AH1" s="146"/>
+      <c r="AI1" s="146"/>
+      <c r="AJ1" s="146"/>
+      <c r="AK1" s="147"/>
+      <c r="AL1" s="182" t="s">
         <v>162</v>
       </c>
-      <c r="AA1" s="149"/>
-      <c r="AB1" s="149"/>
-      <c r="AC1" s="149"/>
-      <c r="AD1" s="149"/>
-      <c r="AE1" s="149"/>
-      <c r="AF1" s="149"/>
-      <c r="AG1" s="149"/>
-      <c r="AH1" s="149"/>
-      <c r="AI1" s="149"/>
-      <c r="AJ1" s="149"/>
-      <c r="AK1" s="149"/>
-      <c r="AL1" s="150"/>
-      <c r="AM1" s="148" t="s">
+      <c r="AM1" s="183"/>
+      <c r="AN1" s="183"/>
+      <c r="AO1" s="183"/>
+      <c r="AP1" s="183"/>
+      <c r="AQ1" s="183"/>
+      <c r="AR1" s="183"/>
+      <c r="AS1" s="183"/>
+      <c r="AT1" s="183"/>
+      <c r="AU1" s="183"/>
+      <c r="AV1" s="183"/>
+      <c r="AW1" s="183"/>
+      <c r="AX1" s="183"/>
+      <c r="AY1" s="183"/>
+      <c r="AZ1" s="183"/>
+      <c r="BA1" s="183"/>
+      <c r="BB1" s="183"/>
+      <c r="BC1" s="183"/>
+      <c r="BD1" s="183"/>
+      <c r="BE1" s="183"/>
+      <c r="BF1" s="183"/>
+      <c r="BG1" s="183"/>
+      <c r="BH1" s="183"/>
+      <c r="BI1" s="183"/>
+      <c r="BJ1" s="183"/>
+      <c r="BK1" s="183"/>
+      <c r="BL1" s="183"/>
+      <c r="BM1" s="183"/>
+      <c r="BN1" s="183"/>
+      <c r="BO1" s="183"/>
+      <c r="BP1" s="183"/>
+      <c r="BQ1" s="183"/>
+      <c r="BR1" s="183"/>
+      <c r="BS1" s="183"/>
+      <c r="BT1" s="183"/>
+      <c r="BU1" s="183"/>
+      <c r="BV1" s="183"/>
+      <c r="BW1" s="183"/>
+      <c r="BX1" s="183"/>
+      <c r="BY1" s="183"/>
+      <c r="BZ1" s="183"/>
+      <c r="CA1" s="183"/>
+      <c r="CB1" s="183"/>
+      <c r="CC1" s="183"/>
+      <c r="CD1" s="184"/>
+      <c r="CE1" s="145" t="s">
+        <v>125</v>
+      </c>
+      <c r="CF1" s="146"/>
+      <c r="CG1" s="146"/>
+      <c r="CH1" s="146"/>
+      <c r="CI1" s="146"/>
+      <c r="CJ1" s="146"/>
+      <c r="CK1" s="146"/>
+      <c r="CL1" s="146"/>
+      <c r="CM1" s="147"/>
+      <c r="CN1" s="145" t="s">
+        <v>135</v>
+      </c>
+      <c r="CO1" s="146"/>
+      <c r="CP1" s="146"/>
+      <c r="CQ1" s="146"/>
+      <c r="CR1" s="146"/>
+      <c r="CS1" s="147"/>
+      <c r="CT1" s="145" t="s">
+        <v>142</v>
+      </c>
+      <c r="CU1" s="146"/>
+      <c r="CV1" s="147"/>
+      <c r="CW1" s="145" t="s">
         <v>163</v>
       </c>
-      <c r="AN1" s="149"/>
-      <c r="AO1" s="149"/>
-      <c r="AP1" s="149"/>
-      <c r="AQ1" s="149"/>
-      <c r="AR1" s="149"/>
-      <c r="AS1" s="149"/>
-      <c r="AT1" s="149"/>
-      <c r="AU1" s="149"/>
-      <c r="AV1" s="149"/>
-      <c r="AW1" s="149"/>
-      <c r="AX1" s="149"/>
-      <c r="AY1" s="149"/>
-      <c r="AZ1" s="149"/>
-      <c r="BA1" s="149"/>
-      <c r="BB1" s="149"/>
-      <c r="BC1" s="149"/>
-      <c r="BD1" s="149"/>
-      <c r="BE1" s="149"/>
-      <c r="BF1" s="149"/>
-      <c r="BG1" s="149"/>
-      <c r="BH1" s="149"/>
-      <c r="BI1" s="149"/>
-      <c r="BJ1" s="149"/>
-      <c r="BK1" s="149"/>
-      <c r="BL1" s="149"/>
-      <c r="BM1" s="149"/>
-      <c r="BN1" s="149"/>
-      <c r="BO1" s="149"/>
-      <c r="BP1" s="149"/>
-      <c r="BQ1" s="149"/>
-      <c r="BR1" s="149"/>
-      <c r="BS1" s="149"/>
-      <c r="BT1" s="149"/>
-      <c r="BU1" s="149"/>
-      <c r="BV1" s="149"/>
-      <c r="BW1" s="149"/>
-      <c r="BX1" s="149"/>
-      <c r="BY1" s="149"/>
-      <c r="BZ1" s="149"/>
-      <c r="CA1" s="149"/>
-      <c r="CB1" s="149"/>
-      <c r="CC1" s="149"/>
-      <c r="CD1" s="149"/>
-      <c r="CE1" s="148" t="s">
+      <c r="CX1" s="146"/>
+      <c r="CY1" s="147"/>
+    </row>
+    <row r="2" spans="1:169" s="1" customFormat="1" ht="140.44999999999999" customHeight="1" thickBot="1">
+      <c r="A2" s="163" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="163" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="163" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="163" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="163" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="163" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="163" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="163" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="163" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="163" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="163" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="163" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="163" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="163" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="163" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="165" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q2" s="63" t="s">
+        <v>148</v>
+      </c>
+      <c r="R2" s="163" t="s">
+        <v>147</v>
+      </c>
+      <c r="S2" s="163" t="s">
+        <v>13</v>
+      </c>
+      <c r="T2" s="163" t="s">
+        <v>25</v>
+      </c>
+      <c r="U2" s="163" t="s">
+        <v>14</v>
+      </c>
+      <c r="V2" s="173" t="s">
+        <v>15</v>
+      </c>
+      <c r="W2" s="175" t="s">
+        <v>68</v>
+      </c>
+      <c r="X2" s="169" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y2" s="171" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z2" s="177" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA2" s="178" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB2" s="178" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC2" s="178" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD2" s="178" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE2" s="179" t="s">
+        <v>74</v>
+      </c>
+      <c r="AF2" s="179" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG2" s="179" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH2" s="179" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI2" s="179" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ2" s="179" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK2" s="179" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL2" s="177" t="s">
+        <v>81</v>
+      </c>
+      <c r="AM2" s="178" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN2" s="178" t="s">
+        <v>83</v>
+      </c>
+      <c r="AO2" s="178" t="s">
+        <v>84</v>
+      </c>
+      <c r="AP2" s="178" t="s">
+        <v>85</v>
+      </c>
+      <c r="AQ2" s="178" t="s">
+        <v>86</v>
+      </c>
+      <c r="AR2" s="178" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS2" s="178" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT2" s="178" t="s">
+        <v>89</v>
+      </c>
+      <c r="AU2" s="178" t="s">
+        <v>90</v>
+      </c>
+      <c r="AV2" s="178" t="s">
+        <v>91</v>
+      </c>
+      <c r="AW2" s="178" t="s">
+        <v>92</v>
+      </c>
+      <c r="AX2" s="178" t="s">
+        <v>93</v>
+      </c>
+      <c r="AY2" s="178" t="s">
+        <v>94</v>
+      </c>
+      <c r="AZ2" s="178" t="s">
+        <v>95</v>
+      </c>
+      <c r="BA2" s="178" t="s">
+        <v>96</v>
+      </c>
+      <c r="BB2" s="178" t="s">
+        <v>97</v>
+      </c>
+      <c r="BC2" s="178" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD2" s="178" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE2" s="178" t="s">
+        <v>100</v>
+      </c>
+      <c r="BF2" s="178" t="s">
+        <v>101</v>
+      </c>
+      <c r="BG2" s="178" t="s">
+        <v>102</v>
+      </c>
+      <c r="BH2" s="178" t="s">
+        <v>103</v>
+      </c>
+      <c r="BI2" s="178" t="s">
+        <v>104</v>
+      </c>
+      <c r="BJ2" s="178" t="s">
+        <v>105</v>
+      </c>
+      <c r="BK2" s="178" t="s">
+        <v>106</v>
+      </c>
+      <c r="BL2" s="178" t="s">
+        <v>107</v>
+      </c>
+      <c r="BM2" s="178" t="s">
+        <v>108</v>
+      </c>
+      <c r="BN2" s="178" t="s">
+        <v>109</v>
+      </c>
+      <c r="BO2" s="178" t="s">
+        <v>110</v>
+      </c>
+      <c r="BP2" s="178" t="s">
+        <v>111</v>
+      </c>
+      <c r="BQ2" s="178" t="s">
+        <v>112</v>
+      </c>
+      <c r="BR2" s="178" t="s">
+        <v>113</v>
+      </c>
+      <c r="BS2" s="178" t="s">
+        <v>114</v>
+      </c>
+      <c r="BT2" s="178" t="s">
+        <v>115</v>
+      </c>
+      <c r="BU2" s="178" t="s">
+        <v>116</v>
+      </c>
+      <c r="BV2" s="178" t="s">
+        <v>117</v>
+      </c>
+      <c r="BW2" s="178" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX2" s="178" t="s">
+        <v>119</v>
+      </c>
+      <c r="BY2" s="178" t="s">
+        <v>120</v>
+      </c>
+      <c r="BZ2" s="178" t="s">
+        <v>121</v>
+      </c>
+      <c r="CA2" s="178" t="s">
+        <v>122</v>
+      </c>
+      <c r="CB2" s="178" t="s">
+        <v>123</v>
+      </c>
+      <c r="CC2" s="178" t="s">
+        <v>124</v>
+      </c>
+      <c r="CD2" s="180" t="s">
+        <v>169</v>
+      </c>
+      <c r="CE2" s="93" t="s">
         <v>126</v>
       </c>
-      <c r="CF1" s="149"/>
-      <c r="CG1" s="149"/>
-      <c r="CH1" s="149"/>
-      <c r="CI1" s="149"/>
-      <c r="CJ1" s="149"/>
-      <c r="CK1" s="149"/>
-      <c r="CL1" s="149"/>
-      <c r="CM1" s="150"/>
-      <c r="CN1" s="148" t="s">
+      <c r="CF2" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="CG2" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH2" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="CI2" s="94" t="s">
+        <v>130</v>
+      </c>
+      <c r="CJ2" s="94" t="s">
+        <v>131</v>
+      </c>
+      <c r="CK2" s="94" t="s">
+        <v>132</v>
+      </c>
+      <c r="CL2" s="94" t="s">
+        <v>133</v>
+      </c>
+      <c r="CM2" s="95" t="s">
+        <v>134</v>
+      </c>
+      <c r="CN2" s="96" t="s">
         <v>136</v>
       </c>
-      <c r="CO1" s="149"/>
-      <c r="CP1" s="149"/>
-      <c r="CQ1" s="149"/>
-      <c r="CR1" s="149"/>
-      <c r="CS1" s="150"/>
-      <c r="CT1" s="148" t="s">
+      <c r="CO2" s="97" t="s">
+        <v>137</v>
+      </c>
+      <c r="CP2" s="98" t="s">
+        <v>138</v>
+      </c>
+      <c r="CQ2" s="98" t="s">
+        <v>139</v>
+      </c>
+      <c r="CR2" s="98" t="s">
+        <v>140</v>
+      </c>
+      <c r="CS2" s="99" t="s">
+        <v>141</v>
+      </c>
+      <c r="CT2" s="100" t="s">
         <v>143</v>
       </c>
-      <c r="CU1" s="149"/>
-      <c r="CV1" s="150"/>
-      <c r="CW1" s="148" t="s">
-        <v>164</v>
-      </c>
-      <c r="CX1" s="149"/>
-      <c r="CY1" s="150"/>
-    </row>
-    <row r="2" spans="1:169" s="1" customFormat="1" ht="140.44999999999999" customHeight="1" thickBot="1">
-      <c r="A2" s="119" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="119" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="119" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="119" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="119" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="119" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="119" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="119" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="119" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="119" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" s="119" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" s="119" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="119" t="s">
-        <v>10</v>
-      </c>
-      <c r="N2" s="119" t="s">
-        <v>11</v>
-      </c>
-      <c r="O2" s="119" t="s">
-        <v>12</v>
-      </c>
-      <c r="P2" s="146" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q2" s="63" t="s">
-        <v>149</v>
-      </c>
-      <c r="R2" s="119" t="s">
-        <v>148</v>
-      </c>
-      <c r="S2" s="119" t="s">
-        <v>13</v>
-      </c>
-      <c r="T2" s="119" t="s">
-        <v>25</v>
-      </c>
-      <c r="U2" s="119" t="s">
-        <v>14</v>
-      </c>
-      <c r="V2" s="127" t="s">
-        <v>15</v>
-      </c>
-      <c r="W2" s="129" t="s">
-        <v>68</v>
-      </c>
-      <c r="X2" s="123" t="s">
-        <v>17</v>
-      </c>
-      <c r="Y2" s="125" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z2" s="93" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA2" s="94" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB2" s="94" t="s">
-        <v>71</v>
-      </c>
-      <c r="AC2" s="94" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD2" s="94" t="s">
-        <v>73</v>
-      </c>
-      <c r="AE2" s="95" t="s">
-        <v>74</v>
-      </c>
-      <c r="AF2" s="95" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG2" s="95" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH2" s="95" t="s">
-        <v>77</v>
-      </c>
-      <c r="AI2" s="95" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ2" s="95" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK2" s="95" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL2" s="96" t="s">
-        <v>81</v>
-      </c>
-      <c r="AM2" s="93" t="s">
-        <v>82</v>
-      </c>
-      <c r="AN2" s="94" t="s">
-        <v>83</v>
-      </c>
-      <c r="AO2" s="94" t="s">
-        <v>84</v>
-      </c>
-      <c r="AP2" s="94" t="s">
-        <v>85</v>
-      </c>
-      <c r="AQ2" s="94" t="s">
-        <v>86</v>
-      </c>
-      <c r="AR2" s="94" t="s">
-        <v>87</v>
-      </c>
-      <c r="AS2" s="94" t="s">
-        <v>88</v>
-      </c>
-      <c r="AT2" s="94" t="s">
-        <v>89</v>
-      </c>
-      <c r="AU2" s="94" t="s">
-        <v>90</v>
-      </c>
-      <c r="AV2" s="94" t="s">
-        <v>91</v>
-      </c>
-      <c r="AW2" s="94" t="s">
-        <v>92</v>
-      </c>
-      <c r="AX2" s="94" t="s">
-        <v>93</v>
-      </c>
-      <c r="AY2" s="94" t="s">
-        <v>94</v>
-      </c>
-      <c r="AZ2" s="94" t="s">
-        <v>95</v>
-      </c>
-      <c r="BA2" s="94" t="s">
-        <v>96</v>
-      </c>
-      <c r="BB2" s="94" t="s">
-        <v>97</v>
-      </c>
-      <c r="BC2" s="94" t="s">
-        <v>98</v>
-      </c>
-      <c r="BD2" s="94" t="s">
-        <v>99</v>
-      </c>
-      <c r="BE2" s="94" t="s">
-        <v>100</v>
-      </c>
-      <c r="BF2" s="94" t="s">
-        <v>101</v>
-      </c>
-      <c r="BG2" s="94" t="s">
-        <v>102</v>
-      </c>
-      <c r="BH2" s="94" t="s">
-        <v>103</v>
-      </c>
-      <c r="BI2" s="94" t="s">
-        <v>104</v>
-      </c>
-      <c r="BJ2" s="94" t="s">
-        <v>105</v>
-      </c>
-      <c r="BK2" s="94" t="s">
-        <v>106</v>
-      </c>
-      <c r="BL2" s="94" t="s">
-        <v>107</v>
-      </c>
-      <c r="BM2" s="94" t="s">
-        <v>108</v>
-      </c>
-      <c r="BN2" s="94" t="s">
-        <v>109</v>
-      </c>
-      <c r="BO2" s="94" t="s">
-        <v>110</v>
-      </c>
-      <c r="BP2" s="94" t="s">
-        <v>111</v>
-      </c>
-      <c r="BQ2" s="94" t="s">
-        <v>112</v>
-      </c>
-      <c r="BR2" s="94" t="s">
-        <v>113</v>
-      </c>
-      <c r="BS2" s="94" t="s">
-        <v>114</v>
-      </c>
-      <c r="BT2" s="94" t="s">
-        <v>115</v>
-      </c>
-      <c r="BU2" s="94" t="s">
-        <v>116</v>
-      </c>
-      <c r="BV2" s="94" t="s">
-        <v>117</v>
-      </c>
-      <c r="BW2" s="94" t="s">
-        <v>118</v>
-      </c>
-      <c r="BX2" s="94" t="s">
-        <v>119</v>
-      </c>
-      <c r="BY2" s="94" t="s">
-        <v>120</v>
-      </c>
-      <c r="BZ2" s="94" t="s">
-        <v>121</v>
-      </c>
-      <c r="CA2" s="94" t="s">
-        <v>122</v>
-      </c>
-      <c r="CB2" s="94" t="s">
-        <v>123</v>
-      </c>
-      <c r="CC2" s="94" t="s">
-        <v>124</v>
-      </c>
-      <c r="CD2" s="94" t="s">
-        <v>125</v>
-      </c>
-      <c r="CE2" s="93" t="s">
-        <v>127</v>
-      </c>
-      <c r="CF2" s="94" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG2" s="94" t="s">
-        <v>129</v>
-      </c>
-      <c r="CH2" s="94" t="s">
-        <v>130</v>
-      </c>
-      <c r="CI2" s="94" t="s">
-        <v>131</v>
-      </c>
-      <c r="CJ2" s="94" t="s">
-        <v>132</v>
-      </c>
-      <c r="CK2" s="94" t="s">
-        <v>133</v>
-      </c>
-      <c r="CL2" s="94" t="s">
-        <v>134</v>
-      </c>
-      <c r="CM2" s="96" t="s">
-        <v>135</v>
-      </c>
-      <c r="CN2" s="97" t="s">
-        <v>137</v>
-      </c>
-      <c r="CO2" s="98" t="s">
-        <v>138</v>
-      </c>
-      <c r="CP2" s="99" t="s">
-        <v>139</v>
-      </c>
-      <c r="CQ2" s="99" t="s">
-        <v>140</v>
-      </c>
-      <c r="CR2" s="99" t="s">
-        <v>141</v>
-      </c>
-      <c r="CS2" s="100" t="s">
-        <v>142</v>
-      </c>
-      <c r="CT2" s="101" t="s">
+      <c r="CU2" s="101" t="s">
         <v>144</v>
       </c>
-      <c r="CU2" s="102" t="s">
+      <c r="CV2" s="102" t="s">
         <v>145</v>
       </c>
-      <c r="CV2" s="103" t="s">
-        <v>146</v>
-      </c>
-      <c r="CW2" s="104" t="s">
+      <c r="CW2" s="103" t="s">
         <v>27</v>
       </c>
-      <c r="CX2" s="102" t="s">
+      <c r="CX2" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="CY2" s="103" t="s">
+      <c r="CY2" s="102" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:169" s="1" customFormat="1" ht="21" hidden="1" customHeight="1" thickBot="1">
-      <c r="A3" s="120"/>
-      <c r="B3" s="120"/>
-      <c r="C3" s="120"/>
-      <c r="D3" s="120"/>
-      <c r="E3" s="120"/>
-      <c r="F3" s="120"/>
-      <c r="G3" s="120"/>
-      <c r="H3" s="120"/>
-      <c r="I3" s="120"/>
-      <c r="J3" s="120"/>
-      <c r="K3" s="120"/>
-      <c r="L3" s="120"/>
-      <c r="M3" s="120"/>
-      <c r="N3" s="120"/>
-      <c r="O3" s="120"/>
-      <c r="P3" s="147"/>
+      <c r="A3" s="164"/>
+      <c r="B3" s="164"/>
+      <c r="C3" s="164"/>
+      <c r="D3" s="164"/>
+      <c r="E3" s="164"/>
+      <c r="F3" s="164"/>
+      <c r="G3" s="164"/>
+      <c r="H3" s="164"/>
+      <c r="I3" s="164"/>
+      <c r="J3" s="164"/>
+      <c r="K3" s="164"/>
+      <c r="L3" s="164"/>
+      <c r="M3" s="164"/>
+      <c r="N3" s="164"/>
+      <c r="O3" s="164"/>
+      <c r="P3" s="166"/>
       <c r="Q3" s="62"/>
-      <c r="R3" s="120"/>
-      <c r="S3" s="120"/>
-      <c r="T3" s="120"/>
-      <c r="U3" s="120"/>
-      <c r="V3" s="128"/>
-      <c r="W3" s="130"/>
-      <c r="X3" s="124"/>
-      <c r="Y3" s="126"/>
+      <c r="R3" s="164"/>
+      <c r="S3" s="164"/>
+      <c r="T3" s="164"/>
+      <c r="U3" s="164"/>
+      <c r="V3" s="174"/>
+      <c r="W3" s="176"/>
+      <c r="X3" s="170"/>
+      <c r="Y3" s="172"/>
       <c r="Z3" s="47" t="e">
         <f>Z4/$W$4</f>
         <v>#DIV/0!</v>
@@ -25442,27 +25525,27 @@
       </c>
     </row>
     <row r="4" spans="1:169" s="1" customFormat="1" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A4" s="158" t="s">
+      <c r="A4" s="142" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="159"/>
-      <c r="C4" s="159"/>
-      <c r="D4" s="159"/>
-      <c r="E4" s="159"/>
-      <c r="F4" s="159"/>
-      <c r="G4" s="159"/>
-      <c r="H4" s="159"/>
-      <c r="I4" s="159"/>
-      <c r="J4" s="159"/>
-      <c r="K4" s="159"/>
-      <c r="L4" s="159"/>
-      <c r="M4" s="159"/>
-      <c r="N4" s="159"/>
-      <c r="O4" s="159"/>
-      <c r="P4" s="159"/>
-      <c r="Q4" s="159"/>
-      <c r="R4" s="159"/>
-      <c r="S4" s="160"/>
+      <c r="B4" s="143"/>
+      <c r="C4" s="143"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="143"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="143"/>
+      <c r="H4" s="143"/>
+      <c r="I4" s="143"/>
+      <c r="J4" s="143"/>
+      <c r="K4" s="143"/>
+      <c r="L4" s="143"/>
+      <c r="M4" s="143"/>
+      <c r="N4" s="143"/>
+      <c r="O4" s="143"/>
+      <c r="P4" s="143"/>
+      <c r="Q4" s="143"/>
+      <c r="R4" s="143"/>
+      <c r="S4" s="144"/>
       <c r="T4" s="42">
         <f>SUM(T11:T1000)</f>
         <v>0</v>
@@ -25795,10 +25878,10 @@
       </c>
     </row>
     <row r="5" spans="1:169" ht="44.25" customHeight="1">
-      <c r="J5" s="142" t="s">
+      <c r="J5" s="159" t="s">
         <v>20</v>
       </c>
-      <c r="K5" s="143"/>
+      <c r="K5" s="160"/>
       <c r="L5" s="20" t="s">
         <v>30</v>
       </c>
@@ -25823,10 +25906,10 @@
       <c r="CZ5" s="9"/>
     </row>
     <row r="6" spans="1:169" ht="45.6" customHeight="1">
-      <c r="J6" s="144">
+      <c r="J6" s="161">
         <v>1</v>
       </c>
-      <c r="K6" s="145"/>
+      <c r="K6" s="162"/>
       <c r="L6" s="22" t="e">
         <f>'Helper-2'!O2</f>
         <v>#N/A</v>
@@ -25855,10 +25938,10 @@
       <c r="CZ6" s="9"/>
     </row>
     <row r="7" spans="1:169" ht="45.6" customHeight="1">
-      <c r="J7" s="134">
+      <c r="J7" s="151">
         <v>2</v>
       </c>
-      <c r="K7" s="135"/>
+      <c r="K7" s="152"/>
       <c r="L7" s="25" t="e">
         <f>'Helper-2'!O3</f>
         <v>#N/A</v>
@@ -25887,10 +25970,10 @@
       <c r="CZ7" s="9"/>
     </row>
     <row r="8" spans="1:169" ht="45.6" customHeight="1">
-      <c r="J8" s="136">
+      <c r="J8" s="153">
         <v>3</v>
       </c>
-      <c r="K8" s="137"/>
+      <c r="K8" s="154"/>
       <c r="L8" s="28" t="e">
         <f>'Helper-2'!O4</f>
         <v>#N/A</v>
@@ -25919,10 +26002,10 @@
       <c r="CZ8" s="9"/>
     </row>
     <row r="9" spans="1:169" ht="45.6" customHeight="1">
-      <c r="J9" s="138">
+      <c r="J9" s="155">
         <v>4</v>
       </c>
-      <c r="K9" s="139"/>
+      <c r="K9" s="156"/>
       <c r="L9" s="31" t="e">
         <f>'Helper-2'!O5</f>
         <v>#N/A</v>
@@ -25951,10 +26034,10 @@
       <c r="CZ9" s="9"/>
     </row>
     <row r="10" spans="1:169" ht="45.6" customHeight="1" thickBot="1">
-      <c r="J10" s="140">
+      <c r="J10" s="157">
         <v>5</v>
       </c>
-      <c r="K10" s="141"/>
+      <c r="K10" s="158"/>
       <c r="L10" s="34" t="e">
         <f>'Helper-2'!O6</f>
         <v>#N/A</v>
@@ -33179,13 +33262,15 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="A4:S4"/>
-    <mergeCell ref="CW1:CY1"/>
-    <mergeCell ref="Z1:AL1"/>
-    <mergeCell ref="AM1:CD1"/>
-    <mergeCell ref="CE1:CM1"/>
-    <mergeCell ref="CN1:CS1"/>
-    <mergeCell ref="CT1:CV1"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="Z1:AK1"/>
+    <mergeCell ref="AL1:CD1"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
     <mergeCell ref="J8:K8"/>
     <mergeCell ref="J9:K9"/>
     <mergeCell ref="J10:K10"/>
@@ -33202,6 +33287,11 @@
     <mergeCell ref="J7:K7"/>
     <mergeCell ref="O2:O3"/>
     <mergeCell ref="R2:R3"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="CW1:CY1"/>
+    <mergeCell ref="CE1:CM1"/>
+    <mergeCell ref="CN1:CS1"/>
+    <mergeCell ref="CT1:CV1"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="H2:H3"/>
@@ -33211,13 +33301,6 @@
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="Y2:Y3"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.3" footer="0.3"/>
@@ -33259,423 +33342,423 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:121" s="1" customFormat="1" ht="24" customHeight="1" thickBot="1">
-      <c r="A1" s="166" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="167"/>
-      <c r="C1" s="167"/>
-      <c r="D1" s="167"/>
-      <c r="E1" s="167"/>
-      <c r="F1" s="167"/>
-      <c r="G1" s="167"/>
-      <c r="H1" s="167"/>
-      <c r="I1" s="167"/>
-      <c r="J1" s="167"/>
-      <c r="K1" s="167"/>
-      <c r="L1" s="167"/>
-      <c r="M1" s="167"/>
-      <c r="N1" s="167"/>
-      <c r="O1" s="167"/>
-      <c r="P1" s="167"/>
-      <c r="Q1" s="167"/>
-      <c r="R1" s="168"/>
-      <c r="S1" s="169" t="s">
+      <c r="A1" s="127" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="128"/>
+      <c r="M1" s="128"/>
+      <c r="N1" s="128"/>
+      <c r="O1" s="128"/>
+      <c r="P1" s="128"/>
+      <c r="Q1" s="128"/>
+      <c r="R1" s="129"/>
+      <c r="S1" s="133" t="s">
         <v>1</v>
       </c>
-      <c r="T1" s="169"/>
-      <c r="U1" s="163" t="s">
+      <c r="T1" s="133"/>
+      <c r="U1" s="130" t="s">
+        <v>164</v>
+      </c>
+      <c r="V1" s="131"/>
+      <c r="W1" s="131"/>
+      <c r="X1" s="131"/>
+      <c r="Y1" s="131"/>
+      <c r="Z1" s="132"/>
+      <c r="AA1" s="130" t="s">
         <v>165</v>
       </c>
-      <c r="V1" s="164"/>
-      <c r="W1" s="164"/>
-      <c r="X1" s="164"/>
-      <c r="Y1" s="164"/>
-      <c r="Z1" s="165"/>
-      <c r="AA1" s="163" t="s">
+      <c r="AB1" s="131"/>
+      <c r="AC1" s="131"/>
+      <c r="AD1" s="131"/>
+      <c r="AE1" s="131"/>
+      <c r="AF1" s="131"/>
+      <c r="AG1" s="131"/>
+      <c r="AH1" s="131"/>
+      <c r="AI1" s="131"/>
+      <c r="AJ1" s="131"/>
+      <c r="AK1" s="131"/>
+      <c r="AL1" s="131"/>
+      <c r="AM1" s="131"/>
+      <c r="AN1" s="131"/>
+      <c r="AO1" s="132"/>
+      <c r="AP1" s="130" t="s">
         <v>166</v>
       </c>
-      <c r="AB1" s="164"/>
-      <c r="AC1" s="164"/>
-      <c r="AD1" s="164"/>
-      <c r="AE1" s="164"/>
-      <c r="AF1" s="164"/>
-      <c r="AG1" s="164"/>
-      <c r="AH1" s="164"/>
-      <c r="AI1" s="164"/>
-      <c r="AJ1" s="164"/>
-      <c r="AK1" s="164"/>
-      <c r="AL1" s="164"/>
-      <c r="AM1" s="164"/>
-      <c r="AN1" s="164"/>
-      <c r="AO1" s="165"/>
-      <c r="AP1" s="163" t="s">
+      <c r="AQ1" s="131"/>
+      <c r="AR1" s="131"/>
+      <c r="AS1" s="131"/>
+      <c r="AT1" s="132"/>
+      <c r="AU1" s="130" t="s">
         <v>167</v>
       </c>
-      <c r="AQ1" s="164"/>
-      <c r="AR1" s="164"/>
-      <c r="AS1" s="164"/>
-      <c r="AT1" s="165"/>
-      <c r="AU1" s="163" t="s">
+      <c r="AV1" s="131"/>
+      <c r="AW1" s="131"/>
+      <c r="AX1" s="131"/>
+      <c r="AY1" s="131"/>
+      <c r="AZ1" s="132"/>
+      <c r="BA1" s="130" t="s">
         <v>168</v>
       </c>
-      <c r="AV1" s="164"/>
-      <c r="AW1" s="164"/>
-      <c r="AX1" s="164"/>
-      <c r="AY1" s="164"/>
-      <c r="AZ1" s="165"/>
-      <c r="BA1" s="163" t="s">
-        <v>169</v>
-      </c>
-      <c r="BB1" s="164"/>
-      <c r="BC1" s="165"/>
+      <c r="BB1" s="131"/>
+      <c r="BC1" s="132"/>
     </row>
     <row r="2" spans="1:121" s="1" customFormat="1" ht="140.44999999999999" customHeight="1" thickBot="1">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="134" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="152" t="s">
+      <c r="B2" s="134" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="152" t="s">
+      <c r="C2" s="134" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="152" t="s">
+      <c r="D2" s="134" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="152" t="s">
+      <c r="E2" s="134" t="s">
         <v>24</v>
       </c>
       <c r="F2" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="152" t="s">
+      <c r="G2" s="134" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="152" t="s">
+      <c r="H2" s="134" t="s">
         <v>6</v>
       </c>
       <c r="I2" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="151" t="s">
+      <c r="J2" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="152" t="s">
+      <c r="K2" s="134" t="s">
         <v>26</v>
       </c>
       <c r="L2" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="152" t="s">
+      <c r="M2" s="134" t="s">
         <v>10</v>
       </c>
       <c r="N2" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="152" t="s">
+      <c r="O2" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="P2" s="152" t="s">
+      <c r="P2" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="157" t="s">
+      <c r="Q2" s="140" t="s">
         <v>15</v>
       </c>
-      <c r="R2" s="153" t="s">
+      <c r="R2" s="135" t="s">
         <v>16</v>
       </c>
-      <c r="S2" s="154" t="s">
+      <c r="S2" s="136" t="s">
         <v>17</v>
       </c>
-      <c r="T2" s="170" t="s">
+      <c r="T2" s="138" t="s">
         <v>18</v>
       </c>
-      <c r="U2" s="172" t="s">
+      <c r="U2" s="121" t="s">
         <v>32</v>
       </c>
-      <c r="V2" s="173" t="s">
+      <c r="V2" s="122" t="s">
         <v>33</v>
       </c>
-      <c r="W2" s="173" t="s">
+      <c r="W2" s="122" t="s">
         <v>34</v>
       </c>
-      <c r="X2" s="173" t="s">
+      <c r="X2" s="122" t="s">
         <v>35</v>
       </c>
-      <c r="Y2" s="173" t="s">
+      <c r="Y2" s="122" t="s">
         <v>36</v>
       </c>
-      <c r="Z2" s="174" t="s">
+      <c r="Z2" s="123" t="s">
         <v>37</v>
       </c>
-      <c r="AA2" s="172" t="s">
+      <c r="AA2" s="121" t="s">
         <v>38</v>
       </c>
-      <c r="AB2" s="173" t="s">
+      <c r="AB2" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="AC2" s="173" t="s">
+      <c r="AC2" s="122" t="s">
         <v>40</v>
       </c>
-      <c r="AD2" s="173" t="s">
+      <c r="AD2" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="AE2" s="173" t="s">
+      <c r="AE2" s="122" t="s">
         <v>42</v>
       </c>
-      <c r="AF2" s="173" t="s">
+      <c r="AF2" s="122" t="s">
         <v>43</v>
       </c>
-      <c r="AG2" s="173" t="s">
+      <c r="AG2" s="122" t="s">
         <v>44</v>
       </c>
-      <c r="AH2" s="173" t="s">
+      <c r="AH2" s="122" t="s">
         <v>45</v>
       </c>
-      <c r="AI2" s="173" t="s">
+      <c r="AI2" s="122" t="s">
         <v>46</v>
       </c>
-      <c r="AJ2" s="173" t="s">
+      <c r="AJ2" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="AK2" s="173" t="s">
+      <c r="AK2" s="122" t="s">
         <v>48</v>
       </c>
-      <c r="AL2" s="173" t="s">
+      <c r="AL2" s="122" t="s">
         <v>49</v>
       </c>
-      <c r="AM2" s="173" t="s">
+      <c r="AM2" s="122" t="s">
         <v>50</v>
       </c>
-      <c r="AN2" s="173" t="s">
+      <c r="AN2" s="122" t="s">
         <v>51</v>
       </c>
-      <c r="AO2" s="174" t="s">
+      <c r="AO2" s="123" t="s">
         <v>52</v>
       </c>
-      <c r="AP2" s="172" t="s">
+      <c r="AP2" s="121" t="s">
         <v>53</v>
       </c>
-      <c r="AQ2" s="173" t="s">
+      <c r="AQ2" s="122" t="s">
         <v>54</v>
       </c>
-      <c r="AR2" s="173" t="s">
+      <c r="AR2" s="122" t="s">
         <v>55</v>
       </c>
-      <c r="AS2" s="173" t="s">
+      <c r="AS2" s="122" t="s">
         <v>56</v>
       </c>
-      <c r="AT2" s="174" t="s">
+      <c r="AT2" s="123" t="s">
         <v>57</v>
       </c>
-      <c r="AU2" s="172" t="s">
+      <c r="AU2" s="121" t="s">
         <v>58</v>
       </c>
-      <c r="AV2" s="173" t="s">
+      <c r="AV2" s="122" t="s">
         <v>59</v>
       </c>
-      <c r="AW2" s="175" t="s">
+      <c r="AW2" s="124" t="s">
         <v>60</v>
       </c>
-      <c r="AX2" s="175" t="s">
+      <c r="AX2" s="124" t="s">
         <v>61</v>
       </c>
-      <c r="AY2" s="175" t="s">
+      <c r="AY2" s="124" t="s">
         <v>62</v>
       </c>
-      <c r="AZ2" s="176" t="s">
+      <c r="AZ2" s="125" t="s">
         <v>63</v>
       </c>
-      <c r="BA2" s="177" t="s">
+      <c r="BA2" s="126" t="s">
         <v>64</v>
       </c>
-      <c r="BB2" s="175" t="s">
+      <c r="BB2" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="BC2" s="176" t="s">
+      <c r="BC2" s="125" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:121" s="1" customFormat="1" ht="21" hidden="1" customHeight="1" thickBot="1">
-      <c r="A3" s="152"/>
-      <c r="B3" s="152"/>
-      <c r="C3" s="152"/>
-      <c r="D3" s="152"/>
-      <c r="E3" s="152"/>
+      <c r="A3" s="134"/>
+      <c r="B3" s="134"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="134"/>
+      <c r="E3" s="134"/>
       <c r="F3" s="54"/>
-      <c r="G3" s="152"/>
-      <c r="H3" s="152"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="134"/>
       <c r="I3" s="54"/>
-      <c r="J3" s="151"/>
-      <c r="K3" s="152"/>
+      <c r="J3" s="141"/>
+      <c r="K3" s="134"/>
       <c r="L3" s="54"/>
-      <c r="M3" s="152"/>
+      <c r="M3" s="134"/>
       <c r="N3" s="54"/>
-      <c r="O3" s="152"/>
-      <c r="P3" s="152"/>
-      <c r="Q3" s="157"/>
-      <c r="R3" s="153"/>
-      <c r="S3" s="155"/>
-      <c r="T3" s="156"/>
-      <c r="U3" s="171" t="e">
+      <c r="O3" s="134"/>
+      <c r="P3" s="134"/>
+      <c r="Q3" s="140"/>
+      <c r="R3" s="135"/>
+      <c r="S3" s="137"/>
+      <c r="T3" s="139"/>
+      <c r="U3" s="120" t="e">
         <f>U4/$R$4</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="V3" s="171" t="e">
+      <c r="V3" s="120" t="e">
         <f t="shared" ref="V3:BC3" si="0">V4/$R$4</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="W3" s="171" t="e">
+      <c r="W3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X3" s="171" t="e">
+      <c r="X3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y3" s="171" t="e">
+      <c r="Y3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z3" s="171" t="e">
+      <c r="Z3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA3" s="171" t="e">
+      <c r="AA3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB3" s="171" t="e">
+      <c r="AB3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC3" s="171" t="e">
+      <c r="AC3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD3" s="171" t="e">
+      <c r="AD3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE3" s="171" t="e">
+      <c r="AE3" s="120" t="e">
         <f>AE4/$R$4</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF3" s="171" t="e">
+      <c r="AF3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AG3" s="171" t="e">
+      <c r="AG3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH3" s="171" t="e">
+      <c r="AH3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI3" s="171" t="e">
+      <c r="AI3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AJ3" s="171" t="e">
+      <c r="AJ3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AK3" s="171" t="e">
+      <c r="AK3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AL3" s="171" t="e">
+      <c r="AL3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM3" s="171" t="e">
+      <c r="AM3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN3" s="171" t="e">
+      <c r="AN3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AO3" s="171" t="e">
+      <c r="AO3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AP3" s="171" t="e">
+      <c r="AP3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ3" s="171" t="e">
+      <c r="AQ3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AR3" s="171" t="e">
+      <c r="AR3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS3" s="171" t="e">
+      <c r="AS3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT3" s="171" t="e">
+      <c r="AT3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU3" s="171" t="e">
+      <c r="AU3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AV3" s="171" t="e">
+      <c r="AV3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AW3" s="171" t="e">
+      <c r="AW3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX3" s="171" t="e">
+      <c r="AX3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AY3" s="171" t="e">
+      <c r="AY3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AZ3" s="171" t="e">
+      <c r="AZ3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA3" s="171" t="e">
+      <c r="BA3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB3" s="171" t="e">
+      <c r="BB3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BC3" s="171" t="e">
+      <c r="BC3" s="120" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="4" spans="1:121" s="1" customFormat="1" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A4" s="161" t="s">
+      <c r="A4" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="162"/>
-      <c r="C4" s="162"/>
-      <c r="D4" s="162"/>
-      <c r="E4" s="162"/>
-      <c r="F4" s="162"/>
-      <c r="G4" s="162"/>
-      <c r="H4" s="162"/>
-      <c r="I4" s="162"/>
-      <c r="J4" s="162"/>
-      <c r="K4" s="162"/>
-      <c r="L4" s="162"/>
-      <c r="M4" s="162"/>
-      <c r="N4" s="162"/>
-      <c r="O4" s="162"/>
+      <c r="B4" s="119"/>
+      <c r="C4" s="119"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="119"/>
+      <c r="L4" s="119"/>
+      <c r="M4" s="119"/>
+      <c r="N4" s="119"/>
+      <c r="O4" s="119"/>
       <c r="P4" s="55">
         <f>SUM(P5:P12)</f>
         <v>0</v>
@@ -33852,65 +33935,65 @@
         <f>IF(H5&gt;=G5,H5-G5,H5-G5+1)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="111" t="s">
+      <c r="J5" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="K5" s="112"/>
-      <c r="L5" s="112"/>
-      <c r="M5" s="113"/>
-      <c r="N5" s="112"/>
+      <c r="K5" s="111"/>
+      <c r="L5" s="111"/>
+      <c r="M5" s="112"/>
+      <c r="N5" s="111"/>
       <c r="O5" s="53">
         <f>IF(LEFT(M5,2)="01","JAPAN",IF(LEFT(M5,2)="03","CHINA",IF(LEFT(M5,2)="07","EUROPE",IF(LEFT(M5,2)="14","AU",IF(LEFT(M5,2)="17","CANADA",IF(LEFT(M5,2)="36","INDIA",IF(LEFT(M5,2)="04","USA",IF(LEFT(M5,2)="27","MALAYSIA",IF(LEFT(M5,2)="05","KOREA",IF(LEFT(M5,2)="11","THAILAND",IF(LEFT(M5,2)="10","TAIWAN",)))))))))))</f>
         <v>0</v>
       </c>
-      <c r="P5" s="114"/>
-      <c r="Q5" s="111" t="s">
+      <c r="P5" s="113"/>
+      <c r="Q5" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="R5" s="115">
+      <c r="R5" s="114">
         <f>SUM(U5:BC5)</f>
         <v>0</v>
       </c>
-      <c r="S5" s="116" t="e">
+      <c r="S5" s="115" t="e">
         <f t="shared" ref="S5" si="2">R5/P5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T5" s="117"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="118"/>
-      <c r="W5" s="118"/>
-      <c r="X5" s="118"/>
-      <c r="Y5" s="118"/>
-      <c r="Z5" s="118"/>
-      <c r="AA5" s="118"/>
-      <c r="AB5" s="118"/>
-      <c r="AC5" s="118"/>
-      <c r="AD5" s="118"/>
-      <c r="AE5" s="118"/>
-      <c r="AF5" s="118"/>
-      <c r="AG5" s="118"/>
-      <c r="AH5" s="118"/>
-      <c r="AI5" s="118"/>
-      <c r="AJ5" s="118"/>
-      <c r="AK5" s="118"/>
-      <c r="AL5" s="118"/>
-      <c r="AM5" s="118"/>
-      <c r="AN5" s="118"/>
-      <c r="AO5" s="118"/>
-      <c r="AP5" s="118"/>
-      <c r="AQ5" s="118"/>
-      <c r="AR5" s="118"/>
-      <c r="AS5" s="118"/>
-      <c r="AT5" s="118"/>
-      <c r="AU5" s="118"/>
-      <c r="AV5" s="118"/>
-      <c r="AW5" s="118"/>
-      <c r="AX5" s="118"/>
-      <c r="AY5" s="118"/>
-      <c r="AZ5" s="118"/>
-      <c r="BA5" s="118"/>
-      <c r="BB5" s="118"/>
-      <c r="BC5" s="118"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="117"/>
+      <c r="V5" s="117"/>
+      <c r="W5" s="117"/>
+      <c r="X5" s="117"/>
+      <c r="Y5" s="117"/>
+      <c r="Z5" s="117"/>
+      <c r="AA5" s="117"/>
+      <c r="AB5" s="117"/>
+      <c r="AC5" s="117"/>
+      <c r="AD5" s="117"/>
+      <c r="AE5" s="117"/>
+      <c r="AF5" s="117"/>
+      <c r="AG5" s="117"/>
+      <c r="AH5" s="117"/>
+      <c r="AI5" s="117"/>
+      <c r="AJ5" s="117"/>
+      <c r="AK5" s="117"/>
+      <c r="AL5" s="117"/>
+      <c r="AM5" s="117"/>
+      <c r="AN5" s="117"/>
+      <c r="AO5" s="117"/>
+      <c r="AP5" s="117"/>
+      <c r="AQ5" s="117"/>
+      <c r="AR5" s="117"/>
+      <c r="AS5" s="117"/>
+      <c r="AT5" s="117"/>
+      <c r="AU5" s="117"/>
+      <c r="AV5" s="117"/>
+      <c r="AW5" s="117"/>
+      <c r="AX5" s="117"/>
+      <c r="AY5" s="117"/>
+      <c r="AZ5" s="117"/>
+      <c r="BA5" s="117"/>
+      <c r="BB5" s="117"/>
+      <c r="BC5" s="117"/>
       <c r="BD5" s="5"/>
       <c r="BE5" s="5"/>
       <c r="BF5" s="5"/>
@@ -33996,65 +34079,65 @@
         <f t="shared" ref="I6:I12" si="4">IF(H6&gt;=G6,H6-G6,H6-G6+1)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="111" t="s">
+      <c r="J6" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="K6" s="112"/>
-      <c r="L6" s="112"/>
-      <c r="M6" s="113"/>
-      <c r="N6" s="112"/>
+      <c r="K6" s="111"/>
+      <c r="L6" s="111"/>
+      <c r="M6" s="112"/>
+      <c r="N6" s="111"/>
       <c r="O6" s="53">
         <f t="shared" ref="O6:O12" si="5">IF(LEFT(M6,2)="01","JAPAN",IF(LEFT(M6,2)="03","CHINA",IF(LEFT(M6,2)="07","EUROPE",IF(LEFT(M6,2)="14","AU",IF(LEFT(M6,2)="17","CANADA",IF(LEFT(M6,2)="36","INDIA",IF(LEFT(M6,2)="04","USA",IF(LEFT(M6,2)="27","MALAYSIA",IF(LEFT(M6,2)="05","KOREA",IF(LEFT(M6,2)="11","THAILAND",IF(LEFT(M6,2)="10","TAIWAN",)))))))))))</f>
         <v>0</v>
       </c>
-      <c r="P6" s="114"/>
-      <c r="Q6" s="111" t="s">
+      <c r="P6" s="113"/>
+      <c r="Q6" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="R6" s="115">
+      <c r="R6" s="114">
         <f t="shared" ref="R6:R8" si="6">SUM(U6:BC6)</f>
         <v>0</v>
       </c>
-      <c r="S6" s="116" t="e">
+      <c r="S6" s="115" t="e">
         <f t="shared" ref="S6:S8" si="7">R6/P6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T6" s="117"/>
-      <c r="U6" s="118"/>
-      <c r="V6" s="118"/>
-      <c r="W6" s="118"/>
-      <c r="X6" s="118"/>
-      <c r="Y6" s="118"/>
-      <c r="Z6" s="118"/>
-      <c r="AA6" s="118"/>
-      <c r="AB6" s="118"/>
-      <c r="AC6" s="118"/>
-      <c r="AD6" s="118"/>
-      <c r="AE6" s="118"/>
-      <c r="AF6" s="118"/>
-      <c r="AG6" s="118"/>
-      <c r="AH6" s="118"/>
-      <c r="AI6" s="118"/>
-      <c r="AJ6" s="118"/>
-      <c r="AK6" s="118"/>
-      <c r="AL6" s="118"/>
-      <c r="AM6" s="118"/>
-      <c r="AN6" s="118"/>
-      <c r="AO6" s="118"/>
-      <c r="AP6" s="118"/>
-      <c r="AQ6" s="118"/>
-      <c r="AR6" s="118"/>
-      <c r="AS6" s="118"/>
-      <c r="AT6" s="118"/>
-      <c r="AU6" s="118"/>
-      <c r="AV6" s="118"/>
-      <c r="AW6" s="118"/>
-      <c r="AX6" s="118"/>
-      <c r="AY6" s="118"/>
-      <c r="AZ6" s="118"/>
-      <c r="BA6" s="118"/>
-      <c r="BB6" s="118"/>
-      <c r="BC6" s="118"/>
+      <c r="T6" s="116"/>
+      <c r="U6" s="117"/>
+      <c r="V6" s="117"/>
+      <c r="W6" s="117"/>
+      <c r="X6" s="117"/>
+      <c r="Y6" s="117"/>
+      <c r="Z6" s="117"/>
+      <c r="AA6" s="117"/>
+      <c r="AB6" s="117"/>
+      <c r="AC6" s="117"/>
+      <c r="AD6" s="117"/>
+      <c r="AE6" s="117"/>
+      <c r="AF6" s="117"/>
+      <c r="AG6" s="117"/>
+      <c r="AH6" s="117"/>
+      <c r="AI6" s="117"/>
+      <c r="AJ6" s="117"/>
+      <c r="AK6" s="117"/>
+      <c r="AL6" s="117"/>
+      <c r="AM6" s="117"/>
+      <c r="AN6" s="117"/>
+      <c r="AO6" s="117"/>
+      <c r="AP6" s="117"/>
+      <c r="AQ6" s="117"/>
+      <c r="AR6" s="117"/>
+      <c r="AS6" s="117"/>
+      <c r="AT6" s="117"/>
+      <c r="AU6" s="117"/>
+      <c r="AV6" s="117"/>
+      <c r="AW6" s="117"/>
+      <c r="AX6" s="117"/>
+      <c r="AY6" s="117"/>
+      <c r="AZ6" s="117"/>
+      <c r="BA6" s="117"/>
+      <c r="BB6" s="117"/>
+      <c r="BC6" s="117"/>
       <c r="BD6" s="5"/>
       <c r="BE6" s="5"/>
       <c r="BF6" s="5"/>
@@ -34140,65 +34223,65 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J7" s="111" t="s">
+      <c r="J7" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="K7" s="112"/>
-      <c r="L7" s="112"/>
-      <c r="M7" s="113"/>
-      <c r="N7" s="112"/>
+      <c r="K7" s="111"/>
+      <c r="L7" s="111"/>
+      <c r="M7" s="112"/>
+      <c r="N7" s="111"/>
       <c r="O7" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P7" s="114"/>
-      <c r="Q7" s="111" t="s">
+      <c r="P7" s="113"/>
+      <c r="Q7" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="R7" s="115">
+      <c r="R7" s="114">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="S7" s="116" t="e">
+      <c r="S7" s="115" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T7" s="117"/>
-      <c r="U7" s="118"/>
-      <c r="V7" s="118"/>
-      <c r="W7" s="118"/>
-      <c r="X7" s="118"/>
-      <c r="Y7" s="118"/>
-      <c r="Z7" s="118"/>
-      <c r="AA7" s="118"/>
-      <c r="AB7" s="118"/>
-      <c r="AC7" s="118"/>
-      <c r="AD7" s="118"/>
-      <c r="AE7" s="118"/>
-      <c r="AF7" s="118"/>
-      <c r="AG7" s="118"/>
-      <c r="AH7" s="118"/>
-      <c r="AI7" s="118"/>
-      <c r="AJ7" s="118"/>
-      <c r="AK7" s="118"/>
-      <c r="AL7" s="118"/>
-      <c r="AM7" s="118"/>
-      <c r="AN7" s="118"/>
-      <c r="AO7" s="118"/>
-      <c r="AP7" s="118"/>
-      <c r="AQ7" s="118"/>
-      <c r="AR7" s="118"/>
-      <c r="AS7" s="118"/>
-      <c r="AT7" s="118"/>
-      <c r="AU7" s="118"/>
-      <c r="AV7" s="118"/>
-      <c r="AW7" s="118"/>
-      <c r="AX7" s="118"/>
-      <c r="AY7" s="118"/>
-      <c r="AZ7" s="118"/>
-      <c r="BA7" s="118"/>
-      <c r="BB7" s="118"/>
-      <c r="BC7" s="118"/>
+      <c r="T7" s="116"/>
+      <c r="U7" s="117"/>
+      <c r="V7" s="117"/>
+      <c r="W7" s="117"/>
+      <c r="X7" s="117"/>
+      <c r="Y7" s="117"/>
+      <c r="Z7" s="117"/>
+      <c r="AA7" s="117"/>
+      <c r="AB7" s="117"/>
+      <c r="AC7" s="117"/>
+      <c r="AD7" s="117"/>
+      <c r="AE7" s="117"/>
+      <c r="AF7" s="117"/>
+      <c r="AG7" s="117"/>
+      <c r="AH7" s="117"/>
+      <c r="AI7" s="117"/>
+      <c r="AJ7" s="117"/>
+      <c r="AK7" s="117"/>
+      <c r="AL7" s="117"/>
+      <c r="AM7" s="117"/>
+      <c r="AN7" s="117"/>
+      <c r="AO7" s="117"/>
+      <c r="AP7" s="117"/>
+      <c r="AQ7" s="117"/>
+      <c r="AR7" s="117"/>
+      <c r="AS7" s="117"/>
+      <c r="AT7" s="117"/>
+      <c r="AU7" s="117"/>
+      <c r="AV7" s="117"/>
+      <c r="AW7" s="117"/>
+      <c r="AX7" s="117"/>
+      <c r="AY7" s="117"/>
+      <c r="AZ7" s="117"/>
+      <c r="BA7" s="117"/>
+      <c r="BB7" s="117"/>
+      <c r="BC7" s="117"/>
       <c r="BD7" s="5"/>
       <c r="BE7" s="5"/>
       <c r="BF7" s="5"/>
@@ -34284,65 +34367,65 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J8" s="111" t="s">
+      <c r="J8" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="K8" s="112"/>
-      <c r="L8" s="112"/>
-      <c r="M8" s="113"/>
-      <c r="N8" s="112"/>
+      <c r="K8" s="111"/>
+      <c r="L8" s="111"/>
+      <c r="M8" s="112"/>
+      <c r="N8" s="111"/>
       <c r="O8" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P8" s="114"/>
-      <c r="Q8" s="111" t="s">
+      <c r="P8" s="113"/>
+      <c r="Q8" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="R8" s="115">
+      <c r="R8" s="114">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="S8" s="116" t="e">
+      <c r="S8" s="115" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T8" s="117"/>
-      <c r="U8" s="118"/>
-      <c r="V8" s="118"/>
-      <c r="W8" s="118"/>
-      <c r="X8" s="118"/>
-      <c r="Y8" s="118"/>
-      <c r="Z8" s="118"/>
-      <c r="AA8" s="118"/>
-      <c r="AB8" s="118"/>
-      <c r="AC8" s="118"/>
-      <c r="AD8" s="118"/>
-      <c r="AE8" s="118"/>
-      <c r="AF8" s="118"/>
-      <c r="AG8" s="118"/>
-      <c r="AH8" s="118"/>
-      <c r="AI8" s="118"/>
-      <c r="AJ8" s="118"/>
-      <c r="AK8" s="118"/>
-      <c r="AL8" s="118"/>
-      <c r="AM8" s="118"/>
-      <c r="AN8" s="118"/>
-      <c r="AO8" s="118"/>
-      <c r="AP8" s="118"/>
-      <c r="AQ8" s="118"/>
-      <c r="AR8" s="118"/>
-      <c r="AS8" s="118"/>
-      <c r="AT8" s="118"/>
-      <c r="AU8" s="118"/>
-      <c r="AV8" s="118"/>
-      <c r="AW8" s="118"/>
-      <c r="AX8" s="118"/>
-      <c r="AY8" s="118"/>
-      <c r="AZ8" s="118"/>
-      <c r="BA8" s="118"/>
-      <c r="BB8" s="118"/>
-      <c r="BC8" s="118"/>
+      <c r="T8" s="116"/>
+      <c r="U8" s="117"/>
+      <c r="V8" s="117"/>
+      <c r="W8" s="117"/>
+      <c r="X8" s="117"/>
+      <c r="Y8" s="117"/>
+      <c r="Z8" s="117"/>
+      <c r="AA8" s="117"/>
+      <c r="AB8" s="117"/>
+      <c r="AC8" s="117"/>
+      <c r="AD8" s="117"/>
+      <c r="AE8" s="117"/>
+      <c r="AF8" s="117"/>
+      <c r="AG8" s="117"/>
+      <c r="AH8" s="117"/>
+      <c r="AI8" s="117"/>
+      <c r="AJ8" s="117"/>
+      <c r="AK8" s="117"/>
+      <c r="AL8" s="117"/>
+      <c r="AM8" s="117"/>
+      <c r="AN8" s="117"/>
+      <c r="AO8" s="117"/>
+      <c r="AP8" s="117"/>
+      <c r="AQ8" s="117"/>
+      <c r="AR8" s="117"/>
+      <c r="AS8" s="117"/>
+      <c r="AT8" s="117"/>
+      <c r="AU8" s="117"/>
+      <c r="AV8" s="117"/>
+      <c r="AW8" s="117"/>
+      <c r="AX8" s="117"/>
+      <c r="AY8" s="117"/>
+      <c r="AZ8" s="117"/>
+      <c r="BA8" s="117"/>
+      <c r="BB8" s="117"/>
+      <c r="BC8" s="117"/>
       <c r="BD8" s="5"/>
       <c r="BE8" s="5"/>
       <c r="BF8" s="5"/>
@@ -34428,65 +34511,65 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J9" s="111" t="s">
+      <c r="J9" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="K9" s="112"/>
-      <c r="L9" s="112"/>
-      <c r="M9" s="113"/>
-      <c r="N9" s="112"/>
+      <c r="K9" s="111"/>
+      <c r="L9" s="111"/>
+      <c r="M9" s="112"/>
+      <c r="N9" s="111"/>
       <c r="O9" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P9" s="114"/>
-      <c r="Q9" s="111" t="s">
+      <c r="P9" s="113"/>
+      <c r="Q9" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="R9" s="115">
+      <c r="R9" s="114">
         <f t="shared" ref="R9:R10" si="8">SUM(U9:BC9)</f>
         <v>0</v>
       </c>
-      <c r="S9" s="116" t="e">
+      <c r="S9" s="115" t="e">
         <f t="shared" ref="S9:S10" si="9">R9/P9</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T9" s="117"/>
-      <c r="U9" s="118"/>
-      <c r="V9" s="118"/>
-      <c r="W9" s="118"/>
-      <c r="X9" s="118"/>
-      <c r="Y9" s="118"/>
-      <c r="Z9" s="118"/>
-      <c r="AA9" s="118"/>
-      <c r="AB9" s="118"/>
-      <c r="AC9" s="118"/>
-      <c r="AD9" s="118"/>
-      <c r="AE9" s="118"/>
-      <c r="AF9" s="118"/>
-      <c r="AG9" s="118"/>
-      <c r="AH9" s="118"/>
-      <c r="AI9" s="118"/>
-      <c r="AJ9" s="118"/>
-      <c r="AK9" s="118"/>
-      <c r="AL9" s="118"/>
-      <c r="AM9" s="118"/>
-      <c r="AN9" s="118"/>
-      <c r="AO9" s="118"/>
-      <c r="AP9" s="118"/>
-      <c r="AQ9" s="118"/>
-      <c r="AR9" s="118"/>
-      <c r="AS9" s="118"/>
-      <c r="AT9" s="118"/>
-      <c r="AU9" s="118"/>
-      <c r="AV9" s="118"/>
-      <c r="AW9" s="118"/>
-      <c r="AX9" s="118"/>
-      <c r="AY9" s="118"/>
-      <c r="AZ9" s="118"/>
-      <c r="BA9" s="118"/>
-      <c r="BB9" s="118"/>
-      <c r="BC9" s="118"/>
+      <c r="T9" s="116"/>
+      <c r="U9" s="117"/>
+      <c r="V9" s="117"/>
+      <c r="W9" s="117"/>
+      <c r="X9" s="117"/>
+      <c r="Y9" s="117"/>
+      <c r="Z9" s="117"/>
+      <c r="AA9" s="117"/>
+      <c r="AB9" s="117"/>
+      <c r="AC9" s="117"/>
+      <c r="AD9" s="117"/>
+      <c r="AE9" s="117"/>
+      <c r="AF9" s="117"/>
+      <c r="AG9" s="117"/>
+      <c r="AH9" s="117"/>
+      <c r="AI9" s="117"/>
+      <c r="AJ9" s="117"/>
+      <c r="AK9" s="117"/>
+      <c r="AL9" s="117"/>
+      <c r="AM9" s="117"/>
+      <c r="AN9" s="117"/>
+      <c r="AO9" s="117"/>
+      <c r="AP9" s="117"/>
+      <c r="AQ9" s="117"/>
+      <c r="AR9" s="117"/>
+      <c r="AS9" s="117"/>
+      <c r="AT9" s="117"/>
+      <c r="AU9" s="117"/>
+      <c r="AV9" s="117"/>
+      <c r="AW9" s="117"/>
+      <c r="AX9" s="117"/>
+      <c r="AY9" s="117"/>
+      <c r="AZ9" s="117"/>
+      <c r="BA9" s="117"/>
+      <c r="BB9" s="117"/>
+      <c r="BC9" s="117"/>
       <c r="BD9" s="5"/>
       <c r="BE9" s="5"/>
       <c r="BF9" s="5"/>
@@ -34572,65 +34655,65 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J10" s="111" t="s">
+      <c r="J10" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="K10" s="112"/>
-      <c r="L10" s="112"/>
-      <c r="M10" s="113"/>
-      <c r="N10" s="112"/>
+      <c r="K10" s="111"/>
+      <c r="L10" s="111"/>
+      <c r="M10" s="112"/>
+      <c r="N10" s="111"/>
       <c r="O10" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P10" s="114"/>
-      <c r="Q10" s="111" t="s">
+      <c r="P10" s="113"/>
+      <c r="Q10" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="R10" s="115">
+      <c r="R10" s="114">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S10" s="116" t="e">
+      <c r="S10" s="115" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T10" s="117"/>
-      <c r="U10" s="118"/>
-      <c r="V10" s="118"/>
-      <c r="W10" s="118"/>
-      <c r="X10" s="118"/>
-      <c r="Y10" s="118"/>
-      <c r="Z10" s="118"/>
-      <c r="AA10" s="118"/>
-      <c r="AB10" s="118"/>
-      <c r="AC10" s="118"/>
-      <c r="AD10" s="118"/>
-      <c r="AE10" s="118"/>
-      <c r="AF10" s="118"/>
-      <c r="AG10" s="118"/>
-      <c r="AH10" s="118"/>
-      <c r="AI10" s="118"/>
-      <c r="AJ10" s="118"/>
-      <c r="AK10" s="118"/>
-      <c r="AL10" s="118"/>
-      <c r="AM10" s="118"/>
-      <c r="AN10" s="118"/>
-      <c r="AO10" s="118"/>
-      <c r="AP10" s="118"/>
-      <c r="AQ10" s="118"/>
-      <c r="AR10" s="118"/>
-      <c r="AS10" s="118"/>
-      <c r="AT10" s="118"/>
-      <c r="AU10" s="118"/>
-      <c r="AV10" s="118"/>
-      <c r="AW10" s="118"/>
-      <c r="AX10" s="118"/>
-      <c r="AY10" s="118"/>
-      <c r="AZ10" s="118"/>
-      <c r="BA10" s="118"/>
-      <c r="BB10" s="118"/>
-      <c r="BC10" s="118"/>
+      <c r="T10" s="116"/>
+      <c r="U10" s="117"/>
+      <c r="V10" s="117"/>
+      <c r="W10" s="117"/>
+      <c r="X10" s="117"/>
+      <c r="Y10" s="117"/>
+      <c r="Z10" s="117"/>
+      <c r="AA10" s="117"/>
+      <c r="AB10" s="117"/>
+      <c r="AC10" s="117"/>
+      <c r="AD10" s="117"/>
+      <c r="AE10" s="117"/>
+      <c r="AF10" s="117"/>
+      <c r="AG10" s="117"/>
+      <c r="AH10" s="117"/>
+      <c r="AI10" s="117"/>
+      <c r="AJ10" s="117"/>
+      <c r="AK10" s="117"/>
+      <c r="AL10" s="117"/>
+      <c r="AM10" s="117"/>
+      <c r="AN10" s="117"/>
+      <c r="AO10" s="117"/>
+      <c r="AP10" s="117"/>
+      <c r="AQ10" s="117"/>
+      <c r="AR10" s="117"/>
+      <c r="AS10" s="117"/>
+      <c r="AT10" s="117"/>
+      <c r="AU10" s="117"/>
+      <c r="AV10" s="117"/>
+      <c r="AW10" s="117"/>
+      <c r="AX10" s="117"/>
+      <c r="AY10" s="117"/>
+      <c r="AZ10" s="117"/>
+      <c r="BA10" s="117"/>
+      <c r="BB10" s="117"/>
+      <c r="BC10" s="117"/>
       <c r="BD10" s="5"/>
       <c r="BE10" s="5"/>
       <c r="BF10" s="5"/>
@@ -34716,65 +34799,65 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J11" s="111" t="s">
+      <c r="J11" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="K11" s="112"/>
-      <c r="L11" s="112"/>
-      <c r="M11" s="113"/>
-      <c r="N11" s="112"/>
+      <c r="K11" s="111"/>
+      <c r="L11" s="111"/>
+      <c r="M11" s="112"/>
+      <c r="N11" s="111"/>
       <c r="O11" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P11" s="114"/>
-      <c r="Q11" s="111" t="s">
+      <c r="P11" s="113"/>
+      <c r="Q11" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="R11" s="115">
+      <c r="R11" s="114">
         <f t="shared" ref="R11:R12" si="10">SUM(U11:BC11)</f>
         <v>0</v>
       </c>
-      <c r="S11" s="116" t="e">
+      <c r="S11" s="115" t="e">
         <f t="shared" ref="S11:S12" si="11">R11/P11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T11" s="117"/>
-      <c r="U11" s="118"/>
-      <c r="V11" s="118"/>
-      <c r="W11" s="118"/>
-      <c r="X11" s="118"/>
-      <c r="Y11" s="118"/>
-      <c r="Z11" s="118"/>
-      <c r="AA11" s="118"/>
-      <c r="AB11" s="118"/>
-      <c r="AC11" s="118"/>
-      <c r="AD11" s="118"/>
-      <c r="AE11" s="118"/>
-      <c r="AF11" s="118"/>
-      <c r="AG11" s="118"/>
-      <c r="AH11" s="118"/>
-      <c r="AI11" s="118"/>
-      <c r="AJ11" s="118"/>
-      <c r="AK11" s="118"/>
-      <c r="AL11" s="118"/>
-      <c r="AM11" s="118"/>
-      <c r="AN11" s="118"/>
-      <c r="AO11" s="118"/>
-      <c r="AP11" s="118"/>
-      <c r="AQ11" s="118"/>
-      <c r="AR11" s="118"/>
-      <c r="AS11" s="118"/>
-      <c r="AT11" s="118"/>
-      <c r="AU11" s="118"/>
-      <c r="AV11" s="118"/>
-      <c r="AW11" s="118"/>
-      <c r="AX11" s="118"/>
-      <c r="AY11" s="118"/>
-      <c r="AZ11" s="118"/>
-      <c r="BA11" s="118"/>
-      <c r="BB11" s="118"/>
-      <c r="BC11" s="118"/>
+      <c r="T11" s="116"/>
+      <c r="U11" s="117"/>
+      <c r="V11" s="117"/>
+      <c r="W11" s="117"/>
+      <c r="X11" s="117"/>
+      <c r="Y11" s="117"/>
+      <c r="Z11" s="117"/>
+      <c r="AA11" s="117"/>
+      <c r="AB11" s="117"/>
+      <c r="AC11" s="117"/>
+      <c r="AD11" s="117"/>
+      <c r="AE11" s="117"/>
+      <c r="AF11" s="117"/>
+      <c r="AG11" s="117"/>
+      <c r="AH11" s="117"/>
+      <c r="AI11" s="117"/>
+      <c r="AJ11" s="117"/>
+      <c r="AK11" s="117"/>
+      <c r="AL11" s="117"/>
+      <c r="AM11" s="117"/>
+      <c r="AN11" s="117"/>
+      <c r="AO11" s="117"/>
+      <c r="AP11" s="117"/>
+      <c r="AQ11" s="117"/>
+      <c r="AR11" s="117"/>
+      <c r="AS11" s="117"/>
+      <c r="AT11" s="117"/>
+      <c r="AU11" s="117"/>
+      <c r="AV11" s="117"/>
+      <c r="AW11" s="117"/>
+      <c r="AX11" s="117"/>
+      <c r="AY11" s="117"/>
+      <c r="AZ11" s="117"/>
+      <c r="BA11" s="117"/>
+      <c r="BB11" s="117"/>
+      <c r="BC11" s="117"/>
       <c r="BD11" s="5"/>
       <c r="BE11" s="5"/>
       <c r="BF11" s="5"/>
@@ -34860,65 +34943,65 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J12" s="111" t="s">
+      <c r="J12" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="K12" s="112"/>
-      <c r="L12" s="112"/>
-      <c r="M12" s="113"/>
-      <c r="N12" s="112"/>
+      <c r="K12" s="111"/>
+      <c r="L12" s="111"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="111"/>
       <c r="O12" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P12" s="114"/>
-      <c r="Q12" s="111" t="s">
+      <c r="P12" s="113"/>
+      <c r="Q12" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="R12" s="115">
+      <c r="R12" s="114">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S12" s="116" t="e">
+      <c r="S12" s="115" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T12" s="117"/>
-      <c r="U12" s="118"/>
-      <c r="V12" s="118"/>
-      <c r="W12" s="118"/>
-      <c r="X12" s="118"/>
-      <c r="Y12" s="118"/>
-      <c r="Z12" s="118"/>
-      <c r="AA12" s="118"/>
-      <c r="AB12" s="118"/>
-      <c r="AC12" s="118"/>
-      <c r="AD12" s="118"/>
-      <c r="AE12" s="118"/>
-      <c r="AF12" s="118"/>
-      <c r="AG12" s="118"/>
-      <c r="AH12" s="118"/>
-      <c r="AI12" s="118"/>
-      <c r="AJ12" s="118"/>
-      <c r="AK12" s="118"/>
-      <c r="AL12" s="118"/>
-      <c r="AM12" s="118"/>
-      <c r="AN12" s="118"/>
-      <c r="AO12" s="118"/>
-      <c r="AP12" s="118"/>
-      <c r="AQ12" s="118"/>
-      <c r="AR12" s="118"/>
-      <c r="AS12" s="118"/>
-      <c r="AT12" s="118"/>
-      <c r="AU12" s="118"/>
-      <c r="AV12" s="118"/>
-      <c r="AW12" s="118"/>
-      <c r="AX12" s="118"/>
-      <c r="AY12" s="118"/>
-      <c r="AZ12" s="118"/>
-      <c r="BA12" s="118"/>
-      <c r="BB12" s="118"/>
-      <c r="BC12" s="118"/>
+      <c r="T12" s="116"/>
+      <c r="U12" s="117"/>
+      <c r="V12" s="117"/>
+      <c r="W12" s="117"/>
+      <c r="X12" s="117"/>
+      <c r="Y12" s="117"/>
+      <c r="Z12" s="117"/>
+      <c r="AA12" s="117"/>
+      <c r="AB12" s="117"/>
+      <c r="AC12" s="117"/>
+      <c r="AD12" s="117"/>
+      <c r="AE12" s="117"/>
+      <c r="AF12" s="117"/>
+      <c r="AG12" s="117"/>
+      <c r="AH12" s="117"/>
+      <c r="AI12" s="117"/>
+      <c r="AJ12" s="117"/>
+      <c r="AK12" s="117"/>
+      <c r="AL12" s="117"/>
+      <c r="AM12" s="117"/>
+      <c r="AN12" s="117"/>
+      <c r="AO12" s="117"/>
+      <c r="AP12" s="117"/>
+      <c r="AQ12" s="117"/>
+      <c r="AR12" s="117"/>
+      <c r="AS12" s="117"/>
+      <c r="AT12" s="117"/>
+      <c r="AU12" s="117"/>
+      <c r="AV12" s="117"/>
+      <c r="AW12" s="117"/>
+      <c r="AX12" s="117"/>
+      <c r="AY12" s="117"/>
+      <c r="AZ12" s="117"/>
+      <c r="BA12" s="117"/>
+      <c r="BB12" s="117"/>
+      <c r="BC12" s="117"/>
       <c r="BD12" s="5"/>
       <c r="BE12" s="5"/>
       <c r="BF12" s="5"/>
@@ -35093,18 +35176,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="U1:Z1"/>
-    <mergeCell ref="AP1:AT1"/>
-    <mergeCell ref="AU1:AZ1"/>
-    <mergeCell ref="BA1:BC1"/>
-    <mergeCell ref="AA1:AO1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="R2:R3"/>
@@ -35116,6 +35187,18 @@
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="O2:O3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="U1:Z1"/>
+    <mergeCell ref="AP1:AT1"/>
+    <mergeCell ref="AU1:AZ1"/>
+    <mergeCell ref="BA1:BC1"/>
+    <mergeCell ref="AA1:AO1"/>
+    <mergeCell ref="S1:T1"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.3" footer="0.3"/>
